--- a/database/event/5274/event_5274_evp_summary.xlsx
+++ b/database/event/5274/event_5274_evp_summary.xlsx
@@ -502,7 +502,7 @@
         <v>0.5552</v>
       </c>
       <c r="D2" t="n">
-        <v>1.1801</v>
+        <v>1.1354</v>
       </c>
       <c r="E2" t="n">
         <v>3.9642</v>
@@ -548,7 +548,7 @@
         <v>0.5282</v>
       </c>
       <c r="D3" t="n">
-        <v>1.1022</v>
+        <v>1.0587</v>
       </c>
       <c r="E3" t="n">
         <v>3.7715</v>
@@ -594,7 +594,7 @@
         <v>0.5044999999999999</v>
       </c>
       <c r="D4" t="n">
-        <v>1.0338</v>
+        <v>0.9912</v>
       </c>
       <c r="E4" t="n">
         <v>3.6021</v>
@@ -640,7 +640,7 @@
         <v>0.3906</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7053</v>
+        <v>0.6671</v>
       </c>
       <c r="E5" t="n">
         <v>2.7888</v>
@@ -686,7 +686,7 @@
         <v>0.3886</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6997</v>
+        <v>0.6616</v>
       </c>
       <c r="E6" t="n">
         <v>2.775</v>
@@ -732,7 +732,7 @@
         <v>0.3418</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5647</v>
+        <v>0.5285</v>
       </c>
       <c r="E7" t="n">
         <v>2.4408</v>
@@ -778,7 +778,7 @@
         <v>0.3387</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5556</v>
+        <v>0.5195</v>
       </c>
       <c r="E8" t="n">
         <v>2.4183</v>
@@ -824,7 +824,7 @@
         <v>0.241</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2737</v>
+        <v>0.2415</v>
       </c>
       <c r="E9" t="n">
         <v>1.7205</v>
@@ -870,7 +870,7 @@
         <v>0.2333</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2516</v>
+        <v>0.2197</v>
       </c>
       <c r="E10" t="n">
         <v>1.6658</v>
@@ -916,7 +916,7 @@
         <v>0.2215</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2176</v>
+        <v>0.1862</v>
       </c>
       <c r="E11" t="n">
         <v>1.5816</v>
@@ -962,7 +962,7 @@
         <v>0.1957</v>
       </c>
       <c r="D12" t="n">
-        <v>0.1433</v>
+        <v>0.1129</v>
       </c>
       <c r="E12" t="n">
         <v>1.3977</v>
@@ -1008,7 +1008,7 @@
         <v>0.1353</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.0311</v>
+        <v>-0.0591</v>
       </c>
       <c r="E13" t="n">
         <v>0.966</v>
@@ -1054,7 +1054,7 @@
         <v>0.1344</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.0337</v>
+        <v>-0.0616</v>
       </c>
       <c r="E14" t="n">
         <v>0.9595</v>
@@ -1100,7 +1100,7 @@
         <v>0.0602</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.2478</v>
+        <v>-0.2728</v>
       </c>
       <c r="E15" t="n">
         <v>0.4296</v>
@@ -1146,7 +1146,7 @@
         <v>0.0512</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.2736</v>
+        <v>-0.2982</v>
       </c>
       <c r="E16" t="n">
         <v>0.3658</v>
@@ -1192,7 +1192,7 @@
         <v>-0.0823</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.6589</v>
+        <v>-0.6781</v>
       </c>
       <c r="E17" t="n">
         <v>-0.5879</v>
@@ -1238,7 +1238,7 @@
         <v>-0.0984</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.7050999999999999</v>
+        <v>-0.7237</v>
       </c>
       <c r="E18" t="n">
         <v>-0.7024</v>
@@ -1284,7 +1284,7 @@
         <v>-0.1158</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.7552</v>
+        <v>-0.7732</v>
       </c>
       <c r="E19" t="n">
         <v>-0.8265</v>
@@ -1330,7 +1330,7 @@
         <v>-0.2222</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.0624</v>
+        <v>-1.0761</v>
       </c>
       <c r="E20" t="n">
         <v>-1.5869</v>
@@ -1376,7 +1376,7 @@
         <v>-0.2765</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.2189</v>
+        <v>-1.2305</v>
       </c>
       <c r="E21" t="n">
         <v>-1.9743</v>

--- a/database/event/5274/event_5274_evp_summary.xlsx
+++ b/database/event/5274/event_5274_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.9642</v>
+        <v>4.3072</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5552</v>
+        <v>0.6032</v>
       </c>
       <c r="D2" t="n">
-        <v>1.1354</v>
+        <v>1.3065</v>
       </c>
       <c r="E2" t="n">
-        <v>3.9642</v>
+        <v>4.3072</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6526999999999999</v>
+        <v>1.3413</v>
       </c>
       <c r="G2" t="n">
-        <v>3.3115</v>
+        <v>2.9659</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6526999999999999</v>
+        <v>1.3413</v>
       </c>
       <c r="I2" t="n">
-        <v>0.529</v>
+        <v>0.6974</v>
       </c>
       <c r="J2" t="n">
-        <v>3.3115</v>
+        <v>2.9659</v>
       </c>
       <c r="K2" t="n">
         <v>171</v>
@@ -529,7 +529,7 @@
         <v>133</v>
       </c>
       <c r="M2" t="n">
-        <v>3.8405</v>
+        <v>3.6633</v>
       </c>
       <c r="N2" t="n">
         <v>304</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.7715</v>
+        <v>3.6499</v>
       </c>
       <c r="C3" t="n">
-        <v>0.5282</v>
+        <v>0.5112</v>
       </c>
       <c r="D3" t="n">
-        <v>1.0587</v>
+        <v>1.0097</v>
       </c>
       <c r="E3" t="n">
-        <v>3.7715</v>
+        <v>3.6499</v>
       </c>
       <c r="F3" t="n">
-        <v>3.1693</v>
+        <v>3.0074</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6022</v>
+        <v>0.6425</v>
       </c>
       <c r="H3" t="n">
-        <v>3.1693</v>
+        <v>5.1099</v>
       </c>
       <c r="I3" t="n">
-        <v>2.5688</v>
+        <v>2.6569</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6022</v>
+        <v>0.6425</v>
       </c>
       <c r="K3" t="n">
         <v>164</v>
@@ -575,7 +575,7 @@
         <v>55</v>
       </c>
       <c r="M3" t="n">
-        <v>3.171</v>
+        <v>3.2994</v>
       </c>
       <c r="N3" t="n">
         <v>219</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.6021</v>
+        <v>3.6451</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5044999999999999</v>
+        <v>0.5105</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9912</v>
+        <v>1.0076</v>
       </c>
       <c r="E4" t="n">
-        <v>3.6021</v>
+        <v>3.6451</v>
       </c>
       <c r="F4" t="n">
-        <v>2.5111</v>
+        <v>2.7735</v>
       </c>
       <c r="G4" t="n">
-        <v>1.091</v>
+        <v>0.8716</v>
       </c>
       <c r="H4" t="n">
-        <v>2.5111</v>
+        <v>4.2858</v>
       </c>
       <c r="I4" t="n">
-        <v>2.0353</v>
+        <v>2.2284</v>
       </c>
       <c r="J4" t="n">
-        <v>1.091</v>
+        <v>0.8716</v>
       </c>
       <c r="K4" t="n">
         <v>83</v>
@@ -621,7 +621,7 @@
         <v>119</v>
       </c>
       <c r="M4" t="n">
-        <v>3.1263</v>
+        <v>3.1</v>
       </c>
       <c r="N4" t="n">
         <v>202</v>
@@ -630,231 +630,231 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>yuurih</t>
+          <t>Ethan</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.7888</v>
+        <v>3.0976</v>
       </c>
       <c r="C5" t="n">
-        <v>0.3906</v>
+        <v>0.4338</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6671</v>
+        <v>0.7604</v>
       </c>
       <c r="E5" t="n">
-        <v>2.7888</v>
+        <v>3.0976</v>
       </c>
       <c r="F5" t="n">
-        <v>2.4904</v>
+        <v>2.2116</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2984</v>
+        <v>0.886</v>
       </c>
       <c r="H5" t="n">
-        <v>2.4904</v>
+        <v>2.306</v>
       </c>
       <c r="I5" t="n">
-        <v>2.0185</v>
+        <v>1.199</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2984</v>
+        <v>0.886</v>
       </c>
       <c r="K5" t="n">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="L5" t="n">
-        <v>55</v>
+        <v>133</v>
       </c>
       <c r="M5" t="n">
-        <v>2.3169</v>
+        <v>2.085</v>
       </c>
       <c r="N5" t="n">
-        <v>219</v>
+        <v>304</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Ethan</t>
+          <t>yuurih</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.775</v>
+        <v>3.0897</v>
       </c>
       <c r="C6" t="n">
-        <v>0.3886</v>
+        <v>0.4327</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6616</v>
+        <v>0.7568</v>
       </c>
       <c r="E6" t="n">
-        <v>2.775</v>
+        <v>3.0897</v>
       </c>
       <c r="F6" t="n">
-        <v>1.434</v>
+        <v>2.7356</v>
       </c>
       <c r="G6" t="n">
-        <v>1.341</v>
+        <v>0.3541</v>
       </c>
       <c r="H6" t="n">
-        <v>1.434</v>
+        <v>4.1523</v>
       </c>
       <c r="I6" t="n">
-        <v>1.1623</v>
+        <v>2.159</v>
       </c>
       <c r="J6" t="n">
-        <v>1.341</v>
+        <v>0.3541</v>
       </c>
       <c r="K6" t="n">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="L6" t="n">
-        <v>133</v>
+        <v>55</v>
       </c>
       <c r="M6" t="n">
-        <v>2.5033</v>
+        <v>2.5131</v>
       </c>
       <c r="N6" t="n">
-        <v>304</v>
+        <v>219</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>kNgV-</t>
+          <t>KSCERATO</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.4408</v>
+        <v>2.8882</v>
       </c>
       <c r="C7" t="n">
-        <v>0.3418</v>
+        <v>0.4045</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5285</v>
+        <v>0.6659</v>
       </c>
       <c r="E7" t="n">
-        <v>2.4408</v>
+        <v>2.8882</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5194</v>
+        <v>2.843</v>
       </c>
       <c r="G7" t="n">
-        <v>1.9214</v>
+        <v>0.0452</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5194</v>
+        <v>4.5308</v>
       </c>
       <c r="I7" t="n">
-        <v>0.421</v>
+        <v>2.3558</v>
       </c>
       <c r="J7" t="n">
-        <v>1.9214</v>
+        <v>0.0452</v>
       </c>
       <c r="K7" t="n">
-        <v>83</v>
+        <v>164</v>
       </c>
       <c r="L7" t="n">
-        <v>119</v>
+        <v>55</v>
       </c>
       <c r="M7" t="n">
-        <v>2.3424</v>
+        <v>2.401</v>
       </c>
       <c r="N7" t="n">
-        <v>202</v>
+        <v>219</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>KSCERATO</t>
+          <t>kNgV-</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.4183</v>
+        <v>2.5113</v>
       </c>
       <c r="C8" t="n">
-        <v>0.3387</v>
+        <v>0.3517</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5195</v>
+        <v>0.4957</v>
       </c>
       <c r="E8" t="n">
-        <v>2.4183</v>
+        <v>2.5113</v>
       </c>
       <c r="F8" t="n">
-        <v>2.4583</v>
+        <v>0.8539</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.04</v>
+        <v>1.6574</v>
       </c>
       <c r="H8" t="n">
-        <v>2.4583</v>
+        <v>0.8539</v>
       </c>
       <c r="I8" t="n">
-        <v>1.9925</v>
+        <v>0.444</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.04</v>
+        <v>1.6574</v>
       </c>
       <c r="K8" t="n">
-        <v>164</v>
+        <v>83</v>
       </c>
       <c r="L8" t="n">
-        <v>55</v>
+        <v>119</v>
       </c>
       <c r="M8" t="n">
-        <v>1.9525</v>
+        <v>2.1014</v>
       </c>
       <c r="N8" t="n">
-        <v>219</v>
+        <v>202</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Brehze</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.7205</v>
+        <v>2.4118</v>
       </c>
       <c r="C9" t="n">
-        <v>0.241</v>
+        <v>0.3378</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2415</v>
+        <v>0.4508</v>
       </c>
       <c r="E9" t="n">
-        <v>1.7205</v>
+        <v>2.4118</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.2475</v>
+        <v>2.6426</v>
       </c>
       <c r="G9" t="n">
-        <v>1.968</v>
+        <v>-0.2308</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.2475</v>
+        <v>3.8246</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2006</v>
+        <v>1.9886</v>
       </c>
       <c r="J9" t="n">
-        <v>1.968</v>
+        <v>-0.2308</v>
       </c>
       <c r="K9" t="n">
-        <v>171</v>
+        <v>83</v>
       </c>
       <c r="L9" t="n">
-        <v>133</v>
+        <v>119</v>
       </c>
       <c r="M9" t="n">
-        <v>1.7674</v>
+        <v>1.7578</v>
       </c>
       <c r="N9" t="n">
-        <v>304</v>
+        <v>202</v>
       </c>
     </row>
     <row r="10">
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.6658</v>
+        <v>2.3364</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2333</v>
+        <v>0.3272</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2197</v>
+        <v>0.4168</v>
       </c>
       <c r="E10" t="n">
-        <v>1.6658</v>
+        <v>2.3364</v>
       </c>
       <c r="F10" t="n">
-        <v>2.0426</v>
+        <v>2.5019</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.3768</v>
+        <v>-0.1655</v>
       </c>
       <c r="H10" t="n">
-        <v>2.0426</v>
+        <v>3.3288</v>
       </c>
       <c r="I10" t="n">
-        <v>1.6556</v>
+        <v>1.7308</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.3768</v>
+        <v>-0.1655</v>
       </c>
       <c r="K10" t="n">
         <v>83</v>
@@ -897,7 +897,7 @@
         <v>119</v>
       </c>
       <c r="M10" t="n">
-        <v>1.2788</v>
+        <v>1.5653</v>
       </c>
       <c r="N10" t="n">
         <v>202</v>
@@ -906,231 +906,231 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>arT</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.5816</v>
+        <v>2.2695</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2215</v>
+        <v>0.3178</v>
       </c>
       <c r="D11" t="n">
-        <v>0.1862</v>
+        <v>0.3866</v>
       </c>
       <c r="E11" t="n">
-        <v>1.5816</v>
+        <v>2.2695</v>
       </c>
       <c r="F11" t="n">
-        <v>2.2482</v>
+        <v>2.4088</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.6666</v>
+        <v>-0.1393</v>
       </c>
       <c r="H11" t="n">
-        <v>2.2482</v>
+        <v>3.0006</v>
       </c>
       <c r="I11" t="n">
-        <v>1.8222</v>
+        <v>1.5602</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.6666</v>
+        <v>-0.1393</v>
       </c>
       <c r="K11" t="n">
-        <v>83</v>
+        <v>164</v>
       </c>
       <c r="L11" t="n">
-        <v>119</v>
+        <v>55</v>
       </c>
       <c r="M11" t="n">
-        <v>1.1556</v>
+        <v>1.4209</v>
       </c>
       <c r="N11" t="n">
-        <v>202</v>
+        <v>219</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>arT</t>
+          <t>Brehze</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.3977</v>
+        <v>2.1524</v>
       </c>
       <c r="C12" t="n">
-        <v>0.1957</v>
+        <v>0.3014</v>
       </c>
       <c r="D12" t="n">
-        <v>0.1129</v>
+        <v>0.3337</v>
       </c>
       <c r="E12" t="n">
-        <v>1.3977</v>
+        <v>2.1524</v>
       </c>
       <c r="F12" t="n">
-        <v>1.6658</v>
+        <v>0.4775</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.2681</v>
+        <v>1.6749</v>
       </c>
       <c r="H12" t="n">
-        <v>1.6658</v>
+        <v>0.4775</v>
       </c>
       <c r="I12" t="n">
-        <v>1.3502</v>
+        <v>0.2483</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.2681</v>
+        <v>1.6749</v>
       </c>
       <c r="K12" t="n">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="L12" t="n">
-        <v>55</v>
+        <v>133</v>
       </c>
       <c r="M12" t="n">
-        <v>1.0821</v>
+        <v>1.9232</v>
       </c>
       <c r="N12" t="n">
-        <v>219</v>
+        <v>304</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>stanislaw</t>
+          <t>NAF</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.966</v>
+        <v>1.5323</v>
       </c>
       <c r="C13" t="n">
-        <v>0.1353</v>
+        <v>0.2146</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.0591</v>
+        <v>0.0537</v>
       </c>
       <c r="E13" t="n">
-        <v>0.966</v>
+        <v>1.5323</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.0672</v>
+        <v>1.3557</v>
       </c>
       <c r="G13" t="n">
-        <v>1.0332</v>
+        <v>0.1766</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.0672</v>
+        <v>1.3557</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.0545</v>
+        <v>0.7049</v>
       </c>
       <c r="J13" t="n">
-        <v>1.0332</v>
+        <v>0.1766</v>
       </c>
       <c r="K13" t="n">
-        <v>171</v>
+        <v>76</v>
       </c>
       <c r="L13" t="n">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="M13" t="n">
-        <v>0.9786999999999999</v>
+        <v>0.8815</v>
       </c>
       <c r="N13" t="n">
-        <v>304</v>
+        <v>145</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>NAF</t>
+          <t>stanislaw</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.9595</v>
+        <v>1.3922</v>
       </c>
       <c r="C14" t="n">
-        <v>0.1344</v>
+        <v>0.195</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.0616</v>
+        <v>-0.0095</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9595</v>
+        <v>1.3922</v>
       </c>
       <c r="F14" t="n">
-        <v>1.0266</v>
+        <v>0.5431</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.06710000000000001</v>
+        <v>0.8491</v>
       </c>
       <c r="H14" t="n">
-        <v>1.0266</v>
+        <v>0.5431</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8321</v>
+        <v>0.2824</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.06710000000000001</v>
+        <v>0.8491</v>
       </c>
       <c r="K14" t="n">
-        <v>76</v>
+        <v>171</v>
       </c>
       <c r="L14" t="n">
-        <v>69</v>
+        <v>133</v>
       </c>
       <c r="M14" t="n">
-        <v>0.7649999999999999</v>
+        <v>1.1315</v>
       </c>
       <c r="N14" t="n">
-        <v>145</v>
+        <v>304</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>VINI</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.4296</v>
+        <v>0.6394</v>
       </c>
       <c r="C15" t="n">
-        <v>0.0602</v>
+        <v>0.0895</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.2728</v>
+        <v>-0.3494</v>
       </c>
       <c r="E15" t="n">
-        <v>0.4296</v>
+        <v>0.6394</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.3065</v>
+        <v>0.4943</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7361</v>
+        <v>0.1451</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.3065</v>
+        <v>0.4943</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2484</v>
+        <v>0.257</v>
       </c>
       <c r="J15" t="n">
-        <v>0.7361</v>
+        <v>0.1451</v>
       </c>
       <c r="K15" t="n">
-        <v>76</v>
+        <v>164</v>
       </c>
       <c r="L15" t="n">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="M15" t="n">
-        <v>0.4877</v>
+        <v>0.4021</v>
       </c>
       <c r="N15" t="n">
-        <v>145</v>
+        <v>219</v>
       </c>
     </row>
     <row r="16">
@@ -1140,31 +1140,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.3658</v>
+        <v>0.5152</v>
       </c>
       <c r="C16" t="n">
-        <v>0.0512</v>
+        <v>0.0722</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.2982</v>
+        <v>-0.4054</v>
       </c>
       <c r="E16" t="n">
-        <v>0.3658</v>
+        <v>0.5152</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.3968</v>
+        <v>-0.2539</v>
       </c>
       <c r="G16" t="n">
-        <v>0.7625999999999999</v>
+        <v>0.7691</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.3968</v>
+        <v>-0.2539</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3216</v>
+        <v>-0.132</v>
       </c>
       <c r="J16" t="n">
-        <v>0.7625999999999999</v>
+        <v>0.7691</v>
       </c>
       <c r="K16" t="n">
         <v>76</v>
@@ -1173,7 +1173,7 @@
         <v>69</v>
       </c>
       <c r="M16" t="n">
-        <v>0.4409999999999999</v>
+        <v>0.6371</v>
       </c>
       <c r="N16" t="n">
         <v>145</v>
@@ -1182,47 +1182,47 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>VINI</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-0.5879</v>
+        <v>0.4069</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.0823</v>
+        <v>0.057</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.6781</v>
+        <v>-0.4543</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.5879</v>
+        <v>0.4069</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.5621</v>
+        <v>-0.0544</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.0258</v>
+        <v>0.4613</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.5621</v>
+        <v>-0.0544</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.4556</v>
+        <v>-0.0283</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.0258</v>
+        <v>0.4613</v>
       </c>
       <c r="K17" t="n">
-        <v>164</v>
+        <v>76</v>
       </c>
       <c r="L17" t="n">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.4814</v>
+        <v>0.433</v>
       </c>
       <c r="N17" t="n">
-        <v>219</v>
+        <v>145</v>
       </c>
     </row>
     <row r="18">
@@ -1232,31 +1232,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.7024</v>
+        <v>-0.1993</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.0984</v>
+        <v>-0.0279</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.7237</v>
+        <v>-0.728</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.7024</v>
+        <v>-0.1993</v>
       </c>
       <c r="F18" t="n">
-        <v>0.06510000000000001</v>
+        <v>0.2044</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.7675</v>
+        <v>-0.4037</v>
       </c>
       <c r="H18" t="n">
-        <v>0.06510000000000001</v>
+        <v>0.2044</v>
       </c>
       <c r="I18" t="n">
-        <v>0.0528</v>
+        <v>0.1063</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.7675</v>
+        <v>-0.4037</v>
       </c>
       <c r="K18" t="n">
         <v>76</v>
@@ -1265,7 +1265,7 @@
         <v>69</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.7147</v>
+        <v>-0.2974</v>
       </c>
       <c r="N18" t="n">
         <v>145</v>
@@ -1278,31 +1278,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.8265</v>
+        <v>-0.3913</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.1158</v>
+        <v>-0.0548</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.7732</v>
+        <v>-0.8147</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.8265</v>
+        <v>-0.3913</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.596</v>
+        <v>-0.6258</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.2305</v>
+        <v>0.2345</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.596</v>
+        <v>-0.6258</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.4831</v>
+        <v>-0.3254</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.2305</v>
+        <v>0.2345</v>
       </c>
       <c r="K19" t="n">
         <v>83</v>
@@ -1311,7 +1311,7 @@
         <v>119</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.7136</v>
+        <v>-0.09090000000000004</v>
       </c>
       <c r="N19" t="n">
         <v>202</v>
@@ -1324,31 +1324,31 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-1.5869</v>
+        <v>-1.3688</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.2222</v>
+        <v>-0.1917</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.0761</v>
+        <v>-1.256</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.5869</v>
+        <v>-1.3688</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.8861</v>
+        <v>-1.9481</v>
       </c>
       <c r="G20" t="n">
-        <v>0.2992</v>
+        <v>0.5793</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.8861</v>
+        <v>-1.9481</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.5287</v>
+        <v>-1.0129</v>
       </c>
       <c r="J20" t="n">
-        <v>0.2992</v>
+        <v>0.5793</v>
       </c>
       <c r="K20" t="n">
         <v>171</v>
@@ -1357,7 +1357,7 @@
         <v>133</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.2295</v>
+        <v>-0.4335999999999999</v>
       </c>
       <c r="N20" t="n">
         <v>304</v>
@@ -1370,31 +1370,31 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-1.9743</v>
+        <v>-1.8927</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.2765</v>
+        <v>-0.2651</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.2305</v>
+        <v>-1.4925</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.9743</v>
+        <v>-1.8927</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.2338</v>
+        <v>-1.4299</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.7405</v>
+        <v>-0.4628</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.2338</v>
+        <v>-1.4299</v>
       </c>
       <c r="I21" t="n">
-        <v>-1</v>
+        <v>-0.7435</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.7405</v>
+        <v>-0.4628</v>
       </c>
       <c r="K21" t="n">
         <v>76</v>
@@ -1403,7 +1403,7 @@
         <v>69</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.7405</v>
+        <v>-1.2063</v>
       </c>
       <c r="N21" t="n">
         <v>145</v>
@@ -1509,10 +1509,10 @@
         <v>1.43</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6806</v>
+        <v>0.8361</v>
       </c>
       <c r="J2" t="n">
-        <v>20.418</v>
+        <v>25.083</v>
       </c>
     </row>
     <row r="3">
@@ -1549,10 +1549,10 @@
         <v>1.11</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2433</v>
+        <v>0.2656</v>
       </c>
       <c r="J3" t="n">
-        <v>7.299</v>
+        <v>7.968</v>
       </c>
     </row>
     <row r="4">
@@ -1589,10 +1589,10 @@
         <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.0048</v>
+        <v>-0.0002</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.144</v>
+        <v>-0.006</v>
       </c>
     </row>
     <row r="5">
@@ -1629,10 +1629,10 @@
         <v>0.76</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4408</v>
+        <v>-0.279</v>
       </c>
       <c r="J5" t="n">
-        <v>-13.224</v>
+        <v>-8.369999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -1669,10 +1669,10 @@
         <v>0.72</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4947</v>
+        <v>-0.3177</v>
       </c>
       <c r="J6" t="n">
-        <v>-14.841</v>
+        <v>-9.531000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -1709,10 +1709,10 @@
         <v>1.47</v>
       </c>
       <c r="I7" t="n">
-        <v>1.2119</v>
+        <v>1.1291</v>
       </c>
       <c r="J7" t="n">
-        <v>36.357</v>
+        <v>33.873</v>
       </c>
     </row>
     <row r="8">
@@ -1749,10 +1749,10 @@
         <v>1.31</v>
       </c>
       <c r="I8" t="n">
-        <v>0.87</v>
+        <v>0.8501</v>
       </c>
       <c r="J8" t="n">
-        <v>26.1</v>
+        <v>25.503</v>
       </c>
     </row>
     <row r="9">
@@ -1789,10 +1789,10 @@
         <v>1.11</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3474</v>
+        <v>0.3495</v>
       </c>
       <c r="J9" t="n">
-        <v>10.422</v>
+        <v>10.485</v>
       </c>
     </row>
     <row r="10">
@@ -1829,10 +1829,10 @@
         <v>0.84</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.6039</v>
+        <v>-0.5448</v>
       </c>
       <c r="J10" t="n">
-        <v>-18.117</v>
+        <v>-16.344</v>
       </c>
     </row>
     <row r="11">
@@ -1869,10 +1869,10 @@
         <v>0.78</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.7511</v>
+        <v>-0.7018</v>
       </c>
       <c r="J11" t="n">
-        <v>-22.533</v>
+        <v>-21.054</v>
       </c>
     </row>
     <row r="12">
@@ -1909,10 +1909,10 @@
         <v>1.63</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8882</v>
+        <v>1.0765</v>
       </c>
       <c r="J12" t="n">
-        <v>30.1988</v>
+        <v>36.601</v>
       </c>
     </row>
     <row r="13">
@@ -1949,10 +1949,10 @@
         <v>1.15</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2862</v>
+        <v>0.3293</v>
       </c>
       <c r="J13" t="n">
-        <v>9.7308</v>
+        <v>11.1962</v>
       </c>
     </row>
     <row r="14">
@@ -1989,10 +1989,10 @@
         <v>0.92</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2114</v>
+        <v>-0.1184</v>
       </c>
       <c r="J14" t="n">
-        <v>-7.1876</v>
+        <v>-4.0256</v>
       </c>
     </row>
     <row r="15">
@@ -2029,10 +2029,10 @@
         <v>0.83</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3537</v>
+        <v>-0.2156</v>
       </c>
       <c r="J15" t="n">
-        <v>-12.0258</v>
+        <v>-7.3304</v>
       </c>
     </row>
     <row r="16">
@@ -2069,10 +2069,10 @@
         <v>0.78</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4246</v>
+        <v>-0.2659</v>
       </c>
       <c r="J16" t="n">
-        <v>-14.4364</v>
+        <v>-9.0406</v>
       </c>
     </row>
     <row r="17">
@@ -2109,10 +2109,10 @@
         <v>1.32</v>
       </c>
       <c r="I17" t="n">
-        <v>0.9226</v>
+        <v>0.8977000000000001</v>
       </c>
       <c r="J17" t="n">
-        <v>31.3684</v>
+        <v>30.5218</v>
       </c>
     </row>
     <row r="18">
@@ -2149,10 +2149,10 @@
         <v>1.1</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3627</v>
+        <v>0.3339</v>
       </c>
       <c r="J18" t="n">
-        <v>12.3318</v>
+        <v>11.3526</v>
       </c>
     </row>
     <row r="19">
@@ -2189,10 +2189,10 @@
         <v>1.03</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1006</v>
+        <v>0.1213</v>
       </c>
       <c r="J19" t="n">
-        <v>3.4204</v>
+        <v>4.1242</v>
       </c>
     </row>
     <row r="20">
@@ -2229,10 +2229,10 @@
         <v>0.97</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1937</v>
+        <v>-0.1421</v>
       </c>
       <c r="J20" t="n">
-        <v>-6.5858</v>
+        <v>-4.8314</v>
       </c>
     </row>
     <row r="21">
@@ -2269,10 +2269,10 @@
         <v>0.82</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.6357</v>
+        <v>-0.5829</v>
       </c>
       <c r="J21" t="n">
-        <v>-21.6138</v>
+        <v>-19.8186</v>
       </c>
     </row>
     <row r="22">
@@ -2309,10 +2309,10 @@
         <v>1.42</v>
       </c>
       <c r="I22" t="n">
-        <v>0.6361</v>
+        <v>0.5551</v>
       </c>
       <c r="J22" t="n">
-        <v>19.083</v>
+        <v>16.653</v>
       </c>
     </row>
     <row r="23">
@@ -2349,10 +2349,10 @@
         <v>1.29</v>
       </c>
       <c r="I23" t="n">
-        <v>0.4724</v>
+        <v>0.4028</v>
       </c>
       <c r="J23" t="n">
-        <v>14.172</v>
+        <v>12.084</v>
       </c>
     </row>
     <row r="24">
@@ -2389,10 +2389,10 @@
         <v>1.02</v>
       </c>
       <c r="I24" t="n">
-        <v>0.0117</v>
+        <v>0.0358</v>
       </c>
       <c r="J24" t="n">
-        <v>0.351</v>
+        <v>1.074</v>
       </c>
     </row>
     <row r="25">
@@ -2429,10 +2429,10 @@
         <v>0.9</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.2556</v>
+        <v>-0.1458</v>
       </c>
       <c r="J25" t="n">
-        <v>-7.668</v>
+        <v>-4.374</v>
       </c>
     </row>
     <row r="26">
@@ -2469,10 +2469,10 @@
         <v>0.9</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.2556</v>
+        <v>-0.1458</v>
       </c>
       <c r="J26" t="n">
-        <v>-7.668</v>
+        <v>-4.374</v>
       </c>
     </row>
     <row r="27">
@@ -2509,10 +2509,10 @@
         <v>1.48</v>
       </c>
       <c r="I27" t="n">
-        <v>0.736</v>
+        <v>0.6992</v>
       </c>
       <c r="J27" t="n">
-        <v>22.08</v>
+        <v>20.976</v>
       </c>
     </row>
     <row r="28">
@@ -2549,10 +2549,10 @@
         <v>1.02</v>
       </c>
       <c r="I28" t="n">
-        <v>0.059</v>
+        <v>0.0491</v>
       </c>
       <c r="J28" t="n">
-        <v>1.77</v>
+        <v>1.473</v>
       </c>
     </row>
     <row r="29">
@@ -2589,10 +2589,10 @@
         <v>0.89</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.249</v>
+        <v>-0.1468</v>
       </c>
       <c r="J29" t="n">
-        <v>-7.47</v>
+        <v>-4.404</v>
       </c>
     </row>
     <row r="30">
@@ -2629,10 +2629,10 @@
         <v>0.87</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.2814</v>
+        <v>-0.1685</v>
       </c>
       <c r="J30" t="n">
-        <v>-8.442</v>
+        <v>-5.055</v>
       </c>
     </row>
     <row r="31">
@@ -2669,10 +2669,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.3724</v>
+        <v>-0.2306</v>
       </c>
       <c r="J31" t="n">
-        <v>-11.172</v>
+        <v>-6.918</v>
       </c>
     </row>
     <row r="32">
@@ -2709,10 +2709,10 @@
         <v>1.19</v>
       </c>
       <c r="I32" t="n">
-        <v>0.3726</v>
+        <v>0.4235</v>
       </c>
       <c r="J32" t="n">
-        <v>11.178</v>
+        <v>12.705</v>
       </c>
     </row>
     <row r="33">
@@ -2749,10 +2749,10 @@
         <v>1.09</v>
       </c>
       <c r="I33" t="n">
-        <v>0.2145</v>
+        <v>0.2283</v>
       </c>
       <c r="J33" t="n">
-        <v>6.435</v>
+        <v>6.849</v>
       </c>
     </row>
     <row r="34">
@@ -2789,10 +2789,10 @@
         <v>1.04</v>
       </c>
       <c r="I34" t="n">
-        <v>0.1191</v>
+        <v>0.118</v>
       </c>
       <c r="J34" t="n">
-        <v>3.573</v>
+        <v>3.54</v>
       </c>
     </row>
     <row r="35">
@@ -2829,10 +2829,10 @@
         <v>0.89</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.2417</v>
+        <v>-0.1441</v>
       </c>
       <c r="J35" t="n">
-        <v>-7.251</v>
+        <v>-4.323</v>
       </c>
     </row>
     <row r="36">
@@ -2869,10 +2869,10 @@
         <v>0.74</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.4652</v>
+        <v>-0.2968</v>
       </c>
       <c r="J36" t="n">
-        <v>-13.956</v>
+        <v>-8.904</v>
       </c>
     </row>
     <row r="37">
@@ -2909,10 +2909,10 @@
         <v>1.19</v>
       </c>
       <c r="I37" t="n">
-        <v>0.6179</v>
+        <v>0.5785</v>
       </c>
       <c r="J37" t="n">
-        <v>18.537</v>
+        <v>17.355</v>
       </c>
     </row>
     <row r="38">
@@ -2949,10 +2949,10 @@
         <v>1.12</v>
       </c>
       <c r="I38" t="n">
-        <v>0.4281</v>
+        <v>0.392</v>
       </c>
       <c r="J38" t="n">
-        <v>12.843</v>
+        <v>11.76</v>
       </c>
     </row>
     <row r="39">
@@ -2989,10 +2989,10 @@
         <v>0.99</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.1045</v>
+        <v>-0.0623</v>
       </c>
       <c r="J39" t="n">
-        <v>-3.135</v>
+        <v>-1.869</v>
       </c>
     </row>
     <row r="40">
@@ -3029,10 +3029,10 @@
         <v>0.96</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.2258</v>
+        <v>-0.1747</v>
       </c>
       <c r="J40" t="n">
-        <v>-6.774</v>
+        <v>-5.241</v>
       </c>
     </row>
     <row r="41">
@@ -3069,10 +3069,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.294</v>
+        <v>-0.2399</v>
       </c>
       <c r="J41" t="n">
-        <v>-8.82</v>
+        <v>-7.197</v>
       </c>
     </row>
     <row r="42">
@@ -3109,10 +3109,10 @@
         <v>1.23</v>
       </c>
       <c r="I42" t="n">
-        <v>0.4091</v>
+        <v>0.4776</v>
       </c>
       <c r="J42" t="n">
-        <v>11.4548</v>
+        <v>13.3728</v>
       </c>
     </row>
     <row r="43">
@@ -3149,10 +3149,10 @@
         <v>1.08</v>
       </c>
       <c r="I43" t="n">
-        <v>0.1708</v>
+        <v>0.195</v>
       </c>
       <c r="J43" t="n">
-        <v>4.7824</v>
+        <v>5.46</v>
       </c>
     </row>
     <row r="44">
@@ -3189,10 +3189,10 @@
         <v>1.03</v>
       </c>
       <c r="I44" t="n">
-        <v>0.0567</v>
+        <v>0.0854</v>
       </c>
       <c r="J44" t="n">
-        <v>1.5876</v>
+        <v>2.3912</v>
       </c>
     </row>
     <row r="45">
@@ -3229,10 +3229,10 @@
         <v>1.02</v>
       </c>
       <c r="I45" t="n">
-        <v>0.0327</v>
+        <v>0.0597</v>
       </c>
       <c r="J45" t="n">
-        <v>0.9156</v>
+        <v>1.6716</v>
       </c>
     </row>
     <row r="46">
@@ -3269,10 +3269,10 @@
         <v>0.89</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.2587</v>
+        <v>-0.1508</v>
       </c>
       <c r="J46" t="n">
-        <v>-7.2436</v>
+        <v>-4.2224</v>
       </c>
     </row>
     <row r="47">
@@ -3309,10 +3309,10 @@
         <v>1.3</v>
       </c>
       <c r="I47" t="n">
-        <v>0.8774999999999999</v>
+        <v>0.8496</v>
       </c>
       <c r="J47" t="n">
-        <v>24.57</v>
+        <v>23.7888</v>
       </c>
     </row>
     <row r="48">
@@ -3349,10 +3349,10 @@
         <v>1.18</v>
       </c>
       <c r="I48" t="n">
-        <v>0.5871</v>
+        <v>0.5496</v>
       </c>
       <c r="J48" t="n">
-        <v>16.4388</v>
+        <v>15.3888</v>
       </c>
     </row>
     <row r="49">
@@ -3389,10 +3389,10 @@
         <v>1.07</v>
       </c>
       <c r="I49" t="n">
-        <v>0.265</v>
+        <v>0.2471</v>
       </c>
       <c r="J49" t="n">
-        <v>7.42</v>
+        <v>6.9188</v>
       </c>
     </row>
     <row r="50">
@@ -3429,10 +3429,10 @@
         <v>0.91</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.3913</v>
+        <v>-0.3334</v>
       </c>
       <c r="J50" t="n">
-        <v>-10.9564</v>
+        <v>-9.3352</v>
       </c>
     </row>
     <row r="51">
@@ -3469,10 +3469,10 @@
         <v>0.78</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.7342</v>
+        <v>-0.6869</v>
       </c>
       <c r="J51" t="n">
-        <v>-20.5576</v>
+        <v>-19.2332</v>
       </c>
     </row>
     <row r="52">
@@ -3509,10 +3509,10 @@
         <v>1.01</v>
       </c>
       <c r="I52" t="n">
-        <v>0.0716</v>
+        <v>0.0381</v>
       </c>
       <c r="J52" t="n">
-        <v>2.0048</v>
+        <v>1.0668</v>
       </c>
     </row>
     <row r="53">
@@ -3549,10 +3549,10 @@
         <v>0.97</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.049</v>
+        <v>-0.0452</v>
       </c>
       <c r="J53" t="n">
-        <v>-1.372</v>
+        <v>-1.2656</v>
       </c>
     </row>
     <row r="54">
@@ -3589,10 +3589,10 @@
         <v>0.92</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.1659</v>
+        <v>-0.1054</v>
       </c>
       <c r="J54" t="n">
-        <v>-4.6452</v>
+        <v>-2.9512</v>
       </c>
     </row>
     <row r="55">
@@ -3629,10 +3629,10 @@
         <v>0.9</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.2044</v>
+        <v>-0.1276</v>
       </c>
       <c r="J55" t="n">
-        <v>-5.7232</v>
+        <v>-3.5728</v>
       </c>
     </row>
     <row r="56">
@@ -3669,10 +3669,10 @@
         <v>0.89</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.2225</v>
+        <v>-0.1384</v>
       </c>
       <c r="J56" t="n">
-        <v>-6.23</v>
+        <v>-3.8752</v>
       </c>
     </row>
     <row r="57">
@@ -3709,10 +3709,10 @@
         <v>1.5</v>
       </c>
       <c r="I57" t="n">
-        <v>0.6996</v>
+        <v>0.6215000000000001</v>
       </c>
       <c r="J57" t="n">
-        <v>19.5888</v>
+        <v>17.402</v>
       </c>
     </row>
     <row r="58">
@@ -3749,10 +3749,10 @@
         <v>1.37</v>
       </c>
       <c r="I58" t="n">
-        <v>0.5433</v>
+        <v>0.4775</v>
       </c>
       <c r="J58" t="n">
-        <v>15.2124</v>
+        <v>13.37</v>
       </c>
     </row>
     <row r="59">
@@ -3789,10 +3789,10 @@
         <v>1.31</v>
       </c>
       <c r="I59" t="n">
-        <v>0.4653</v>
+        <v>0.4092</v>
       </c>
       <c r="J59" t="n">
-        <v>13.0284</v>
+        <v>11.4576</v>
       </c>
     </row>
     <row r="60">
@@ -3829,10 +3829,10 @@
         <v>0.98</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.1305</v>
+        <v>-0.0567</v>
       </c>
       <c r="J60" t="n">
-        <v>-3.654</v>
+        <v>-1.5876</v>
       </c>
     </row>
     <row r="61">
@@ -3869,10 +3869,10 @@
         <v>0.89</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.291</v>
+        <v>-0.1673</v>
       </c>
       <c r="J61" t="n">
-        <v>-8.148</v>
+        <v>-4.6844</v>
       </c>
     </row>
     <row r="62">
@@ -3909,10 +3909,10 @@
         <v>1.81</v>
       </c>
       <c r="I62" t="n">
-        <v>1.67</v>
+        <v>1.4507</v>
       </c>
       <c r="J62" t="n">
-        <v>33.4</v>
+        <v>29.014</v>
       </c>
     </row>
     <row r="63">
@@ -3949,10 +3949,10 @@
         <v>1.62</v>
       </c>
       <c r="I63" t="n">
-        <v>1.3185</v>
+        <v>1.2331</v>
       </c>
       <c r="J63" t="n">
-        <v>26.37</v>
+        <v>24.662</v>
       </c>
     </row>
     <row r="64">
@@ -3989,10 +3989,10 @@
         <v>1.57</v>
       </c>
       <c r="I64" t="n">
-        <v>1.2182</v>
+        <v>1.1751</v>
       </c>
       <c r="J64" t="n">
-        <v>24.364</v>
+        <v>23.502</v>
       </c>
     </row>
     <row r="65">
@@ -4029,10 +4029,10 @@
         <v>1.52</v>
       </c>
       <c r="I65" t="n">
-        <v>1.1106</v>
+        <v>1.1171</v>
       </c>
       <c r="J65" t="n">
-        <v>22.212</v>
+        <v>22.342</v>
       </c>
     </row>
     <row r="66">
@@ -4069,10 +4069,10 @@
         <v>0.97</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.336</v>
+        <v>-0.2474</v>
       </c>
       <c r="J66" t="n">
-        <v>-6.72</v>
+        <v>-4.948</v>
       </c>
     </row>
     <row r="67">
@@ -4109,10 +4109,10 @@
         <v>0.88</v>
       </c>
       <c r="I67" t="n">
-        <v>-0.0877</v>
+        <v>-0.0988</v>
       </c>
       <c r="J67" t="n">
-        <v>-1.754</v>
+        <v>-1.976</v>
       </c>
     </row>
     <row r="68">
@@ -4149,10 +4149,10 @@
         <v>0.85</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.1373</v>
+        <v>-0.1341</v>
       </c>
       <c r="J68" t="n">
-        <v>-2.746</v>
+        <v>-2.682</v>
       </c>
     </row>
     <row r="69">
@@ -4189,10 +4189,10 @@
         <v>0.59</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.5728</v>
+        <v>-0.3915</v>
       </c>
       <c r="J69" t="n">
-        <v>-11.456</v>
+        <v>-7.83</v>
       </c>
     </row>
     <row r="70">
@@ -4229,10 +4229,10 @@
         <v>0.49</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.7131</v>
+        <v>-0.4851</v>
       </c>
       <c r="J70" t="n">
-        <v>-14.262</v>
+        <v>-9.702</v>
       </c>
     </row>
     <row r="71">
@@ -4269,10 +4269,10 @@
         <v>0.48</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.7264</v>
+        <v>-0.4945</v>
       </c>
       <c r="J71" t="n">
-        <v>-14.528</v>
+        <v>-9.890000000000001</v>
       </c>
     </row>
     <row r="72">
@@ -4309,10 +4309,10 @@
         <v>1.33</v>
       </c>
       <c r="I72" t="n">
-        <v>0.8953</v>
+        <v>0.8831</v>
       </c>
       <c r="J72" t="n">
-        <v>31.3355</v>
+        <v>30.9085</v>
       </c>
     </row>
     <row r="73">
@@ -4349,10 +4349,10 @@
         <v>1.33</v>
       </c>
       <c r="I73" t="n">
-        <v>0.8953</v>
+        <v>0.8831</v>
       </c>
       <c r="J73" t="n">
-        <v>31.3355</v>
+        <v>30.9085</v>
       </c>
     </row>
     <row r="74">
@@ -4389,10 +4389,10 @@
         <v>1.25</v>
       </c>
       <c r="I74" t="n">
-        <v>0.7087</v>
+        <v>0.6941000000000001</v>
       </c>
       <c r="J74" t="n">
-        <v>24.8045</v>
+        <v>24.2935</v>
       </c>
     </row>
     <row r="75">
@@ -4429,10 +4429,10 @@
         <v>1</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.09810000000000001</v>
+        <v>-0.0328</v>
       </c>
       <c r="J75" t="n">
-        <v>-3.4335</v>
+        <v>-1.148</v>
       </c>
     </row>
     <row r="76">
@@ -4469,10 +4469,10 @@
         <v>0.78</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.7612</v>
+        <v>-0.7112000000000001</v>
       </c>
       <c r="J76" t="n">
-        <v>-26.642</v>
+        <v>-24.892</v>
       </c>
     </row>
     <row r="77">
@@ -4509,10 +4509,10 @@
         <v>1.37</v>
       </c>
       <c r="I77" t="n">
-        <v>0.6077</v>
+        <v>0.7356</v>
       </c>
       <c r="J77" t="n">
-        <v>21.2695</v>
+        <v>25.746</v>
       </c>
     </row>
     <row r="78">
@@ -4549,10 +4549,10 @@
         <v>1.08</v>
       </c>
       <c r="I78" t="n">
-        <v>0.1911</v>
+        <v>0.204</v>
       </c>
       <c r="J78" t="n">
-        <v>6.6885</v>
+        <v>7.14</v>
       </c>
     </row>
     <row r="79">
@@ -4589,10 +4589,10 @@
         <v>0.97</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.0941</v>
+        <v>-0.0504</v>
       </c>
       <c r="J79" t="n">
-        <v>-3.2935</v>
+        <v>-1.764</v>
       </c>
     </row>
     <row r="80">
@@ -4629,10 +4629,10 @@
         <v>0.85</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.3101</v>
+        <v>-0.1884</v>
       </c>
       <c r="J80" t="n">
-        <v>-10.8535</v>
+        <v>-6.594</v>
       </c>
     </row>
     <row r="81">
@@ -4669,10 +4669,10 @@
         <v>0.75</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.4545</v>
+        <v>-0.2888</v>
       </c>
       <c r="J81" t="n">
-        <v>-15.9075</v>
+        <v>-10.108</v>
       </c>
     </row>
     <row r="82">
@@ -4709,10 +4709,10 @@
         <v>1.72</v>
       </c>
       <c r="I82" t="n">
-        <v>1.5798</v>
+        <v>1.3812</v>
       </c>
       <c r="J82" t="n">
-        <v>41.0748</v>
+        <v>35.9112</v>
       </c>
     </row>
     <row r="83">
@@ -4749,10 +4749,10 @@
         <v>1.41</v>
       </c>
       <c r="I83" t="n">
-        <v>0.9684</v>
+        <v>0.9932</v>
       </c>
       <c r="J83" t="n">
-        <v>25.1784</v>
+        <v>25.8232</v>
       </c>
     </row>
     <row r="84">
@@ -4789,10 +4789,10 @@
         <v>1.22</v>
       </c>
       <c r="I84" t="n">
-        <v>0.492</v>
+        <v>0.5839</v>
       </c>
       <c r="J84" t="n">
-        <v>12.792</v>
+        <v>15.1814</v>
       </c>
     </row>
     <row r="85">
@@ -4829,10 +4829,10 @@
         <v>1.19</v>
       </c>
       <c r="I85" t="n">
-        <v>0.4181</v>
+        <v>0.5103</v>
       </c>
       <c r="J85" t="n">
-        <v>10.8706</v>
+        <v>13.2678</v>
       </c>
     </row>
     <row r="86">
@@ -4869,10 +4869,10 @@
         <v>1.11</v>
       </c>
       <c r="I86" t="n">
-        <v>0.2118</v>
+        <v>0.3003</v>
       </c>
       <c r="J86" t="n">
-        <v>5.5068</v>
+        <v>7.8078</v>
       </c>
     </row>
     <row r="87">
@@ -4909,10 +4909,10 @@
         <v>1.02</v>
       </c>
       <c r="I87" t="n">
-        <v>0.1585</v>
+        <v>0.1322</v>
       </c>
       <c r="J87" t="n">
-        <v>4.121</v>
+        <v>3.4372</v>
       </c>
     </row>
     <row r="88">
@@ -4949,10 +4949,10 @@
         <v>1.01</v>
       </c>
       <c r="I88" t="n">
-        <v>0.1336</v>
+        <v>0.1016</v>
       </c>
       <c r="J88" t="n">
-        <v>3.4736</v>
+        <v>2.6416</v>
       </c>
     </row>
     <row r="89">
@@ -4989,10 +4989,10 @@
         <v>0.88</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.1515</v>
+        <v>-0.132</v>
       </c>
       <c r="J89" t="n">
-        <v>-3.939</v>
+        <v>-3.432</v>
       </c>
     </row>
     <row r="90">
@@ -5029,10 +5029,10 @@
         <v>0.7</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.466</v>
+        <v>-0.3091</v>
       </c>
       <c r="J90" t="n">
-        <v>-12.116</v>
+        <v>-8.0366</v>
       </c>
     </row>
     <row r="91">
@@ -5069,10 +5069,10 @@
         <v>0.34</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.9218</v>
+        <v>-0.6423</v>
       </c>
       <c r="J91" t="n">
-        <v>-23.9668</v>
+        <v>-16.6998</v>
       </c>
     </row>
     <row r="92">
@@ -5109,10 +5109,10 @@
         <v>1.14</v>
       </c>
       <c r="I92" t="n">
-        <v>0.348</v>
+        <v>0.2905</v>
       </c>
       <c r="J92" t="n">
-        <v>9.048</v>
+        <v>7.553</v>
       </c>
     </row>
     <row r="93">
@@ -5149,10 +5149,10 @@
         <v>1</v>
       </c>
       <c r="I93" t="n">
-        <v>0.0722</v>
+        <v>0.0271</v>
       </c>
       <c r="J93" t="n">
-        <v>1.8772</v>
+        <v>0.7046</v>
       </c>
     </row>
     <row r="94">
@@ -5189,10 +5189,10 @@
         <v>0.74</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.43</v>
+        <v>-0.2797</v>
       </c>
       <c r="J94" t="n">
-        <v>-11.18</v>
+        <v>-7.2722</v>
       </c>
     </row>
     <row r="95">
@@ -5229,10 +5229,10 @@
         <v>0.74</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.43</v>
+        <v>-0.2797</v>
       </c>
       <c r="J95" t="n">
-        <v>-11.18</v>
+        <v>-7.2722</v>
       </c>
     </row>
     <row r="96">
@@ -5269,10 +5269,10 @@
         <v>0.65</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.5551</v>
+        <v>-0.3654</v>
       </c>
       <c r="J96" t="n">
-        <v>-14.4326</v>
+        <v>-9.500400000000001</v>
       </c>
     </row>
     <row r="97">
@@ -5309,10 +5309,10 @@
         <v>1.5</v>
       </c>
       <c r="I97" t="n">
-        <v>0.6767</v>
+        <v>0.6066</v>
       </c>
       <c r="J97" t="n">
-        <v>17.5942</v>
+        <v>15.7716</v>
       </c>
     </row>
     <row r="98">
@@ -5349,10 +5349,10 @@
         <v>1.44</v>
       </c>
       <c r="I98" t="n">
-        <v>0.6054</v>
+        <v>0.5422</v>
       </c>
       <c r="J98" t="n">
-        <v>15.7404</v>
+        <v>14.0972</v>
       </c>
     </row>
     <row r="99">
@@ -5389,10 +5389,10 @@
         <v>1.27</v>
       </c>
       <c r="I99" t="n">
-        <v>0.3666</v>
+        <v>0.3561</v>
       </c>
       <c r="J99" t="n">
-        <v>9.531599999999999</v>
+        <v>9.258599999999999</v>
       </c>
     </row>
     <row r="100">
@@ -5429,10 +5429,10 @@
         <v>1.15</v>
       </c>
       <c r="I100" t="n">
-        <v>0.1908</v>
+        <v>0.2096</v>
       </c>
       <c r="J100" t="n">
-        <v>4.9608</v>
+        <v>5.4496</v>
       </c>
     </row>
     <row r="101">
@@ -5469,10 +5469,10 @@
         <v>1.1</v>
       </c>
       <c r="I101" t="n">
-        <v>0.1135</v>
+        <v>0.1413</v>
       </c>
       <c r="J101" t="n">
-        <v>2.951</v>
+        <v>3.6738</v>
       </c>
     </row>
     <row r="102">
@@ -5509,10 +5509,10 @@
         <v>1.62</v>
       </c>
       <c r="I102" t="n">
-        <v>1.381</v>
+        <v>1.2553</v>
       </c>
       <c r="J102" t="n">
-        <v>33.144</v>
+        <v>30.1272</v>
       </c>
     </row>
     <row r="103">
@@ -5549,10 +5549,10 @@
         <v>1.49</v>
       </c>
       <c r="I103" t="n">
-        <v>1.1237</v>
+        <v>1.0976</v>
       </c>
       <c r="J103" t="n">
-        <v>26.9688</v>
+        <v>26.3424</v>
       </c>
     </row>
     <row r="104">
@@ -5589,10 +5589,10 @@
         <v>1.33</v>
       </c>
       <c r="I104" t="n">
-        <v>0.7421</v>
+        <v>0.8298</v>
       </c>
       <c r="J104" t="n">
-        <v>17.8104</v>
+        <v>19.9152</v>
       </c>
     </row>
     <row r="105">
@@ -5629,10 +5629,10 @@
         <v>1.24</v>
       </c>
       <c r="I105" t="n">
-        <v>0.5271</v>
+        <v>0.6254</v>
       </c>
       <c r="J105" t="n">
-        <v>12.6504</v>
+        <v>15.0096</v>
       </c>
     </row>
     <row r="106">
@@ -5669,10 +5669,10 @@
         <v>1.12</v>
       </c>
       <c r="I106" t="n">
-        <v>0.2289</v>
+        <v>0.3212</v>
       </c>
       <c r="J106" t="n">
-        <v>5.4936</v>
+        <v>7.7088</v>
       </c>
     </row>
     <row r="107">
@@ -5709,10 +5709,10 @@
         <v>0.96</v>
       </c>
       <c r="I107" t="n">
-        <v>-0.0031</v>
+        <v>-0.0339</v>
       </c>
       <c r="J107" t="n">
-        <v>-0.07439999999999999</v>
+        <v>-0.8136</v>
       </c>
     </row>
     <row r="108">
@@ -5749,10 +5749,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I108" t="n">
-        <v>-0.2716</v>
+        <v>-0.2049</v>
       </c>
       <c r="J108" t="n">
-        <v>-6.5184</v>
+        <v>-4.9176</v>
       </c>
     </row>
     <row r="109">
@@ -5789,10 +5789,10 @@
         <v>0.77</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.3537</v>
+        <v>-0.2425</v>
       </c>
       <c r="J109" t="n">
-        <v>-8.488799999999999</v>
+        <v>-5.82</v>
       </c>
     </row>
     <row r="110">
@@ -5829,10 +5829,10 @@
         <v>0.75</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.3878</v>
+        <v>-0.2614</v>
       </c>
       <c r="J110" t="n">
-        <v>-9.3072</v>
+        <v>-6.2736</v>
       </c>
     </row>
     <row r="111">
@@ -5869,10 +5869,10 @@
         <v>0.65</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.5367</v>
+        <v>-0.3561</v>
       </c>
       <c r="J111" t="n">
-        <v>-12.8808</v>
+        <v>-8.5464</v>
       </c>
     </row>
     <row r="112">
@@ -5909,10 +5909,10 @@
         <v>1.89</v>
       </c>
       <c r="I112" t="n">
-        <v>1.0587</v>
+        <v>0.7145</v>
       </c>
       <c r="J112" t="n">
-        <v>24.3501</v>
+        <v>16.4335</v>
       </c>
     </row>
     <row r="113">
@@ -5949,10 +5949,10 @@
         <v>1.56</v>
       </c>
       <c r="I113" t="n">
-        <v>0.7119</v>
+        <v>0.521</v>
       </c>
       <c r="J113" t="n">
-        <v>16.3737</v>
+        <v>11.983</v>
       </c>
     </row>
     <row r="114">
@@ -5989,10 +5989,10 @@
         <v>1.25</v>
       </c>
       <c r="I114" t="n">
-        <v>0.3037</v>
+        <v>0.3193</v>
       </c>
       <c r="J114" t="n">
-        <v>6.9851</v>
+        <v>7.3439</v>
       </c>
     </row>
     <row r="115">
@@ -6029,10 +6029,10 @@
         <v>1.21</v>
       </c>
       <c r="I115" t="n">
-        <v>0.25</v>
+        <v>0.2722</v>
       </c>
       <c r="J115" t="n">
-        <v>5.75</v>
+        <v>6.2606</v>
       </c>
     </row>
     <row r="116">
@@ -6069,10 +6069,10 @@
         <v>1.17</v>
       </c>
       <c r="I116" t="n">
-        <v>0.1946</v>
+        <v>0.2219</v>
       </c>
       <c r="J116" t="n">
-        <v>4.4758</v>
+        <v>5.1037</v>
       </c>
     </row>
     <row r="117">
@@ -6109,10 +6109,10 @@
         <v>0.95</v>
       </c>
       <c r="I117" t="n">
-        <v>-0.0026</v>
+        <v>-0.036</v>
       </c>
       <c r="J117" t="n">
-        <v>-0.0598</v>
+        <v>-0.828</v>
       </c>
     </row>
     <row r="118">
@@ -6149,10 +6149,10 @@
         <v>0.77</v>
       </c>
       <c r="I118" t="n">
-        <v>-0.3124</v>
+        <v>-0.2379</v>
       </c>
       <c r="J118" t="n">
-        <v>-7.1852</v>
+        <v>-5.4717</v>
       </c>
     </row>
     <row r="119">
@@ -6189,10 +6189,10 @@
         <v>0.71</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.4284</v>
+        <v>-0.293</v>
       </c>
       <c r="J119" t="n">
-        <v>-9.853199999999999</v>
+        <v>-6.739</v>
       </c>
     </row>
     <row r="120">
@@ -6229,10 +6229,10 @@
         <v>0.7</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.4447</v>
+        <v>-0.3023</v>
       </c>
       <c r="J120" t="n">
-        <v>-10.2281</v>
+        <v>-6.9529</v>
       </c>
     </row>
     <row r="121">
@@ -6269,10 +6269,10 @@
         <v>0.58</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.6182</v>
+        <v>-0.4147</v>
       </c>
       <c r="J121" t="n">
-        <v>-14.2186</v>
+        <v>-9.5381</v>
       </c>
     </row>
     <row r="122">
@@ -6309,10 +6309,10 @@
         <v>1.1</v>
       </c>
       <c r="I122" t="n">
-        <v>0.2878</v>
+        <v>0.3003</v>
       </c>
       <c r="J122" t="n">
-        <v>6.9072</v>
+        <v>7.2072</v>
       </c>
     </row>
     <row r="123">
@@ -6349,10 +6349,10 @@
         <v>1.03</v>
       </c>
       <c r="I123" t="n">
-        <v>0.1583</v>
+        <v>0.1363</v>
       </c>
       <c r="J123" t="n">
-        <v>3.7992</v>
+        <v>3.2712</v>
       </c>
     </row>
     <row r="124">
@@ -6389,10 +6389,10 @@
         <v>0.83</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.2811</v>
+        <v>-0.1905</v>
       </c>
       <c r="J124" t="n">
-        <v>-6.7464</v>
+        <v>-4.572</v>
       </c>
     </row>
     <row r="125">
@@ -6429,10 +6429,10 @@
         <v>0.67</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.5256</v>
+        <v>-0.3452</v>
       </c>
       <c r="J125" t="n">
-        <v>-12.6144</v>
+        <v>-8.284800000000001</v>
       </c>
     </row>
     <row r="126">
@@ -6469,10 +6469,10 @@
         <v>0.59</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.6309</v>
+        <v>-0.4201</v>
       </c>
       <c r="J126" t="n">
-        <v>-15.1416</v>
+        <v>-10.0824</v>
       </c>
     </row>
     <row r="127">
@@ -6509,10 +6509,10 @@
         <v>1.6</v>
       </c>
       <c r="I127" t="n">
-        <v>1.3554</v>
+        <v>0.9629</v>
       </c>
       <c r="J127" t="n">
-        <v>32.5296</v>
+        <v>23.1096</v>
       </c>
     </row>
     <row r="128">
@@ -6549,10 +6549,10 @@
         <v>1.43</v>
       </c>
       <c r="I128" t="n">
-        <v>1.0111</v>
+        <v>0.7536</v>
       </c>
       <c r="J128" t="n">
-        <v>24.2664</v>
+        <v>18.0864</v>
       </c>
     </row>
     <row r="129">
@@ -6589,10 +6589,10 @@
         <v>1.26</v>
       </c>
       <c r="I129" t="n">
-        <v>0.5883</v>
+        <v>0.5366</v>
       </c>
       <c r="J129" t="n">
-        <v>14.1192</v>
+        <v>12.8784</v>
       </c>
     </row>
     <row r="130">
@@ -6629,10 +6629,10 @@
         <v>1.21</v>
       </c>
       <c r="I130" t="n">
-        <v>0.4666</v>
+        <v>0.4667</v>
       </c>
       <c r="J130" t="n">
-        <v>11.1984</v>
+        <v>11.2008</v>
       </c>
     </row>
     <row r="131">
@@ -6669,10 +6669,10 @@
         <v>1.16</v>
       </c>
       <c r="I131" t="n">
-        <v>0.342</v>
+        <v>0.3928</v>
       </c>
       <c r="J131" t="n">
-        <v>8.208</v>
+        <v>9.427199999999999</v>
       </c>
     </row>
     <row r="132">
@@ -6709,10 +6709,10 @@
         <v>1.15</v>
       </c>
       <c r="I132" t="n">
-        <v>0.4097</v>
+        <v>0.4109</v>
       </c>
       <c r="J132" t="n">
-        <v>9.013400000000001</v>
+        <v>9.0398</v>
       </c>
     </row>
     <row r="133">
@@ -6749,10 +6749,10 @@
         <v>0.93</v>
       </c>
       <c r="I133" t="n">
-        <v>-0.0415</v>
+        <v>-0.06270000000000001</v>
       </c>
       <c r="J133" t="n">
-        <v>-0.913</v>
+        <v>-1.3794</v>
       </c>
     </row>
     <row r="134">
@@ -6789,10 +6789,10 @@
         <v>0.67</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.4919</v>
+        <v>-0.3307</v>
       </c>
       <c r="J134" t="n">
-        <v>-10.8218</v>
+        <v>-7.2754</v>
       </c>
     </row>
     <row r="135">
@@ -6829,10 +6829,10 @@
         <v>0.55</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.6586</v>
+        <v>-0.443</v>
       </c>
       <c r="J135" t="n">
-        <v>-14.4892</v>
+        <v>-9.746</v>
       </c>
     </row>
     <row r="136">
@@ -6869,10 +6869,10 @@
         <v>0.42</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.8215</v>
+        <v>-0.5637</v>
       </c>
       <c r="J136" t="n">
-        <v>-18.073</v>
+        <v>-12.4014</v>
       </c>
     </row>
     <row r="137">
@@ -6909,10 +6909,10 @@
         <v>1.62</v>
       </c>
       <c r="I137" t="n">
-        <v>1.3622</v>
+        <v>0.9738</v>
       </c>
       <c r="J137" t="n">
-        <v>29.9684</v>
+        <v>21.4236</v>
       </c>
     </row>
     <row r="138">
@@ -6949,10 +6949,10 @@
         <v>1.59</v>
       </c>
       <c r="I138" t="n">
-        <v>1.3043</v>
+        <v>0.9381</v>
       </c>
       <c r="J138" t="n">
-        <v>28.6946</v>
+        <v>20.6382</v>
       </c>
     </row>
     <row r="139">
@@ -6989,10 +6989,10 @@
         <v>1.48</v>
       </c>
       <c r="I139" t="n">
-        <v>1.0808</v>
+        <v>0.8058999999999999</v>
       </c>
       <c r="J139" t="n">
-        <v>23.7776</v>
+        <v>17.7298</v>
       </c>
     </row>
     <row r="140">
@@ -7029,10 +7029,10 @@
         <v>1.24</v>
       </c>
       <c r="I140" t="n">
-        <v>0.5104</v>
+        <v>0.5004999999999999</v>
       </c>
       <c r="J140" t="n">
-        <v>11.2288</v>
+        <v>11.011</v>
       </c>
     </row>
     <row r="141">
@@ -7069,10 +7069,10 @@
         <v>1.08</v>
       </c>
       <c r="I141" t="n">
-        <v>0.1073</v>
+        <v>0.1982</v>
       </c>
       <c r="J141" t="n">
-        <v>2.3606</v>
+        <v>4.3604</v>
       </c>
     </row>
     <row r="142">
@@ -7109,10 +7109,10 @@
         <v>1.22</v>
       </c>
       <c r="I142" t="n">
-        <v>0.3833</v>
+        <v>0.4029</v>
       </c>
       <c r="J142" t="n">
-        <v>11.499</v>
+        <v>12.087</v>
       </c>
     </row>
     <row r="143">
@@ -7149,10 +7149,10 @@
         <v>1.21</v>
       </c>
       <c r="I143" t="n">
-        <v>0.3689</v>
+        <v>0.3925</v>
       </c>
       <c r="J143" t="n">
-        <v>11.067</v>
+        <v>11.775</v>
       </c>
     </row>
     <row r="144">
@@ -7189,10 +7189,10 @@
         <v>1.21</v>
       </c>
       <c r="I144" t="n">
-        <v>0.3689</v>
+        <v>0.3925</v>
       </c>
       <c r="J144" t="n">
-        <v>11.067</v>
+        <v>11.775</v>
       </c>
     </row>
     <row r="145">
@@ -7229,10 +7229,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.1815</v>
+        <v>-0.097</v>
       </c>
       <c r="J145" t="n">
-        <v>-5.445</v>
+        <v>-2.91</v>
       </c>
     </row>
     <row r="146">
@@ -7269,10 +7269,10 @@
         <v>0.84</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.3435</v>
+        <v>-0.2077</v>
       </c>
       <c r="J146" t="n">
-        <v>-10.305</v>
+        <v>-6.231</v>
       </c>
     </row>
     <row r="147">
@@ -7309,10 +7309,10 @@
         <v>1.22</v>
       </c>
       <c r="I147" t="n">
-        <v>0.7206</v>
+        <v>0.5353</v>
       </c>
       <c r="J147" t="n">
-        <v>21.618</v>
+        <v>16.059</v>
       </c>
     </row>
     <row r="148">
@@ -7349,10 +7349,10 @@
         <v>1.1</v>
       </c>
       <c r="I148" t="n">
-        <v>0.4006</v>
+        <v>0.3432</v>
       </c>
       <c r="J148" t="n">
-        <v>12.018</v>
+        <v>10.296</v>
       </c>
     </row>
     <row r="149">
@@ -7389,10 +7389,10 @@
         <v>0.93</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.2995</v>
+        <v>-0.2583</v>
       </c>
       <c r="J149" t="n">
-        <v>-8.984999999999999</v>
+        <v>-7.749</v>
       </c>
     </row>
     <row r="150">
@@ -7429,10 +7429,10 @@
         <v>0.91</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.3628</v>
+        <v>-0.3181</v>
       </c>
       <c r="J150" t="n">
-        <v>-10.884</v>
+        <v>-9.542999999999999</v>
       </c>
     </row>
     <row r="151">
@@ -7469,10 +7469,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.6397</v>
+        <v>-0.5931999999999999</v>
       </c>
       <c r="J151" t="n">
-        <v>-19.191</v>
+        <v>-17.796</v>
       </c>
     </row>
     <row r="152">
@@ -7509,10 +7509,10 @@
         <v>1.1</v>
       </c>
       <c r="I152" t="n">
-        <v>0.2333</v>
+        <v>0.25</v>
       </c>
       <c r="J152" t="n">
-        <v>5.8325</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="153">
@@ -7549,10 +7549,10 @@
         <v>1.05</v>
       </c>
       <c r="I153" t="n">
-        <v>0.1415</v>
+        <v>0.1422</v>
       </c>
       <c r="J153" t="n">
-        <v>3.5375</v>
+        <v>3.555</v>
       </c>
     </row>
     <row r="154">
@@ -7589,10 +7589,10 @@
         <v>1.02</v>
       </c>
       <c r="I154" t="n">
-        <v>0.07539999999999999</v>
+        <v>0.0684</v>
       </c>
       <c r="J154" t="n">
-        <v>1.885</v>
+        <v>1.71</v>
       </c>
     </row>
     <row r="155">
@@ -7629,10 +7629,10 @@
         <v>0.97</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.0849</v>
+        <v>-0.0488</v>
       </c>
       <c r="J155" t="n">
-        <v>-2.1225</v>
+        <v>-1.22</v>
       </c>
     </row>
     <row r="156">
@@ -7669,10 +7669,10 @@
         <v>0.79</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.3947</v>
+        <v>-0.2474</v>
       </c>
       <c r="J156" t="n">
-        <v>-9.8675</v>
+        <v>-6.185</v>
       </c>
     </row>
     <row r="157">
@@ -7709,10 +7709,10 @@
         <v>1.42</v>
       </c>
       <c r="I157" t="n">
-        <v>1.0765</v>
+        <v>0.7724</v>
       </c>
       <c r="J157" t="n">
-        <v>26.9125</v>
+        <v>19.31</v>
       </c>
     </row>
     <row r="158">
@@ -7749,10 +7749,10 @@
         <v>1.38</v>
       </c>
       <c r="I158" t="n">
-        <v>0.9913</v>
+        <v>0.7193000000000001</v>
       </c>
       <c r="J158" t="n">
-        <v>24.7825</v>
+        <v>17.9825</v>
       </c>
     </row>
     <row r="159">
@@ -7789,10 +7789,10 @@
         <v>1.13</v>
       </c>
       <c r="I159" t="n">
-        <v>0.3445</v>
+        <v>0.3684</v>
       </c>
       <c r="J159" t="n">
-        <v>8.612500000000001</v>
+        <v>9.210000000000001</v>
       </c>
     </row>
     <row r="160">
@@ -7829,10 +7829,10 @@
         <v>0.96</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.2829</v>
+        <v>-0.2078</v>
       </c>
       <c r="J160" t="n">
-        <v>-7.0725</v>
+        <v>-5.195</v>
       </c>
     </row>
     <row r="161">
@@ -7869,10 +7869,10 @@
         <v>0.93</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.3784</v>
+        <v>-0.3047</v>
       </c>
       <c r="J161" t="n">
-        <v>-9.460000000000001</v>
+        <v>-7.6175</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/5274/event_5274_evp_summary.xlsx
+++ b/database/event/5274/event_5274_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.3072</v>
+        <v>4.1402</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6032</v>
+        <v>0.5798</v>
       </c>
       <c r="D2" t="n">
-        <v>1.3065</v>
+        <v>1.2605</v>
       </c>
       <c r="E2" t="n">
-        <v>4.3072</v>
+        <v>4.1402</v>
       </c>
       <c r="F2" t="n">
-        <v>1.3413</v>
+        <v>1.1652</v>
       </c>
       <c r="G2" t="n">
-        <v>2.9659</v>
+        <v>2.975</v>
       </c>
       <c r="H2" t="n">
-        <v>1.3413</v>
+        <v>1.1652</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6974</v>
+        <v>0.6292</v>
       </c>
       <c r="J2" t="n">
-        <v>2.9659</v>
+        <v>2.975</v>
       </c>
       <c r="K2" t="n">
         <v>171</v>
@@ -529,7 +529,7 @@
         <v>133</v>
       </c>
       <c r="M2" t="n">
-        <v>3.6633</v>
+        <v>3.6042</v>
       </c>
       <c r="N2" t="n">
         <v>304</v>
@@ -538,93 +538,93 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>HEN1</t>
+          <t>fer</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.6499</v>
+        <v>3.6705</v>
       </c>
       <c r="C3" t="n">
-        <v>0.5112</v>
+        <v>0.5141</v>
       </c>
       <c r="D3" t="n">
-        <v>1.0097</v>
+        <v>1.0467</v>
       </c>
       <c r="E3" t="n">
-        <v>3.6499</v>
+        <v>3.6705</v>
       </c>
       <c r="F3" t="n">
-        <v>3.0074</v>
+        <v>2.6923</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6425</v>
+        <v>0.9782</v>
       </c>
       <c r="H3" t="n">
-        <v>5.1099</v>
+        <v>3.9888</v>
       </c>
       <c r="I3" t="n">
-        <v>2.6569</v>
+        <v>2.1539</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6425</v>
+        <v>0.9782</v>
       </c>
       <c r="K3" t="n">
-        <v>164</v>
+        <v>83</v>
       </c>
       <c r="L3" t="n">
-        <v>55</v>
+        <v>119</v>
       </c>
       <c r="M3" t="n">
-        <v>3.2994</v>
+        <v>3.1321</v>
       </c>
       <c r="N3" t="n">
-        <v>219</v>
+        <v>202</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>fer</t>
+          <t>HEN1</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.6451</v>
+        <v>3.649</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5105</v>
+        <v>0.511</v>
       </c>
       <c r="D4" t="n">
-        <v>1.0076</v>
+        <v>1.0369</v>
       </c>
       <c r="E4" t="n">
-        <v>3.6451</v>
+        <v>3.649</v>
       </c>
       <c r="F4" t="n">
-        <v>2.7735</v>
+        <v>2.9627</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8716</v>
+        <v>0.6863</v>
       </c>
       <c r="H4" t="n">
-        <v>4.2858</v>
+        <v>4.881</v>
       </c>
       <c r="I4" t="n">
-        <v>2.2284</v>
+        <v>2.6357</v>
       </c>
       <c r="J4" t="n">
-        <v>0.8716</v>
+        <v>0.6863</v>
       </c>
       <c r="K4" t="n">
-        <v>83</v>
+        <v>164</v>
       </c>
       <c r="L4" t="n">
-        <v>119</v>
+        <v>55</v>
       </c>
       <c r="M4" t="n">
-        <v>3.1</v>
+        <v>3.322</v>
       </c>
       <c r="N4" t="n">
-        <v>202</v>
+        <v>219</v>
       </c>
     </row>
     <row r="5">
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.0976</v>
+        <v>3.2568</v>
       </c>
       <c r="C5" t="n">
-        <v>0.4338</v>
+        <v>0.4561</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7604</v>
+        <v>0.8584000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>3.0976</v>
+        <v>3.2568</v>
       </c>
       <c r="F5" t="n">
-        <v>2.2116</v>
+        <v>2.1397</v>
       </c>
       <c r="G5" t="n">
-        <v>0.886</v>
+        <v>1.1171</v>
       </c>
       <c r="H5" t="n">
-        <v>2.306</v>
+        <v>2.1656</v>
       </c>
       <c r="I5" t="n">
-        <v>1.199</v>
+        <v>1.1694</v>
       </c>
       <c r="J5" t="n">
-        <v>0.886</v>
+        <v>1.1171</v>
       </c>
       <c r="K5" t="n">
         <v>171</v>
@@ -667,7 +667,7 @@
         <v>133</v>
       </c>
       <c r="M5" t="n">
-        <v>2.085</v>
+        <v>2.2865</v>
       </c>
       <c r="N5" t="n">
         <v>304</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.0897</v>
+        <v>3.069</v>
       </c>
       <c r="C6" t="n">
-        <v>0.4327</v>
+        <v>0.4298</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7568</v>
+        <v>0.7729</v>
       </c>
       <c r="E6" t="n">
-        <v>3.0897</v>
+        <v>3.069</v>
       </c>
       <c r="F6" t="n">
-        <v>2.7356</v>
+        <v>2.681</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3541</v>
+        <v>0.388</v>
       </c>
       <c r="H6" t="n">
-        <v>4.1523</v>
+        <v>3.9515</v>
       </c>
       <c r="I6" t="n">
-        <v>2.159</v>
+        <v>2.1338</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3541</v>
+        <v>0.388</v>
       </c>
       <c r="K6" t="n">
         <v>164</v>
@@ -713,7 +713,7 @@
         <v>55</v>
       </c>
       <c r="M6" t="n">
-        <v>2.5131</v>
+        <v>2.5218</v>
       </c>
       <c r="N6" t="n">
         <v>219</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.8882</v>
+        <v>2.7982</v>
       </c>
       <c r="C7" t="n">
-        <v>0.4045</v>
+        <v>0.3919</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6659</v>
+        <v>0.6496</v>
       </c>
       <c r="E7" t="n">
-        <v>2.8882</v>
+        <v>2.7982</v>
       </c>
       <c r="F7" t="n">
-        <v>2.843</v>
+        <v>2.7541</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0452</v>
+        <v>0.0441</v>
       </c>
       <c r="H7" t="n">
-        <v>4.5308</v>
+        <v>4.1927</v>
       </c>
       <c r="I7" t="n">
-        <v>2.3558</v>
+        <v>2.264</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0452</v>
+        <v>0.0441</v>
       </c>
       <c r="K7" t="n">
         <v>164</v>
@@ -759,7 +759,7 @@
         <v>55</v>
       </c>
       <c r="M7" t="n">
-        <v>2.401</v>
+        <v>2.3081</v>
       </c>
       <c r="N7" t="n">
         <v>219</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.5113</v>
+        <v>2.6121</v>
       </c>
       <c r="C8" t="n">
-        <v>0.3517</v>
+        <v>0.3658</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4957</v>
+        <v>0.5649</v>
       </c>
       <c r="E8" t="n">
-        <v>2.5113</v>
+        <v>2.6121</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8539</v>
+        <v>0.8678</v>
       </c>
       <c r="G8" t="n">
-        <v>1.6574</v>
+        <v>1.7443</v>
       </c>
       <c r="H8" t="n">
-        <v>0.8539</v>
+        <v>0.8678</v>
       </c>
       <c r="I8" t="n">
-        <v>0.444</v>
+        <v>0.4686</v>
       </c>
       <c r="J8" t="n">
-        <v>1.6574</v>
+        <v>1.7443</v>
       </c>
       <c r="K8" t="n">
         <v>83</v>
@@ -805,7 +805,7 @@
         <v>119</v>
       </c>
       <c r="M8" t="n">
-        <v>2.1014</v>
+        <v>2.2129</v>
       </c>
       <c r="N8" t="n">
         <v>202</v>
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.4118</v>
+        <v>2.3047</v>
       </c>
       <c r="C9" t="n">
-        <v>0.3378</v>
+        <v>0.3228</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4508</v>
+        <v>0.4249</v>
       </c>
       <c r="E9" t="n">
-        <v>2.4118</v>
+        <v>2.3047</v>
       </c>
       <c r="F9" t="n">
-        <v>2.6426</v>
+        <v>2.5494</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.2308</v>
+        <v>-0.2447</v>
       </c>
       <c r="H9" t="n">
-        <v>3.8246</v>
+        <v>3.5171</v>
       </c>
       <c r="I9" t="n">
-        <v>1.9886</v>
+        <v>1.8992</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.2308</v>
+        <v>-0.2447</v>
       </c>
       <c r="K9" t="n">
         <v>83</v>
@@ -851,7 +851,7 @@
         <v>119</v>
       </c>
       <c r="M9" t="n">
-        <v>1.7578</v>
+        <v>1.6545</v>
       </c>
       <c r="N9" t="n">
         <v>202</v>
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.3364</v>
+        <v>2.2642</v>
       </c>
       <c r="C10" t="n">
-        <v>0.3272</v>
+        <v>0.3171</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4168</v>
+        <v>0.4065</v>
       </c>
       <c r="E10" t="n">
-        <v>2.3364</v>
+        <v>2.2642</v>
       </c>
       <c r="F10" t="n">
-        <v>2.5019</v>
+        <v>2.415</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.1655</v>
+        <v>-0.1508</v>
       </c>
       <c r="H10" t="n">
-        <v>3.3288</v>
+        <v>3.0738</v>
       </c>
       <c r="I10" t="n">
-        <v>1.7308</v>
+        <v>1.6598</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.1655</v>
+        <v>-0.1508</v>
       </c>
       <c r="K10" t="n">
         <v>83</v>
@@ -897,7 +897,7 @@
         <v>119</v>
       </c>
       <c r="M10" t="n">
-        <v>1.5653</v>
+        <v>1.509</v>
       </c>
       <c r="N10" t="n">
         <v>202</v>
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.2695</v>
+        <v>2.21</v>
       </c>
       <c r="C11" t="n">
-        <v>0.3178</v>
+        <v>0.3095</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3866</v>
+        <v>0.3818</v>
       </c>
       <c r="E11" t="n">
-        <v>2.2695</v>
+        <v>2.21</v>
       </c>
       <c r="F11" t="n">
-        <v>2.4088</v>
+        <v>2.3541</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.1393</v>
+        <v>-0.1441</v>
       </c>
       <c r="H11" t="n">
-        <v>3.0006</v>
+        <v>2.8728</v>
       </c>
       <c r="I11" t="n">
-        <v>1.5602</v>
+        <v>1.5513</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.1393</v>
+        <v>-0.1441</v>
       </c>
       <c r="K11" t="n">
         <v>164</v>
@@ -943,7 +943,7 @@
         <v>55</v>
       </c>
       <c r="M11" t="n">
-        <v>1.4209</v>
+        <v>1.4072</v>
       </c>
       <c r="N11" t="n">
         <v>219</v>
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.1524</v>
+        <v>2.1184</v>
       </c>
       <c r="C12" t="n">
-        <v>0.3014</v>
+        <v>0.2967</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3337</v>
+        <v>0.3401</v>
       </c>
       <c r="E12" t="n">
-        <v>2.1524</v>
+        <v>2.1184</v>
       </c>
       <c r="F12" t="n">
-        <v>0.4775</v>
+        <v>0.2993</v>
       </c>
       <c r="G12" t="n">
-        <v>1.6749</v>
+        <v>1.8191</v>
       </c>
       <c r="H12" t="n">
-        <v>0.4775</v>
+        <v>0.2993</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2483</v>
+        <v>0.1616</v>
       </c>
       <c r="J12" t="n">
-        <v>1.6749</v>
+        <v>1.8191</v>
       </c>
       <c r="K12" t="n">
         <v>171</v>
@@ -989,7 +989,7 @@
         <v>133</v>
       </c>
       <c r="M12" t="n">
-        <v>1.9232</v>
+        <v>1.9807</v>
       </c>
       <c r="N12" t="n">
         <v>304</v>
@@ -998,185 +998,185 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>NAF</t>
+          <t>stanislaw</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.5323</v>
+        <v>1.4726</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2146</v>
+        <v>0.2062</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0537</v>
+        <v>0.0462</v>
       </c>
       <c r="E13" t="n">
-        <v>1.5323</v>
+        <v>1.4726</v>
       </c>
       <c r="F13" t="n">
-        <v>1.3557</v>
+        <v>0.4441</v>
       </c>
       <c r="G13" t="n">
-        <v>0.1766</v>
+        <v>1.0285</v>
       </c>
       <c r="H13" t="n">
-        <v>1.3557</v>
+        <v>0.4441</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7049</v>
+        <v>0.2398</v>
       </c>
       <c r="J13" t="n">
-        <v>0.1766</v>
+        <v>1.0285</v>
       </c>
       <c r="K13" t="n">
-        <v>76</v>
+        <v>171</v>
       </c>
       <c r="L13" t="n">
-        <v>69</v>
+        <v>133</v>
       </c>
       <c r="M13" t="n">
-        <v>0.8815</v>
+        <v>1.2683</v>
       </c>
       <c r="N13" t="n">
-        <v>145</v>
+        <v>304</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>stanislaw</t>
+          <t>NAF</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.3922</v>
+        <v>1.4445</v>
       </c>
       <c r="C14" t="n">
-        <v>0.195</v>
+        <v>0.2023</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.0095</v>
+        <v>0.0334</v>
       </c>
       <c r="E14" t="n">
-        <v>1.3922</v>
+        <v>1.4445</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5431</v>
+        <v>1.2663</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8491</v>
+        <v>0.1782</v>
       </c>
       <c r="H14" t="n">
-        <v>0.5431</v>
+        <v>1.2663</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2824</v>
+        <v>0.6838</v>
       </c>
       <c r="J14" t="n">
-        <v>0.8491</v>
+        <v>0.1782</v>
       </c>
       <c r="K14" t="n">
-        <v>171</v>
+        <v>76</v>
       </c>
       <c r="L14" t="n">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="M14" t="n">
-        <v>1.1315</v>
+        <v>0.862</v>
       </c>
       <c r="N14" t="n">
-        <v>304</v>
+        <v>145</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>VINI</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.6394</v>
+        <v>0.5337</v>
       </c>
       <c r="C15" t="n">
-        <v>0.0895</v>
+        <v>0.0747</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.3494</v>
+        <v>-0.3813</v>
       </c>
       <c r="E15" t="n">
-        <v>0.6394</v>
+        <v>0.5337</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4943</v>
+        <v>-0.2761</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1451</v>
+        <v>0.8098</v>
       </c>
       <c r="H15" t="n">
-        <v>0.4943</v>
+        <v>-0.2761</v>
       </c>
       <c r="I15" t="n">
-        <v>0.257</v>
+        <v>-0.1491</v>
       </c>
       <c r="J15" t="n">
-        <v>0.1451</v>
+        <v>0.8098</v>
       </c>
       <c r="K15" t="n">
-        <v>164</v>
+        <v>76</v>
       </c>
       <c r="L15" t="n">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="M15" t="n">
-        <v>0.4021</v>
+        <v>0.6607</v>
       </c>
       <c r="N15" t="n">
-        <v>219</v>
+        <v>145</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>VINI</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.5152</v>
+        <v>0.5072</v>
       </c>
       <c r="C16" t="n">
-        <v>0.0722</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.4054</v>
+        <v>-0.3933</v>
       </c>
       <c r="E16" t="n">
-        <v>0.5152</v>
+        <v>0.5072</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.2539</v>
+        <v>0.337</v>
       </c>
       <c r="G16" t="n">
-        <v>0.7691</v>
+        <v>0.1702</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.2539</v>
+        <v>0.337</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.132</v>
+        <v>0.182</v>
       </c>
       <c r="J16" t="n">
-        <v>0.7691</v>
+        <v>0.1702</v>
       </c>
       <c r="K16" t="n">
-        <v>76</v>
+        <v>164</v>
       </c>
       <c r="L16" t="n">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="M16" t="n">
-        <v>0.6371</v>
+        <v>0.3522</v>
       </c>
       <c r="N16" t="n">
-        <v>145</v>
+        <v>219</v>
       </c>
     </row>
     <row r="17">
@@ -1186,31 +1186,31 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.4069</v>
+        <v>0.4319</v>
       </c>
       <c r="C17" t="n">
-        <v>0.057</v>
+        <v>0.0605</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.4543</v>
+        <v>-0.4276</v>
       </c>
       <c r="E17" t="n">
-        <v>0.4069</v>
+        <v>0.4319</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.0544</v>
+        <v>-0.1015</v>
       </c>
       <c r="G17" t="n">
-        <v>0.4613</v>
+        <v>0.5334</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.0544</v>
+        <v>-0.1015</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.0283</v>
+        <v>-0.0548</v>
       </c>
       <c r="J17" t="n">
-        <v>0.4613</v>
+        <v>0.5334</v>
       </c>
       <c r="K17" t="n">
         <v>76</v>
@@ -1219,7 +1219,7 @@
         <v>69</v>
       </c>
       <c r="M17" t="n">
-        <v>0.433</v>
+        <v>0.4786</v>
       </c>
       <c r="N17" t="n">
         <v>145</v>
@@ -1232,31 +1232,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.1993</v>
+        <v>-0.2358</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.0279</v>
+        <v>-0.033</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.728</v>
+        <v>-0.7315</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.1993</v>
+        <v>-0.2358</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2044</v>
+        <v>0.178</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.4037</v>
+        <v>-0.4138</v>
       </c>
       <c r="H18" t="n">
-        <v>0.2044</v>
+        <v>0.178</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1063</v>
+        <v>0.0961</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.4037</v>
+        <v>-0.4138</v>
       </c>
       <c r="K18" t="n">
         <v>76</v>
@@ -1265,7 +1265,7 @@
         <v>69</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.2974</v>
+        <v>-0.3177</v>
       </c>
       <c r="N18" t="n">
         <v>145</v>
@@ -1278,31 +1278,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.3913</v>
+        <v>-0.3277</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.0548</v>
+        <v>-0.0459</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.8147</v>
+        <v>-0.7734</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.3913</v>
+        <v>-0.3277</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.6258</v>
+        <v>-0.5454</v>
       </c>
       <c r="G19" t="n">
-        <v>0.2345</v>
+        <v>0.2177</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.6258</v>
+        <v>-0.5454</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.3254</v>
+        <v>-0.2945</v>
       </c>
       <c r="J19" t="n">
-        <v>0.2345</v>
+        <v>0.2177</v>
       </c>
       <c r="K19" t="n">
         <v>83</v>
@@ -1311,7 +1311,7 @@
         <v>119</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.09090000000000004</v>
+        <v>-0.07679999999999998</v>
       </c>
       <c r="N19" t="n">
         <v>202</v>
@@ -1324,31 +1324,31 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-1.3688</v>
+        <v>-1.2719</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.1917</v>
+        <v>-0.1781</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.256</v>
+        <v>-1.2032</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.3688</v>
+        <v>-1.2719</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.9481</v>
+        <v>-1.9098</v>
       </c>
       <c r="G20" t="n">
-        <v>0.5793</v>
+        <v>0.6379</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.9481</v>
+        <v>-1.9098</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.0129</v>
+        <v>-1.0313</v>
       </c>
       <c r="J20" t="n">
-        <v>0.5793</v>
+        <v>0.6379</v>
       </c>
       <c r="K20" t="n">
         <v>171</v>
@@ -1357,7 +1357,7 @@
         <v>133</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.4335999999999999</v>
+        <v>-0.3934000000000001</v>
       </c>
       <c r="N20" t="n">
         <v>304</v>
@@ -1370,31 +1370,31 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-1.8927</v>
+        <v>-1.7709</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.2651</v>
+        <v>-0.248</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.4925</v>
+        <v>-1.4304</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.8927</v>
+        <v>-1.7709</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.4299</v>
+        <v>-1.3709</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.4628</v>
+        <v>-0.4</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.4299</v>
+        <v>-1.3709</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.7435</v>
+        <v>-0.7403</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.4628</v>
+        <v>-0.4</v>
       </c>
       <c r="K21" t="n">
         <v>76</v>
@@ -1403,7 +1403,7 @@
         <v>69</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.2063</v>
+        <v>-1.1403</v>
       </c>
       <c r="N21" t="n">
         <v>145</v>
@@ -1509,10 +1509,10 @@
         <v>1.43</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8361</v>
+        <v>0.7947</v>
       </c>
       <c r="J2" t="n">
-        <v>25.083</v>
+        <v>23.841</v>
       </c>
     </row>
     <row r="3">
@@ -1549,10 +1549,10 @@
         <v>1.11</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2656</v>
+        <v>0.2711</v>
       </c>
       <c r="J3" t="n">
-        <v>7.968</v>
+        <v>8.132999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -1589,10 +1589,10 @@
         <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.0002</v>
+        <v>-0.0001</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.006</v>
+        <v>-0.003</v>
       </c>
     </row>
     <row r="5">
@@ -1629,10 +1629,10 @@
         <v>0.76</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.279</v>
+        <v>-0.2918</v>
       </c>
       <c r="J5" t="n">
-        <v>-8.369999999999999</v>
+        <v>-8.754</v>
       </c>
     </row>
     <row r="6">
@@ -1669,10 +1669,10 @@
         <v>0.72</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3177</v>
+        <v>-0.3295</v>
       </c>
       <c r="J6" t="n">
-        <v>-9.531000000000001</v>
+        <v>-9.885</v>
       </c>
     </row>
     <row r="7">
@@ -1709,10 +1709,10 @@
         <v>1.47</v>
       </c>
       <c r="I7" t="n">
-        <v>1.1291</v>
+        <v>1.1148</v>
       </c>
       <c r="J7" t="n">
-        <v>33.873</v>
+        <v>33.444</v>
       </c>
     </row>
     <row r="8">
@@ -1749,10 +1749,10 @@
         <v>1.31</v>
       </c>
       <c r="I8" t="n">
-        <v>0.8501</v>
+        <v>0.7965</v>
       </c>
       <c r="J8" t="n">
-        <v>25.503</v>
+        <v>23.895</v>
       </c>
     </row>
     <row r="9">
@@ -1789,10 +1789,10 @@
         <v>1.11</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3495</v>
+        <v>0.349</v>
       </c>
       <c r="J9" t="n">
-        <v>10.485</v>
+        <v>10.47</v>
       </c>
     </row>
     <row r="10">
@@ -1829,10 +1829,10 @@
         <v>0.84</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5448</v>
+        <v>-0.5137</v>
       </c>
       <c r="J10" t="n">
-        <v>-16.344</v>
+        <v>-15.411</v>
       </c>
     </row>
     <row r="11">
@@ -1869,10 +1869,10 @@
         <v>0.78</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.7018</v>
+        <v>-0.6535</v>
       </c>
       <c r="J11" t="n">
-        <v>-21.054</v>
+        <v>-19.605</v>
       </c>
     </row>
     <row r="12">
@@ -1909,10 +1909,10 @@
         <v>1.63</v>
       </c>
       <c r="I12" t="n">
-        <v>1.0765</v>
+        <v>1.0586</v>
       </c>
       <c r="J12" t="n">
-        <v>36.601</v>
+        <v>35.9924</v>
       </c>
     </row>
     <row r="13">
@@ -1949,10 +1949,10 @@
         <v>1.15</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3293</v>
+        <v>0.3348</v>
       </c>
       <c r="J13" t="n">
-        <v>11.1962</v>
+        <v>11.3832</v>
       </c>
     </row>
     <row r="14">
@@ -1989,10 +1989,10 @@
         <v>0.92</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1184</v>
+        <v>-0.1288</v>
       </c>
       <c r="J14" t="n">
-        <v>-4.0256</v>
+        <v>-4.3792</v>
       </c>
     </row>
     <row r="15">
@@ -2029,10 +2029,10 @@
         <v>0.83</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2156</v>
+        <v>-0.2277</v>
       </c>
       <c r="J15" t="n">
-        <v>-7.3304</v>
+        <v>-7.7418</v>
       </c>
     </row>
     <row r="16">
@@ -2069,10 +2069,10 @@
         <v>0.78</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.2659</v>
+        <v>-0.2775</v>
       </c>
       <c r="J16" t="n">
-        <v>-9.0406</v>
+        <v>-9.435</v>
       </c>
     </row>
     <row r="17">
@@ -2109,10 +2109,10 @@
         <v>1.32</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8977000000000001</v>
+        <v>0.8341</v>
       </c>
       <c r="J17" t="n">
-        <v>30.5218</v>
+        <v>28.3594</v>
       </c>
     </row>
     <row r="18">
@@ -2149,10 +2149,10 @@
         <v>1.1</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3339</v>
+        <v>0.3316</v>
       </c>
       <c r="J18" t="n">
-        <v>11.3526</v>
+        <v>11.2744</v>
       </c>
     </row>
     <row r="19">
@@ -2189,10 +2189,10 @@
         <v>1.03</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1213</v>
+        <v>0.1296</v>
       </c>
       <c r="J19" t="n">
-        <v>4.1242</v>
+        <v>4.4064</v>
       </c>
     </row>
     <row r="20">
@@ -2229,10 +2229,10 @@
         <v>0.97</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1421</v>
+        <v>-0.1437</v>
       </c>
       <c r="J20" t="n">
-        <v>-4.8314</v>
+        <v>-4.8858</v>
       </c>
     </row>
     <row r="21">
@@ -2269,10 +2269,10 @@
         <v>0.82</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.5829</v>
+        <v>-0.5507</v>
       </c>
       <c r="J21" t="n">
-        <v>-19.8186</v>
+        <v>-18.7238</v>
       </c>
     </row>
     <row r="22">
@@ -2309,10 +2309,10 @@
         <v>1.42</v>
       </c>
       <c r="I22" t="n">
-        <v>0.5551</v>
+        <v>0.5576</v>
       </c>
       <c r="J22" t="n">
-        <v>16.653</v>
+        <v>16.728</v>
       </c>
     </row>
     <row r="23">
@@ -2349,10 +2349,10 @@
         <v>1.29</v>
       </c>
       <c r="I23" t="n">
-        <v>0.4028</v>
+        <v>0.4136</v>
       </c>
       <c r="J23" t="n">
-        <v>12.084</v>
+        <v>12.408</v>
       </c>
     </row>
     <row r="24">
@@ -2389,10 +2389,10 @@
         <v>1.02</v>
       </c>
       <c r="I24" t="n">
-        <v>0.0358</v>
+        <v>0.0462</v>
       </c>
       <c r="J24" t="n">
-        <v>1.074</v>
+        <v>1.386</v>
       </c>
     </row>
     <row r="25">
@@ -2429,10 +2429,10 @@
         <v>0.9</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.1458</v>
+        <v>-0.1559</v>
       </c>
       <c r="J25" t="n">
-        <v>-4.374</v>
+        <v>-4.677</v>
       </c>
     </row>
     <row r="26">
@@ -2469,10 +2469,10 @@
         <v>0.9</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.1458</v>
+        <v>-0.1559</v>
       </c>
       <c r="J26" t="n">
-        <v>-4.374</v>
+        <v>-4.677</v>
       </c>
     </row>
     <row r="27">
@@ -2509,10 +2509,10 @@
         <v>1.48</v>
       </c>
       <c r="I27" t="n">
-        <v>0.6992</v>
+        <v>0.6771</v>
       </c>
       <c r="J27" t="n">
-        <v>20.976</v>
+        <v>20.313</v>
       </c>
     </row>
     <row r="28">
@@ -2549,10 +2549,10 @@
         <v>1.02</v>
       </c>
       <c r="I28" t="n">
-        <v>0.0491</v>
+        <v>0.0564</v>
       </c>
       <c r="J28" t="n">
-        <v>1.473</v>
+        <v>1.692</v>
       </c>
     </row>
     <row r="29">
@@ -2589,10 +2589,10 @@
         <v>0.89</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.1468</v>
+        <v>-0.1594</v>
       </c>
       <c r="J29" t="n">
-        <v>-4.404</v>
+        <v>-4.782</v>
       </c>
     </row>
     <row r="30">
@@ -2629,10 +2629,10 @@
         <v>0.87</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.1685</v>
+        <v>-0.1814</v>
       </c>
       <c r="J30" t="n">
-        <v>-5.055</v>
+        <v>-5.442</v>
       </c>
     </row>
     <row r="31">
@@ -2669,10 +2669,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.2306</v>
+        <v>-0.2437</v>
       </c>
       <c r="J31" t="n">
-        <v>-6.918</v>
+        <v>-7.311</v>
       </c>
     </row>
     <row r="32">
@@ -2709,10 +2709,10 @@
         <v>1.19</v>
       </c>
       <c r="I32" t="n">
-        <v>0.4235</v>
+        <v>0.4189</v>
       </c>
       <c r="J32" t="n">
-        <v>12.705</v>
+        <v>12.567</v>
       </c>
     </row>
     <row r="33">
@@ -2749,10 +2749,10 @@
         <v>1.09</v>
       </c>
       <c r="I33" t="n">
-        <v>0.2283</v>
+        <v>0.2345</v>
       </c>
       <c r="J33" t="n">
-        <v>6.849</v>
+        <v>7.035</v>
       </c>
     </row>
     <row r="34">
@@ -2789,10 +2789,10 @@
         <v>1.04</v>
       </c>
       <c r="I34" t="n">
-        <v>0.118</v>
+        <v>0.126</v>
       </c>
       <c r="J34" t="n">
-        <v>3.54</v>
+        <v>3.78</v>
       </c>
     </row>
     <row r="35">
@@ -2829,10 +2829,10 @@
         <v>0.89</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.1441</v>
+        <v>-0.1574</v>
       </c>
       <c r="J35" t="n">
-        <v>-4.323</v>
+        <v>-4.722</v>
       </c>
     </row>
     <row r="36">
@@ -2869,10 +2869,10 @@
         <v>0.74</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.2968</v>
+        <v>-0.3095</v>
       </c>
       <c r="J36" t="n">
-        <v>-8.904</v>
+        <v>-9.285</v>
       </c>
     </row>
     <row r="37">
@@ -2909,10 +2909,10 @@
         <v>1.19</v>
       </c>
       <c r="I37" t="n">
-        <v>0.5785</v>
+        <v>0.5527</v>
       </c>
       <c r="J37" t="n">
-        <v>17.355</v>
+        <v>16.581</v>
       </c>
     </row>
     <row r="38">
@@ -2949,10 +2949,10 @@
         <v>1.12</v>
       </c>
       <c r="I38" t="n">
-        <v>0.392</v>
+        <v>0.3845</v>
       </c>
       <c r="J38" t="n">
-        <v>11.76</v>
+        <v>11.535</v>
       </c>
     </row>
     <row r="39">
@@ -2989,10 +2989,10 @@
         <v>0.99</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.0623</v>
+        <v>-0.0648</v>
       </c>
       <c r="J39" t="n">
-        <v>-1.869</v>
+        <v>-1.944</v>
       </c>
     </row>
     <row r="40">
@@ -3029,10 +3029,10 @@
         <v>0.96</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.1747</v>
+        <v>-0.1759</v>
       </c>
       <c r="J40" t="n">
-        <v>-5.241</v>
+        <v>-5.277</v>
       </c>
     </row>
     <row r="41">
@@ -3069,10 +3069,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.2399</v>
+        <v>-0.2379</v>
       </c>
       <c r="J41" t="n">
-        <v>-7.197</v>
+        <v>-7.137</v>
       </c>
     </row>
     <row r="42">
@@ -3109,10 +3109,10 @@
         <v>1.23</v>
       </c>
       <c r="I42" t="n">
-        <v>0.4776</v>
+        <v>0.4727</v>
       </c>
       <c r="J42" t="n">
-        <v>13.3728</v>
+        <v>13.2356</v>
       </c>
     </row>
     <row r="43">
@@ -3149,10 +3149,10 @@
         <v>1.08</v>
       </c>
       <c r="I43" t="n">
-        <v>0.195</v>
+        <v>0.2053</v>
       </c>
       <c r="J43" t="n">
-        <v>5.46</v>
+        <v>5.7484</v>
       </c>
     </row>
     <row r="44">
@@ -3189,10 +3189,10 @@
         <v>1.03</v>
       </c>
       <c r="I44" t="n">
-        <v>0.0854</v>
+        <v>0.0955</v>
       </c>
       <c r="J44" t="n">
-        <v>2.3912</v>
+        <v>2.674</v>
       </c>
     </row>
     <row r="45">
@@ -3229,10 +3229,10 @@
         <v>1.02</v>
       </c>
       <c r="I45" t="n">
-        <v>0.0597</v>
+        <v>0.0689</v>
       </c>
       <c r="J45" t="n">
-        <v>1.6716</v>
+        <v>1.9292</v>
       </c>
     </row>
     <row r="46">
@@ -3269,10 +3269,10 @@
         <v>0.89</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.1508</v>
+        <v>-0.1626</v>
       </c>
       <c r="J46" t="n">
-        <v>-4.2224</v>
+        <v>-4.5528</v>
       </c>
     </row>
     <row r="47">
@@ -3309,10 +3309,10 @@
         <v>1.3</v>
       </c>
       <c r="I47" t="n">
-        <v>0.8496</v>
+        <v>0.7921</v>
       </c>
       <c r="J47" t="n">
-        <v>23.7888</v>
+        <v>22.1788</v>
       </c>
     </row>
     <row r="48">
@@ -3349,10 +3349,10 @@
         <v>1.18</v>
       </c>
       <c r="I48" t="n">
-        <v>0.5496</v>
+        <v>0.5274</v>
       </c>
       <c r="J48" t="n">
-        <v>15.3888</v>
+        <v>14.7672</v>
       </c>
     </row>
     <row r="49">
@@ -3389,10 +3389,10 @@
         <v>1.07</v>
       </c>
       <c r="I49" t="n">
-        <v>0.2471</v>
+        <v>0.2507</v>
       </c>
       <c r="J49" t="n">
-        <v>6.9188</v>
+        <v>7.0196</v>
       </c>
     </row>
     <row r="50">
@@ -3429,10 +3429,10 @@
         <v>0.91</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.3334</v>
+        <v>-0.3246</v>
       </c>
       <c r="J50" t="n">
-        <v>-9.3352</v>
+        <v>-9.088800000000001</v>
       </c>
     </row>
     <row r="51">
@@ -3469,10 +3469,10 @@
         <v>0.78</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.6869</v>
+        <v>-0.6431</v>
       </c>
       <c r="J51" t="n">
-        <v>-19.2332</v>
+        <v>-18.0068</v>
       </c>
     </row>
     <row r="52">
@@ -3509,10 +3509,10 @@
         <v>1.01</v>
       </c>
       <c r="I52" t="n">
-        <v>0.0381</v>
+        <v>0.0407</v>
       </c>
       <c r="J52" t="n">
-        <v>1.0668</v>
+        <v>1.1396</v>
       </c>
     </row>
     <row r="53">
@@ -3549,10 +3549,10 @@
         <v>0.97</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.0452</v>
+        <v>-0.0545</v>
       </c>
       <c r="J53" t="n">
-        <v>-1.2656</v>
+        <v>-1.526</v>
       </c>
     </row>
     <row r="54">
@@ -3589,10 +3589,10 @@
         <v>0.92</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.1054</v>
+        <v>-0.1188</v>
       </c>
       <c r="J54" t="n">
-        <v>-2.9512</v>
+        <v>-3.3264</v>
       </c>
     </row>
     <row r="55">
@@ -3629,10 +3629,10 @@
         <v>0.9</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.1276</v>
+        <v>-0.1418</v>
       </c>
       <c r="J55" t="n">
-        <v>-3.5728</v>
+        <v>-3.9704</v>
       </c>
     </row>
     <row r="56">
@@ -3669,10 +3669,10 @@
         <v>0.89</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.1384</v>
+        <v>-0.1529</v>
       </c>
       <c r="J56" t="n">
-        <v>-3.8752</v>
+        <v>-4.2812</v>
       </c>
     </row>
     <row r="57">
@@ -3709,10 +3709,10 @@
         <v>1.5</v>
       </c>
       <c r="I57" t="n">
-        <v>0.6215000000000001</v>
+        <v>0.6236</v>
       </c>
       <c r="J57" t="n">
-        <v>17.402</v>
+        <v>17.4608</v>
       </c>
     </row>
     <row r="58">
@@ -3749,10 +3749,10 @@
         <v>1.37</v>
       </c>
       <c r="I58" t="n">
-        <v>0.4775</v>
+        <v>0.4882</v>
       </c>
       <c r="J58" t="n">
-        <v>13.37</v>
+        <v>13.6696</v>
       </c>
     </row>
     <row r="59">
@@ -3789,10 +3789,10 @@
         <v>1.31</v>
       </c>
       <c r="I59" t="n">
-        <v>0.4092</v>
+        <v>0.4231</v>
       </c>
       <c r="J59" t="n">
-        <v>11.4576</v>
+        <v>11.8468</v>
       </c>
     </row>
     <row r="60">
@@ -3829,10 +3829,10 @@
         <v>0.98</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.0567</v>
+        <v>-0.0587</v>
       </c>
       <c r="J60" t="n">
-        <v>-1.5876</v>
+        <v>-1.6436</v>
       </c>
     </row>
     <row r="61">
@@ -3869,10 +3869,10 @@
         <v>0.89</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.1673</v>
+        <v>-0.1754</v>
       </c>
       <c r="J61" t="n">
-        <v>-4.6844</v>
+        <v>-4.9112</v>
       </c>
     </row>
     <row r="62">
@@ -3909,10 +3909,10 @@
         <v>1.81</v>
       </c>
       <c r="I62" t="n">
-        <v>1.4507</v>
+        <v>1.445</v>
       </c>
       <c r="J62" t="n">
-        <v>29.014</v>
+        <v>28.9</v>
       </c>
     </row>
     <row r="63">
@@ -3949,10 +3949,10 @@
         <v>1.62</v>
       </c>
       <c r="I63" t="n">
-        <v>1.2331</v>
+        <v>1.2133</v>
       </c>
       <c r="J63" t="n">
-        <v>24.662</v>
+        <v>24.266</v>
       </c>
     </row>
     <row r="64">
@@ -3989,10 +3989,10 @@
         <v>1.57</v>
       </c>
       <c r="I64" t="n">
-        <v>1.1751</v>
+        <v>1.1509</v>
       </c>
       <c r="J64" t="n">
-        <v>23.502</v>
+        <v>23.018</v>
       </c>
     </row>
     <row r="65">
@@ -4029,10 +4029,10 @@
         <v>1.52</v>
       </c>
       <c r="I65" t="n">
-        <v>1.1171</v>
+        <v>1.088</v>
       </c>
       <c r="J65" t="n">
-        <v>22.342</v>
+        <v>21.76</v>
       </c>
     </row>
     <row r="66">
@@ -4069,10 +4069,10 @@
         <v>0.97</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.2474</v>
+        <v>-0.2175</v>
       </c>
       <c r="J66" t="n">
-        <v>-4.948</v>
+        <v>-4.35</v>
       </c>
     </row>
     <row r="67">
@@ -4109,10 +4109,10 @@
         <v>0.88</v>
       </c>
       <c r="I67" t="n">
-        <v>-0.0988</v>
+        <v>-0.1248</v>
       </c>
       <c r="J67" t="n">
-        <v>-1.976</v>
+        <v>-2.496</v>
       </c>
     </row>
     <row r="68">
@@ -4149,10 +4149,10 @@
         <v>0.85</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.1341</v>
+        <v>-0.1597</v>
       </c>
       <c r="J68" t="n">
-        <v>-2.682</v>
+        <v>-3.194</v>
       </c>
     </row>
     <row r="69">
@@ -4189,10 +4189,10 @@
         <v>0.59</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.3915</v>
+        <v>-0.4092</v>
       </c>
       <c r="J69" t="n">
-        <v>-7.83</v>
+        <v>-8.183999999999999</v>
       </c>
     </row>
     <row r="70">
@@ -4229,10 +4229,10 @@
         <v>0.49</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.4851</v>
+        <v>-0.4973</v>
       </c>
       <c r="J70" t="n">
-        <v>-9.702</v>
+        <v>-9.946</v>
       </c>
     </row>
     <row r="71">
@@ -4269,10 +4269,10 @@
         <v>0.48</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.4945</v>
+        <v>-0.506</v>
       </c>
       <c r="J71" t="n">
-        <v>-9.890000000000001</v>
+        <v>-10.12</v>
       </c>
     </row>
     <row r="72">
@@ -4309,10 +4309,10 @@
         <v>1.33</v>
       </c>
       <c r="I72" t="n">
-        <v>0.8831</v>
+        <v>0.8277</v>
       </c>
       <c r="J72" t="n">
-        <v>30.9085</v>
+        <v>28.9695</v>
       </c>
     </row>
     <row r="73">
@@ -4349,10 +4349,10 @@
         <v>1.33</v>
       </c>
       <c r="I73" t="n">
-        <v>0.8831</v>
+        <v>0.8277</v>
       </c>
       <c r="J73" t="n">
-        <v>30.9085</v>
+        <v>28.9695</v>
       </c>
     </row>
     <row r="74">
@@ -4389,10 +4389,10 @@
         <v>1.25</v>
       </c>
       <c r="I74" t="n">
-        <v>0.6941000000000001</v>
+        <v>0.6618000000000001</v>
       </c>
       <c r="J74" t="n">
-        <v>24.2935</v>
+        <v>23.163</v>
       </c>
     </row>
     <row r="75">
@@ -4429,10 +4429,10 @@
         <v>1</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.0328</v>
+        <v>-0.0225</v>
       </c>
       <c r="J75" t="n">
-        <v>-1.148</v>
+        <v>-0.7875</v>
       </c>
     </row>
     <row r="76">
@@ -4469,10 +4469,10 @@
         <v>0.78</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.7112000000000001</v>
+        <v>-0.6601</v>
       </c>
       <c r="J76" t="n">
-        <v>-24.892</v>
+        <v>-23.1035</v>
       </c>
     </row>
     <row r="77">
@@ -4509,10 +4509,10 @@
         <v>1.37</v>
       </c>
       <c r="I77" t="n">
-        <v>0.7356</v>
+        <v>0.7046</v>
       </c>
       <c r="J77" t="n">
-        <v>25.746</v>
+        <v>24.661</v>
       </c>
     </row>
     <row r="78">
@@ -4549,10 +4549,10 @@
         <v>1.08</v>
       </c>
       <c r="I78" t="n">
-        <v>0.204</v>
+        <v>0.2118</v>
       </c>
       <c r="J78" t="n">
-        <v>7.14</v>
+        <v>7.413</v>
       </c>
     </row>
     <row r="79">
@@ -4589,10 +4589,10 @@
         <v>0.97</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.0504</v>
+        <v>-0.0585</v>
       </c>
       <c r="J79" t="n">
-        <v>-1.764</v>
+        <v>-2.0475</v>
       </c>
     </row>
     <row r="80">
@@ -4629,10 +4629,10 @@
         <v>0.85</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.1884</v>
+        <v>-0.2018</v>
       </c>
       <c r="J80" t="n">
-        <v>-6.594</v>
+        <v>-7.063</v>
       </c>
     </row>
     <row r="81">
@@ -4669,10 +4669,10 @@
         <v>0.75</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.2888</v>
+        <v>-0.3013</v>
       </c>
       <c r="J81" t="n">
-        <v>-10.108</v>
+        <v>-10.5455</v>
       </c>
     </row>
     <row r="82">
@@ -4709,10 +4709,10 @@
         <v>1.72</v>
       </c>
       <c r="I82" t="n">
-        <v>1.3812</v>
+        <v>1.3653</v>
       </c>
       <c r="J82" t="n">
-        <v>35.9112</v>
+        <v>35.4978</v>
       </c>
     </row>
     <row r="83">
@@ -4749,10 +4749,10 @@
         <v>1.41</v>
       </c>
       <c r="I83" t="n">
-        <v>0.9932</v>
+        <v>0.9421</v>
       </c>
       <c r="J83" t="n">
-        <v>25.8232</v>
+        <v>24.4946</v>
       </c>
     </row>
     <row r="84">
@@ -4789,10 +4789,10 @@
         <v>1.22</v>
       </c>
       <c r="I84" t="n">
-        <v>0.5839</v>
+        <v>0.5717</v>
       </c>
       <c r="J84" t="n">
-        <v>15.1814</v>
+        <v>14.8642</v>
       </c>
     </row>
     <row r="85">
@@ -4829,10 +4829,10 @@
         <v>1.19</v>
       </c>
       <c r="I85" t="n">
-        <v>0.5103</v>
+        <v>0.5058</v>
       </c>
       <c r="J85" t="n">
-        <v>13.2678</v>
+        <v>13.1508</v>
       </c>
     </row>
     <row r="86">
@@ -4869,10 +4869,10 @@
         <v>1.11</v>
       </c>
       <c r="I86" t="n">
-        <v>0.3003</v>
+        <v>0.3151</v>
       </c>
       <c r="J86" t="n">
-        <v>7.8078</v>
+        <v>8.192600000000001</v>
       </c>
     </row>
     <row r="87">
@@ -4909,10 +4909,10 @@
         <v>1.02</v>
       </c>
       <c r="I87" t="n">
-        <v>0.1322</v>
+        <v>0.1216</v>
       </c>
       <c r="J87" t="n">
-        <v>3.4372</v>
+        <v>3.1616</v>
       </c>
     </row>
     <row r="88">
@@ -4949,10 +4949,10 @@
         <v>1.01</v>
       </c>
       <c r="I88" t="n">
-        <v>0.1016</v>
+        <v>0.0898</v>
       </c>
       <c r="J88" t="n">
-        <v>2.6416</v>
+        <v>2.3348</v>
       </c>
     </row>
     <row r="89">
@@ -4989,10 +4989,10 @@
         <v>0.88</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.132</v>
+        <v>-0.1508</v>
       </c>
       <c r="J89" t="n">
-        <v>-3.432</v>
+        <v>-3.9208</v>
       </c>
     </row>
     <row r="90">
@@ -5029,10 +5029,10 @@
         <v>0.7</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.3091</v>
+        <v>-0.3265</v>
       </c>
       <c r="J90" t="n">
-        <v>-8.0366</v>
+        <v>-8.489000000000001</v>
       </c>
     </row>
     <row r="91">
@@ -5069,10 +5069,10 @@
         <v>0.34</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.6423</v>
+        <v>-0.6409</v>
       </c>
       <c r="J91" t="n">
-        <v>-16.6998</v>
+        <v>-16.6634</v>
       </c>
     </row>
     <row r="92">
@@ -5109,10 +5109,10 @@
         <v>1.14</v>
       </c>
       <c r="I92" t="n">
-        <v>0.2905</v>
+        <v>0.288</v>
       </c>
       <c r="J92" t="n">
-        <v>7.553</v>
+        <v>7.488</v>
       </c>
     </row>
     <row r="93">
@@ -5149,10 +5149,10 @@
         <v>1</v>
       </c>
       <c r="I93" t="n">
-        <v>0.0271</v>
+        <v>0.02</v>
       </c>
       <c r="J93" t="n">
-        <v>0.7046</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="94">
@@ -5189,10 +5189,10 @@
         <v>0.74</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.2797</v>
+        <v>-0.2961</v>
       </c>
       <c r="J94" t="n">
-        <v>-7.2722</v>
+        <v>-7.6986</v>
       </c>
     </row>
     <row r="95">
@@ -5229,10 +5229,10 @@
         <v>0.74</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.2797</v>
+        <v>-0.2961</v>
       </c>
       <c r="J95" t="n">
-        <v>-7.2722</v>
+        <v>-7.6986</v>
       </c>
     </row>
     <row r="96">
@@ -5269,10 +5269,10 @@
         <v>0.65</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.3654</v>
+        <v>-0.3791</v>
       </c>
       <c r="J96" t="n">
-        <v>-9.500400000000001</v>
+        <v>-9.8566</v>
       </c>
     </row>
     <row r="97">
@@ -5309,10 +5309,10 @@
         <v>1.5</v>
       </c>
       <c r="I97" t="n">
-        <v>0.6066</v>
+        <v>0.6121</v>
       </c>
       <c r="J97" t="n">
-        <v>15.7716</v>
+        <v>15.9146</v>
       </c>
     </row>
     <row r="98">
@@ -5349,10 +5349,10 @@
         <v>1.44</v>
       </c>
       <c r="I98" t="n">
-        <v>0.5422</v>
+        <v>0.5517</v>
       </c>
       <c r="J98" t="n">
-        <v>14.0972</v>
+        <v>14.3442</v>
       </c>
     </row>
     <row r="99">
@@ -5389,10 +5389,10 @@
         <v>1.27</v>
       </c>
       <c r="I99" t="n">
-        <v>0.3561</v>
+        <v>0.3735</v>
       </c>
       <c r="J99" t="n">
-        <v>9.258599999999999</v>
+        <v>9.711</v>
       </c>
     </row>
     <row r="100">
@@ -5429,10 +5429,10 @@
         <v>1.15</v>
       </c>
       <c r="I100" t="n">
-        <v>0.2096</v>
+        <v>0.2302</v>
       </c>
       <c r="J100" t="n">
-        <v>5.4496</v>
+        <v>5.9852</v>
       </c>
     </row>
     <row r="101">
@@ -5469,10 +5469,10 @@
         <v>1.1</v>
       </c>
       <c r="I101" t="n">
-        <v>0.1413</v>
+        <v>0.162</v>
       </c>
       <c r="J101" t="n">
-        <v>3.6738</v>
+        <v>4.212</v>
       </c>
     </row>
     <row r="102">
@@ -5509,10 +5509,10 @@
         <v>1.62</v>
       </c>
       <c r="I102" t="n">
-        <v>1.2553</v>
+        <v>1.2327</v>
       </c>
       <c r="J102" t="n">
-        <v>30.1272</v>
+        <v>29.5848</v>
       </c>
     </row>
     <row r="103">
@@ -5549,10 +5549,10 @@
         <v>1.49</v>
       </c>
       <c r="I103" t="n">
-        <v>1.0976</v>
+        <v>1.0628</v>
       </c>
       <c r="J103" t="n">
-        <v>26.3424</v>
+        <v>25.5072</v>
       </c>
     </row>
     <row r="104">
@@ -5589,10 +5589,10 @@
         <v>1.33</v>
       </c>
       <c r="I104" t="n">
-        <v>0.8298</v>
+        <v>0.791</v>
       </c>
       <c r="J104" t="n">
-        <v>19.9152</v>
+        <v>18.984</v>
       </c>
     </row>
     <row r="105">
@@ -5629,10 +5629,10 @@
         <v>1.24</v>
       </c>
       <c r="I105" t="n">
-        <v>0.6254</v>
+        <v>0.61</v>
       </c>
       <c r="J105" t="n">
-        <v>15.0096</v>
+        <v>14.64</v>
       </c>
     </row>
     <row r="106">
@@ -5669,10 +5669,10 @@
         <v>1.12</v>
       </c>
       <c r="I106" t="n">
-        <v>0.3212</v>
+        <v>0.3357</v>
       </c>
       <c r="J106" t="n">
-        <v>7.7088</v>
+        <v>8.056800000000001</v>
       </c>
     </row>
     <row r="107">
@@ -5709,10 +5709,10 @@
         <v>0.96</v>
       </c>
       <c r="I107" t="n">
-        <v>-0.0339</v>
+        <v>-0.0499</v>
       </c>
       <c r="J107" t="n">
-        <v>-0.8136</v>
+        <v>-1.1976</v>
       </c>
     </row>
     <row r="108">
@@ -5749,10 +5749,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I108" t="n">
-        <v>-0.2049</v>
+        <v>-0.2239</v>
       </c>
       <c r="J108" t="n">
-        <v>-4.9176</v>
+        <v>-5.3736</v>
       </c>
     </row>
     <row r="109">
@@ -5789,10 +5789,10 @@
         <v>0.77</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.2425</v>
+        <v>-0.2614</v>
       </c>
       <c r="J109" t="n">
-        <v>-5.82</v>
+        <v>-6.2736</v>
       </c>
     </row>
     <row r="110">
@@ -5829,10 +5829,10 @@
         <v>0.75</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.2614</v>
+        <v>-0.28</v>
       </c>
       <c r="J110" t="n">
-        <v>-6.2736</v>
+        <v>-6.72</v>
       </c>
     </row>
     <row r="111">
@@ -5869,10 +5869,10 @@
         <v>0.65</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.3561</v>
+        <v>-0.3718</v>
       </c>
       <c r="J111" t="n">
-        <v>-8.5464</v>
+        <v>-8.9232</v>
       </c>
     </row>
     <row r="112">
@@ -5909,10 +5909,10 @@
         <v>1.89</v>
       </c>
       <c r="I112" t="n">
-        <v>0.7145</v>
+        <v>0.8243</v>
       </c>
       <c r="J112" t="n">
-        <v>16.4335</v>
+        <v>18.9589</v>
       </c>
     </row>
     <row r="113">
@@ -5949,10 +5949,10 @@
         <v>1.56</v>
       </c>
       <c r="I113" t="n">
-        <v>0.521</v>
+        <v>0.6002</v>
       </c>
       <c r="J113" t="n">
-        <v>11.983</v>
+        <v>13.8046</v>
       </c>
     </row>
     <row r="114">
@@ -5989,10 +5989,10 @@
         <v>1.25</v>
       </c>
       <c r="I114" t="n">
-        <v>0.3193</v>
+        <v>0.3418</v>
       </c>
       <c r="J114" t="n">
-        <v>7.3439</v>
+        <v>7.8614</v>
       </c>
     </row>
     <row r="115">
@@ -6029,10 +6029,10 @@
         <v>1.21</v>
       </c>
       <c r="I115" t="n">
-        <v>0.2722</v>
+        <v>0.2947</v>
       </c>
       <c r="J115" t="n">
-        <v>6.2606</v>
+        <v>6.7781</v>
       </c>
     </row>
     <row r="116">
@@ -6069,10 +6069,10 @@
         <v>1.17</v>
       </c>
       <c r="I116" t="n">
-        <v>0.2219</v>
+        <v>0.2454</v>
       </c>
       <c r="J116" t="n">
-        <v>5.1037</v>
+        <v>5.6442</v>
       </c>
     </row>
     <row r="117">
@@ -6109,10 +6109,10 @@
         <v>0.95</v>
       </c>
       <c r="I117" t="n">
-        <v>-0.036</v>
+        <v>-0.0552</v>
       </c>
       <c r="J117" t="n">
-        <v>-0.828</v>
+        <v>-1.2696</v>
       </c>
     </row>
     <row r="118">
@@ -6149,10 +6149,10 @@
         <v>0.77</v>
       </c>
       <c r="I118" t="n">
-        <v>-0.2379</v>
+        <v>-0.2579</v>
       </c>
       <c r="J118" t="n">
-        <v>-5.4717</v>
+        <v>-5.9317</v>
       </c>
     </row>
     <row r="119">
@@ -6189,10 +6189,10 @@
         <v>0.71</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.293</v>
+        <v>-0.3122</v>
       </c>
       <c r="J119" t="n">
-        <v>-6.739</v>
+        <v>-7.1806</v>
       </c>
     </row>
     <row r="120">
@@ -6229,10 +6229,10 @@
         <v>0.7</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.3023</v>
+        <v>-0.3212</v>
       </c>
       <c r="J120" t="n">
-        <v>-6.9529</v>
+        <v>-7.3876</v>
       </c>
     </row>
     <row r="121">
@@ -6269,10 +6269,10 @@
         <v>0.58</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.4147</v>
+        <v>-0.4288</v>
       </c>
       <c r="J121" t="n">
-        <v>-9.5381</v>
+        <v>-9.862399999999999</v>
       </c>
     </row>
     <row r="122">
@@ -6309,10 +6309,10 @@
         <v>1.1</v>
       </c>
       <c r="I122" t="n">
-        <v>0.3003</v>
+        <v>0.292</v>
       </c>
       <c r="J122" t="n">
-        <v>7.2072</v>
+        <v>7.008</v>
       </c>
     </row>
     <row r="123">
@@ -6349,10 +6349,10 @@
         <v>1.03</v>
       </c>
       <c r="I123" t="n">
-        <v>0.1363</v>
+        <v>0.1323</v>
       </c>
       <c r="J123" t="n">
-        <v>3.2712</v>
+        <v>3.1752</v>
       </c>
     </row>
     <row r="124">
@@ -6389,10 +6389,10 @@
         <v>0.83</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.1905</v>
+        <v>-0.2082</v>
       </c>
       <c r="J124" t="n">
-        <v>-4.572</v>
+        <v>-4.9968</v>
       </c>
     </row>
     <row r="125">
@@ -6429,10 +6429,10 @@
         <v>0.67</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.3452</v>
+        <v>-0.3599</v>
       </c>
       <c r="J125" t="n">
-        <v>-8.284800000000001</v>
+        <v>-8.637600000000001</v>
       </c>
     </row>
     <row r="126">
@@ -6469,10 +6469,10 @@
         <v>0.59</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.4201</v>
+        <v>-0.4316</v>
       </c>
       <c r="J126" t="n">
-        <v>-10.0824</v>
+        <v>-10.3584</v>
       </c>
     </row>
     <row r="127">
@@ -6509,10 +6509,10 @@
         <v>1.6</v>
       </c>
       <c r="I127" t="n">
-        <v>0.9629</v>
+        <v>1.0645</v>
       </c>
       <c r="J127" t="n">
-        <v>23.1096</v>
+        <v>25.548</v>
       </c>
     </row>
     <row r="128">
@@ -6549,10 +6549,10 @@
         <v>1.43</v>
       </c>
       <c r="I128" t="n">
-        <v>0.7536</v>
+        <v>0.8388</v>
       </c>
       <c r="J128" t="n">
-        <v>18.0864</v>
+        <v>20.1312</v>
       </c>
     </row>
     <row r="129">
@@ -6589,10 +6589,10 @@
         <v>1.26</v>
       </c>
       <c r="I129" t="n">
-        <v>0.5366</v>
+        <v>0.599</v>
       </c>
       <c r="J129" t="n">
-        <v>12.8784</v>
+        <v>14.376</v>
       </c>
     </row>
     <row r="130">
@@ -6629,10 +6629,10 @@
         <v>1.21</v>
       </c>
       <c r="I130" t="n">
-        <v>0.4667</v>
+        <v>0.5207000000000001</v>
       </c>
       <c r="J130" t="n">
-        <v>11.2008</v>
+        <v>12.4968</v>
       </c>
     </row>
     <row r="131">
@@ -6669,10 +6669,10 @@
         <v>1.16</v>
       </c>
       <c r="I131" t="n">
-        <v>0.3928</v>
+        <v>0.4343</v>
       </c>
       <c r="J131" t="n">
-        <v>9.427199999999999</v>
+        <v>10.4232</v>
       </c>
     </row>
     <row r="132">
@@ -6709,10 +6709,10 @@
         <v>1.15</v>
       </c>
       <c r="I132" t="n">
-        <v>0.4109</v>
+        <v>0.4321</v>
       </c>
       <c r="J132" t="n">
-        <v>9.0398</v>
+        <v>9.5062</v>
       </c>
     </row>
     <row r="133">
@@ -6749,10 +6749,10 @@
         <v>0.93</v>
       </c>
       <c r="I133" t="n">
-        <v>-0.06270000000000001</v>
+        <v>-0.0827</v>
       </c>
       <c r="J133" t="n">
-        <v>-1.3794</v>
+        <v>-1.8194</v>
       </c>
     </row>
     <row r="134">
@@ -6789,10 +6789,10 @@
         <v>0.67</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.3307</v>
+        <v>-0.3486</v>
       </c>
       <c r="J134" t="n">
-        <v>-7.2754</v>
+        <v>-7.6692</v>
       </c>
     </row>
     <row r="135">
@@ -6829,10 +6829,10 @@
         <v>0.55</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.443</v>
+        <v>-0.4556</v>
       </c>
       <c r="J135" t="n">
-        <v>-9.746</v>
+        <v>-10.0232</v>
       </c>
     </row>
     <row r="136">
@@ -6869,10 +6869,10 @@
         <v>0.42</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.5637</v>
+        <v>-0.5686</v>
       </c>
       <c r="J136" t="n">
-        <v>-12.4014</v>
+        <v>-12.5092</v>
       </c>
     </row>
     <row r="137">
@@ -6909,10 +6909,10 @@
         <v>1.62</v>
       </c>
       <c r="I137" t="n">
-        <v>0.9738</v>
+        <v>1.0786</v>
       </c>
       <c r="J137" t="n">
-        <v>21.4236</v>
+        <v>23.7292</v>
       </c>
     </row>
     <row r="138">
@@ -6949,10 +6949,10 @@
         <v>1.59</v>
       </c>
       <c r="I138" t="n">
-        <v>0.9381</v>
+        <v>1.0404</v>
       </c>
       <c r="J138" t="n">
-        <v>20.6382</v>
+        <v>22.8888</v>
       </c>
     </row>
     <row r="139">
@@ -6989,10 +6989,10 @@
         <v>1.48</v>
       </c>
       <c r="I139" t="n">
-        <v>0.8058999999999999</v>
+        <v>0.8977000000000001</v>
       </c>
       <c r="J139" t="n">
-        <v>17.7298</v>
+        <v>19.7494</v>
       </c>
     </row>
     <row r="140">
@@ -7029,10 +7029,10 @@
         <v>1.24</v>
       </c>
       <c r="I140" t="n">
-        <v>0.5004999999999999</v>
+        <v>0.5608</v>
       </c>
       <c r="J140" t="n">
-        <v>11.011</v>
+        <v>12.3376</v>
       </c>
     </row>
     <row r="141">
@@ -7069,10 +7069,10 @@
         <v>1.08</v>
       </c>
       <c r="I141" t="n">
-        <v>0.1982</v>
+        <v>0.2241</v>
       </c>
       <c r="J141" t="n">
-        <v>4.3604</v>
+        <v>4.9302</v>
       </c>
     </row>
     <row r="142">
@@ -7109,10 +7109,10 @@
         <v>1.22</v>
       </c>
       <c r="I142" t="n">
-        <v>0.4029</v>
+        <v>0.4453</v>
       </c>
       <c r="J142" t="n">
-        <v>12.087</v>
+        <v>13.359</v>
       </c>
     </row>
     <row r="143">
@@ -7149,10 +7149,10 @@
         <v>1.21</v>
       </c>
       <c r="I143" t="n">
-        <v>0.3925</v>
+        <v>0.4312</v>
       </c>
       <c r="J143" t="n">
-        <v>11.775</v>
+        <v>12.936</v>
       </c>
     </row>
     <row r="144">
@@ -7189,10 +7189,10 @@
         <v>1.21</v>
       </c>
       <c r="I144" t="n">
-        <v>0.3925</v>
+        <v>0.4312</v>
       </c>
       <c r="J144" t="n">
-        <v>11.775</v>
+        <v>12.936</v>
       </c>
     </row>
     <row r="145">
@@ -7229,10 +7229,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.097</v>
+        <v>-0.1059</v>
       </c>
       <c r="J145" t="n">
-        <v>-2.91</v>
+        <v>-3.177</v>
       </c>
     </row>
     <row r="146">
@@ -7269,10 +7269,10 @@
         <v>0.84</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.2077</v>
+        <v>-0.2192</v>
       </c>
       <c r="J146" t="n">
-        <v>-6.231</v>
+        <v>-6.576</v>
       </c>
     </row>
     <row r="147">
@@ -7309,10 +7309,10 @@
         <v>1.22</v>
       </c>
       <c r="I147" t="n">
-        <v>0.5353</v>
+        <v>0.5839</v>
       </c>
       <c r="J147" t="n">
-        <v>16.059</v>
+        <v>17.517</v>
       </c>
     </row>
     <row r="148">
@@ -7349,10 +7349,10 @@
         <v>1.1</v>
       </c>
       <c r="I148" t="n">
-        <v>0.3432</v>
+        <v>0.3434</v>
       </c>
       <c r="J148" t="n">
-        <v>10.296</v>
+        <v>10.302</v>
       </c>
     </row>
     <row r="149">
@@ -7389,10 +7389,10 @@
         <v>0.93</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.2583</v>
+        <v>-0.2584</v>
       </c>
       <c r="J149" t="n">
-        <v>-7.749</v>
+        <v>-7.752</v>
       </c>
     </row>
     <row r="150">
@@ -7429,10 +7429,10 @@
         <v>0.91</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.3181</v>
+        <v>-0.314</v>
       </c>
       <c r="J150" t="n">
-        <v>-9.542999999999999</v>
+        <v>-9.42</v>
       </c>
     </row>
     <row r="151">
@@ -7469,10 +7469,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.5931999999999999</v>
+        <v>-0.5629999999999999</v>
       </c>
       <c r="J151" t="n">
-        <v>-17.796</v>
+        <v>-16.89</v>
       </c>
     </row>
     <row r="152">
@@ -7509,10 +7509,10 @@
         <v>1.1</v>
       </c>
       <c r="I152" t="n">
-        <v>0.25</v>
+        <v>0.2551</v>
       </c>
       <c r="J152" t="n">
-        <v>6.25</v>
+        <v>6.3775</v>
       </c>
     </row>
     <row r="153">
@@ -7549,10 +7549,10 @@
         <v>1.05</v>
       </c>
       <c r="I153" t="n">
-        <v>0.1422</v>
+        <v>0.15</v>
       </c>
       <c r="J153" t="n">
-        <v>3.555</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="154">
@@ -7589,10 +7589,10 @@
         <v>1.02</v>
       </c>
       <c r="I154" t="n">
-        <v>0.0684</v>
+        <v>0.0751</v>
       </c>
       <c r="J154" t="n">
-        <v>1.71</v>
+        <v>1.8775</v>
       </c>
     </row>
     <row r="155">
@@ -7629,10 +7629,10 @@
         <v>0.97</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.0488</v>
+        <v>-0.0573</v>
       </c>
       <c r="J155" t="n">
-        <v>-1.22</v>
+        <v>-1.4325</v>
       </c>
     </row>
     <row r="156">
@@ -7669,10 +7669,10 @@
         <v>0.79</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.2474</v>
+        <v>-0.261</v>
       </c>
       <c r="J156" t="n">
-        <v>-6.185</v>
+        <v>-6.525</v>
       </c>
     </row>
     <row r="157">
@@ -7709,10 +7709,10 @@
         <v>1.42</v>
       </c>
       <c r="I157" t="n">
-        <v>0.7724</v>
+        <v>0.8526</v>
       </c>
       <c r="J157" t="n">
-        <v>19.31</v>
+        <v>21.315</v>
       </c>
     </row>
     <row r="158">
@@ -7749,10 +7749,10 @@
         <v>1.38</v>
       </c>
       <c r="I158" t="n">
-        <v>0.7193000000000001</v>
+        <v>0.795</v>
       </c>
       <c r="J158" t="n">
-        <v>17.9825</v>
+        <v>19.875</v>
       </c>
     </row>
     <row r="159">
@@ -7789,10 +7789,10 @@
         <v>1.13</v>
       </c>
       <c r="I159" t="n">
-        <v>0.3684</v>
+        <v>0.391</v>
       </c>
       <c r="J159" t="n">
-        <v>9.210000000000001</v>
+        <v>9.775</v>
       </c>
     </row>
     <row r="160">
@@ -7829,10 +7829,10 @@
         <v>0.96</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.2078</v>
+        <v>-0.1989</v>
       </c>
       <c r="J160" t="n">
-        <v>-5.195</v>
+        <v>-4.9725</v>
       </c>
     </row>
     <row r="161">
@@ -7869,10 +7869,10 @@
         <v>0.93</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.3047</v>
+        <v>-0.2907</v>
       </c>
       <c r="J161" t="n">
-        <v>-7.6175</v>
+        <v>-7.2675</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/5274/event_5274_evp_summary.xlsx
+++ b/database/event/5274/event_5274_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.1402</v>
+        <v>3.9211</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5798</v>
+        <v>0.5491</v>
       </c>
       <c r="D2" t="n">
-        <v>1.2605</v>
+        <v>1.1805</v>
       </c>
       <c r="E2" t="n">
-        <v>4.1402</v>
+        <v>3.9211</v>
       </c>
       <c r="F2" t="n">
-        <v>1.1652</v>
+        <v>0.9986</v>
       </c>
       <c r="G2" t="n">
-        <v>2.975</v>
+        <v>2.9225</v>
       </c>
       <c r="H2" t="n">
-        <v>1.1652</v>
+        <v>0.9986</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6292</v>
+        <v>0.5607</v>
       </c>
       <c r="J2" t="n">
-        <v>2.975</v>
+        <v>2.9225</v>
       </c>
       <c r="K2" t="n">
         <v>171</v>
@@ -529,7 +529,7 @@
         <v>133</v>
       </c>
       <c r="M2" t="n">
-        <v>3.6042</v>
+        <v>3.4832</v>
       </c>
       <c r="N2" t="n">
         <v>304</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.6705</v>
+        <v>3.7332</v>
       </c>
       <c r="C3" t="n">
-        <v>0.5141</v>
+        <v>0.5228</v>
       </c>
       <c r="D3" t="n">
-        <v>1.0467</v>
+        <v>1.0949</v>
       </c>
       <c r="E3" t="n">
-        <v>3.6705</v>
+        <v>3.7332</v>
       </c>
       <c r="F3" t="n">
-        <v>2.6923</v>
+        <v>2.7478</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9782</v>
+        <v>0.9854000000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>3.9888</v>
+        <v>3.8739</v>
       </c>
       <c r="I3" t="n">
-        <v>2.1539</v>
+        <v>2.1751</v>
       </c>
       <c r="J3" t="n">
-        <v>0.9782</v>
+        <v>0.9854000000000001</v>
       </c>
       <c r="K3" t="n">
         <v>83</v>
@@ -575,7 +575,7 @@
         <v>119</v>
       </c>
       <c r="M3" t="n">
-        <v>3.1321</v>
+        <v>3.1605</v>
       </c>
       <c r="N3" t="n">
         <v>202</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.649</v>
+        <v>3.4776</v>
       </c>
       <c r="C4" t="n">
-        <v>0.511</v>
+        <v>0.487</v>
       </c>
       <c r="D4" t="n">
-        <v>1.0369</v>
+        <v>0.9784</v>
       </c>
       <c r="E4" t="n">
-        <v>3.649</v>
+        <v>3.4776</v>
       </c>
       <c r="F4" t="n">
-        <v>2.9627</v>
+        <v>2.8931</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6863</v>
+        <v>0.5845</v>
       </c>
       <c r="H4" t="n">
-        <v>4.881</v>
+        <v>4.4193</v>
       </c>
       <c r="I4" t="n">
-        <v>2.6357</v>
+        <v>2.4813</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6863</v>
+        <v>0.5845</v>
       </c>
       <c r="K4" t="n">
         <v>164</v>
@@ -621,7 +621,7 @@
         <v>55</v>
       </c>
       <c r="M4" t="n">
-        <v>3.322</v>
+        <v>3.0658</v>
       </c>
       <c r="N4" t="n">
         <v>219</v>
@@ -630,93 +630,93 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Ethan</t>
+          <t>yuurih</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.2568</v>
+        <v>3.0307</v>
       </c>
       <c r="C5" t="n">
-        <v>0.4561</v>
+        <v>0.4244</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8584000000000001</v>
+        <v>0.7748</v>
       </c>
       <c r="E5" t="n">
-        <v>3.2568</v>
+        <v>3.0307</v>
       </c>
       <c r="F5" t="n">
-        <v>2.1397</v>
+        <v>2.6836</v>
       </c>
       <c r="G5" t="n">
-        <v>1.1171</v>
+        <v>0.3471</v>
       </c>
       <c r="H5" t="n">
-        <v>2.1656</v>
+        <v>3.6328</v>
       </c>
       <c r="I5" t="n">
-        <v>1.1694</v>
+        <v>2.0397</v>
       </c>
       <c r="J5" t="n">
-        <v>1.1171</v>
+        <v>0.3471</v>
       </c>
       <c r="K5" t="n">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="L5" t="n">
-        <v>133</v>
+        <v>55</v>
       </c>
       <c r="M5" t="n">
-        <v>2.2865</v>
+        <v>2.3868</v>
       </c>
       <c r="N5" t="n">
-        <v>304</v>
+        <v>219</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>yuurih</t>
+          <t>Ethan</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.069</v>
+        <v>2.9802</v>
       </c>
       <c r="C6" t="n">
-        <v>0.4298</v>
+        <v>0.4174</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7729</v>
+        <v>0.7518</v>
       </c>
       <c r="E6" t="n">
-        <v>3.069</v>
+        <v>2.9802</v>
       </c>
       <c r="F6" t="n">
-        <v>2.681</v>
+        <v>1.8594</v>
       </c>
       <c r="G6" t="n">
-        <v>0.388</v>
+        <v>1.1208</v>
       </c>
       <c r="H6" t="n">
-        <v>3.9515</v>
+        <v>1.8594</v>
       </c>
       <c r="I6" t="n">
-        <v>2.1338</v>
+        <v>1.044</v>
       </c>
       <c r="J6" t="n">
-        <v>0.388</v>
+        <v>1.1208</v>
       </c>
       <c r="K6" t="n">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="L6" t="n">
-        <v>55</v>
+        <v>133</v>
       </c>
       <c r="M6" t="n">
-        <v>2.5218</v>
+        <v>2.1648</v>
       </c>
       <c r="N6" t="n">
-        <v>219</v>
+        <v>304</v>
       </c>
     </row>
     <row r="7">
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.7982</v>
+        <v>2.791</v>
       </c>
       <c r="C7" t="n">
-        <v>0.3919</v>
+        <v>0.3909</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6496</v>
+        <v>0.6656</v>
       </c>
       <c r="E7" t="n">
-        <v>2.7982</v>
+        <v>2.791</v>
       </c>
       <c r="F7" t="n">
-        <v>2.7541</v>
+        <v>2.7638</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0441</v>
+        <v>0.0272</v>
       </c>
       <c r="H7" t="n">
-        <v>4.1927</v>
+        <v>3.934</v>
       </c>
       <c r="I7" t="n">
-        <v>2.264</v>
+        <v>2.2088</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0441</v>
+        <v>0.0272</v>
       </c>
       <c r="K7" t="n">
         <v>164</v>
@@ -759,7 +759,7 @@
         <v>55</v>
       </c>
       <c r="M7" t="n">
-        <v>2.3081</v>
+        <v>2.236</v>
       </c>
       <c r="N7" t="n">
         <v>219</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.6121</v>
+        <v>2.4927</v>
       </c>
       <c r="C8" t="n">
-        <v>0.3658</v>
+        <v>0.3491</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5649</v>
+        <v>0.5298</v>
       </c>
       <c r="E8" t="n">
-        <v>2.6121</v>
+        <v>2.4927</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8678</v>
+        <v>0.9064</v>
       </c>
       <c r="G8" t="n">
-        <v>1.7443</v>
+        <v>1.5863</v>
       </c>
       <c r="H8" t="n">
-        <v>0.8678</v>
+        <v>0.9064</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4686</v>
+        <v>0.5089</v>
       </c>
       <c r="J8" t="n">
-        <v>1.7443</v>
+        <v>1.5863</v>
       </c>
       <c r="K8" t="n">
         <v>83</v>
@@ -805,7 +805,7 @@
         <v>119</v>
       </c>
       <c r="M8" t="n">
-        <v>2.2129</v>
+        <v>2.0952</v>
       </c>
       <c r="N8" t="n">
         <v>202</v>
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.3047</v>
+        <v>2.4203</v>
       </c>
       <c r="C9" t="n">
-        <v>0.3228</v>
+        <v>0.339</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4249</v>
+        <v>0.4968</v>
       </c>
       <c r="E9" t="n">
-        <v>2.3047</v>
+        <v>2.4203</v>
       </c>
       <c r="F9" t="n">
-        <v>2.5494</v>
+        <v>2.6234</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.2447</v>
+        <v>-0.2031</v>
       </c>
       <c r="H9" t="n">
-        <v>3.5171</v>
+        <v>3.4068</v>
       </c>
       <c r="I9" t="n">
-        <v>1.8992</v>
+        <v>1.9128</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.2447</v>
+        <v>-0.2031</v>
       </c>
       <c r="K9" t="n">
         <v>83</v>
@@ -851,7 +851,7 @@
         <v>119</v>
       </c>
       <c r="M9" t="n">
-        <v>1.6545</v>
+        <v>1.7097</v>
       </c>
       <c r="N9" t="n">
         <v>202</v>
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.2642</v>
+        <v>2.3797</v>
       </c>
       <c r="C10" t="n">
-        <v>0.3171</v>
+        <v>0.3333</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4065</v>
+        <v>0.4783</v>
       </c>
       <c r="E10" t="n">
-        <v>2.2642</v>
+        <v>2.3797</v>
       </c>
       <c r="F10" t="n">
-        <v>2.415</v>
+        <v>2.5049</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.1508</v>
+        <v>-0.1252</v>
       </c>
       <c r="H10" t="n">
-        <v>3.0738</v>
+        <v>2.9619</v>
       </c>
       <c r="I10" t="n">
-        <v>1.6598</v>
+        <v>1.663</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.1508</v>
+        <v>-0.1252</v>
       </c>
       <c r="K10" t="n">
         <v>83</v>
@@ -897,7 +897,7 @@
         <v>119</v>
       </c>
       <c r="M10" t="n">
-        <v>1.509</v>
+        <v>1.5378</v>
       </c>
       <c r="N10" t="n">
         <v>202</v>
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.21</v>
+        <v>2.2429</v>
       </c>
       <c r="C11" t="n">
-        <v>0.3095</v>
+        <v>0.3141</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3818</v>
+        <v>0.416</v>
       </c>
       <c r="E11" t="n">
-        <v>2.21</v>
+        <v>2.2429</v>
       </c>
       <c r="F11" t="n">
-        <v>2.3541</v>
+        <v>2.3884</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.1441</v>
+        <v>-0.1455</v>
       </c>
       <c r="H11" t="n">
-        <v>2.8728</v>
+        <v>2.5246</v>
       </c>
       <c r="I11" t="n">
-        <v>1.5513</v>
+        <v>1.4175</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.1441</v>
+        <v>-0.1455</v>
       </c>
       <c r="K11" t="n">
         <v>164</v>
@@ -943,7 +943,7 @@
         <v>55</v>
       </c>
       <c r="M11" t="n">
-        <v>1.4072</v>
+        <v>1.272</v>
       </c>
       <c r="N11" t="n">
         <v>219</v>
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.1184</v>
+        <v>2.0992</v>
       </c>
       <c r="C12" t="n">
-        <v>0.2967</v>
+        <v>0.294</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3401</v>
+        <v>0.3505</v>
       </c>
       <c r="E12" t="n">
-        <v>2.1184</v>
+        <v>2.0992</v>
       </c>
       <c r="F12" t="n">
-        <v>0.2993</v>
+        <v>0.2552</v>
       </c>
       <c r="G12" t="n">
-        <v>1.8191</v>
+        <v>1.844</v>
       </c>
       <c r="H12" t="n">
-        <v>0.2993</v>
+        <v>0.2552</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1616</v>
+        <v>0.1433</v>
       </c>
       <c r="J12" t="n">
-        <v>1.8191</v>
+        <v>1.844</v>
       </c>
       <c r="K12" t="n">
         <v>171</v>
@@ -989,7 +989,7 @@
         <v>133</v>
       </c>
       <c r="M12" t="n">
-        <v>1.9807</v>
+        <v>1.9873</v>
       </c>
       <c r="N12" t="n">
         <v>304</v>
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.4726</v>
+        <v>1.5385</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2062</v>
+        <v>0.2155</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0462</v>
+        <v>0.0951</v>
       </c>
       <c r="E13" t="n">
-        <v>1.4726</v>
+        <v>1.5385</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4441</v>
+        <v>0.5147</v>
       </c>
       <c r="G13" t="n">
-        <v>1.0285</v>
+        <v>1.0238</v>
       </c>
       <c r="H13" t="n">
-        <v>0.4441</v>
+        <v>0.5147</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2398</v>
+        <v>0.289</v>
       </c>
       <c r="J13" t="n">
-        <v>1.0285</v>
+        <v>1.0238</v>
       </c>
       <c r="K13" t="n">
         <v>171</v>
@@ -1035,7 +1035,7 @@
         <v>133</v>
       </c>
       <c r="M13" t="n">
-        <v>1.2683</v>
+        <v>1.3128</v>
       </c>
       <c r="N13" t="n">
         <v>304</v>
@@ -1048,31 +1048,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.4445</v>
+        <v>1.1515</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2023</v>
+        <v>0.1613</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0334</v>
+        <v>-0.08119999999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>1.4445</v>
+        <v>1.1515</v>
       </c>
       <c r="F14" t="n">
-        <v>1.2663</v>
+        <v>1.0667</v>
       </c>
       <c r="G14" t="n">
-        <v>0.1782</v>
+        <v>0.0848</v>
       </c>
       <c r="H14" t="n">
-        <v>1.2663</v>
+        <v>1.0667</v>
       </c>
       <c r="I14" t="n">
-        <v>0.6838</v>
+        <v>0.5989</v>
       </c>
       <c r="J14" t="n">
-        <v>0.1782</v>
+        <v>0.0848</v>
       </c>
       <c r="K14" t="n">
         <v>76</v>
@@ -1081,7 +1081,7 @@
         <v>69</v>
       </c>
       <c r="M14" t="n">
-        <v>0.862</v>
+        <v>0.6837</v>
       </c>
       <c r="N14" t="n">
         <v>145</v>
@@ -1090,93 +1090,93 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>VINI</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.5337</v>
+        <v>0.5063</v>
       </c>
       <c r="C15" t="n">
-        <v>0.0747</v>
+        <v>0.0709</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.3813</v>
+        <v>-0.3751</v>
       </c>
       <c r="E15" t="n">
-        <v>0.5337</v>
+        <v>0.5063</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.2761</v>
+        <v>0.3713</v>
       </c>
       <c r="G15" t="n">
-        <v>0.8098</v>
+        <v>0.135</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.2761</v>
+        <v>0.3713</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1491</v>
+        <v>0.2085</v>
       </c>
       <c r="J15" t="n">
-        <v>0.8098</v>
+        <v>0.135</v>
       </c>
       <c r="K15" t="n">
-        <v>76</v>
+        <v>164</v>
       </c>
       <c r="L15" t="n">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="M15" t="n">
-        <v>0.6607</v>
+        <v>0.3435</v>
       </c>
       <c r="N15" t="n">
-        <v>145</v>
+        <v>219</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>VINI</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.5072</v>
+        <v>0.3804</v>
       </c>
       <c r="C16" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.0533</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.3933</v>
+        <v>-0.4325</v>
       </c>
       <c r="E16" t="n">
-        <v>0.5072</v>
+        <v>0.3804</v>
       </c>
       <c r="F16" t="n">
-        <v>0.337</v>
+        <v>-0.3156</v>
       </c>
       <c r="G16" t="n">
-        <v>0.1702</v>
+        <v>0.696</v>
       </c>
       <c r="H16" t="n">
-        <v>0.337</v>
+        <v>-0.3156</v>
       </c>
       <c r="I16" t="n">
-        <v>0.182</v>
+        <v>-0.1772</v>
       </c>
       <c r="J16" t="n">
-        <v>0.1702</v>
+        <v>0.696</v>
       </c>
       <c r="K16" t="n">
-        <v>164</v>
+        <v>76</v>
       </c>
       <c r="L16" t="n">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="M16" t="n">
-        <v>0.3522</v>
+        <v>0.5187999999999999</v>
       </c>
       <c r="N16" t="n">
-        <v>219</v>
+        <v>145</v>
       </c>
     </row>
     <row r="17">
@@ -1186,31 +1186,31 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.4319</v>
+        <v>0.3512</v>
       </c>
       <c r="C17" t="n">
-        <v>0.0605</v>
+        <v>0.0492</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.4276</v>
+        <v>-0.4458</v>
       </c>
       <c r="E17" t="n">
-        <v>0.4319</v>
+        <v>0.3512</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1015</v>
+        <v>-0.1614</v>
       </c>
       <c r="G17" t="n">
-        <v>0.5334</v>
+        <v>0.5125999999999999</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.1015</v>
+        <v>-0.1614</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.0548</v>
+        <v>-0.0906</v>
       </c>
       <c r="J17" t="n">
-        <v>0.5334</v>
+        <v>0.5125999999999999</v>
       </c>
       <c r="K17" t="n">
         <v>76</v>
@@ -1219,7 +1219,7 @@
         <v>69</v>
       </c>
       <c r="M17" t="n">
-        <v>0.4786</v>
+        <v>0.4219999999999999</v>
       </c>
       <c r="N17" t="n">
         <v>145</v>
@@ -1228,93 +1228,93 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Stewie2K</t>
+          <t>TACO</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.2358</v>
+        <v>-0.1725</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.033</v>
+        <v>-0.0242</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.7315</v>
+        <v>-0.6844</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.2358</v>
+        <v>-0.1725</v>
       </c>
       <c r="F18" t="n">
-        <v>0.178</v>
+        <v>-0.4524</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.4138</v>
+        <v>0.2799</v>
       </c>
       <c r="H18" t="n">
-        <v>0.178</v>
+        <v>-0.4524</v>
       </c>
       <c r="I18" t="n">
-        <v>0.0961</v>
+        <v>-0.254</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.4138</v>
+        <v>0.2799</v>
       </c>
       <c r="K18" t="n">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="L18" t="n">
-        <v>69</v>
+        <v>119</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.3177</v>
+        <v>0.02589999999999998</v>
       </c>
       <c r="N18" t="n">
-        <v>145</v>
+        <v>202</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>TACO</t>
+          <t>Stewie2K</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.3277</v>
+        <v>-0.3429</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.0459</v>
+        <v>-0.048</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.7734</v>
+        <v>-0.762</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.3277</v>
+        <v>-0.3429</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.5454</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="G19" t="n">
-        <v>0.2177</v>
+        <v>-0.4337</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.5454</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2945</v>
+        <v>0.051</v>
       </c>
       <c r="J19" t="n">
-        <v>0.2177</v>
+        <v>-0.4337</v>
       </c>
       <c r="K19" t="n">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="L19" t="n">
-        <v>119</v>
+        <v>69</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.07679999999999998</v>
+        <v>-0.3827</v>
       </c>
       <c r="N19" t="n">
-        <v>202</v>
+        <v>145</v>
       </c>
     </row>
     <row r="20">
@@ -1324,31 +1324,31 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-1.2719</v>
+        <v>-1.1125</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.1781</v>
+        <v>-0.1558</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.2032</v>
+        <v>-1.1126</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.2719</v>
+        <v>-1.1125</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.9098</v>
+        <v>-1.7221</v>
       </c>
       <c r="G20" t="n">
-        <v>0.6379</v>
+        <v>0.6096</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.9098</v>
+        <v>-1.7221</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.0313</v>
+        <v>-0.9669</v>
       </c>
       <c r="J20" t="n">
-        <v>0.6379</v>
+        <v>0.6096</v>
       </c>
       <c r="K20" t="n">
         <v>171</v>
@@ -1357,7 +1357,7 @@
         <v>133</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.3934000000000001</v>
+        <v>-0.3573</v>
       </c>
       <c r="N20" t="n">
         <v>304</v>
@@ -1370,31 +1370,31 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-1.7709</v>
+        <v>-1.8238</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.248</v>
+        <v>-0.2554</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.4304</v>
+        <v>-1.4366</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.7709</v>
+        <v>-1.8238</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.3709</v>
+        <v>-1.388</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.4</v>
+        <v>-0.4358</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.3709</v>
+        <v>-1.388</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.7403</v>
+        <v>-0.7793</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.4</v>
+        <v>-0.4358</v>
       </c>
       <c r="K21" t="n">
         <v>76</v>
@@ -1403,7 +1403,7 @@
         <v>69</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.1403</v>
+        <v>-1.2151</v>
       </c>
       <c r="N21" t="n">
         <v>145</v>
@@ -1509,10 +1509,10 @@
         <v>1.43</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7947</v>
+        <v>0.7427</v>
       </c>
       <c r="J2" t="n">
-        <v>23.841</v>
+        <v>22.281</v>
       </c>
     </row>
     <row r="3">
@@ -1549,10 +1549,10 @@
         <v>1.11</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2711</v>
+        <v>0.223</v>
       </c>
       <c r="J3" t="n">
-        <v>8.132999999999999</v>
+        <v>6.69</v>
       </c>
     </row>
     <row r="4">
@@ -1589,10 +1589,10 @@
         <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.0001</v>
+        <v>-0</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.003</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="5">
@@ -1629,10 +1629,10 @@
         <v>0.76</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2918</v>
+        <v>-0.2735</v>
       </c>
       <c r="J5" t="n">
-        <v>-8.754</v>
+        <v>-8.205</v>
       </c>
     </row>
     <row r="6">
@@ -1669,10 +1669,10 @@
         <v>0.72</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3295</v>
+        <v>-0.3134</v>
       </c>
       <c r="J6" t="n">
-        <v>-9.885</v>
+        <v>-9.401999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -1709,10 +1709,10 @@
         <v>1.47</v>
       </c>
       <c r="I7" t="n">
-        <v>1.1148</v>
+        <v>1.1207</v>
       </c>
       <c r="J7" t="n">
-        <v>33.444</v>
+        <v>33.621</v>
       </c>
     </row>
     <row r="8">
@@ -1749,10 +1749,10 @@
         <v>1.31</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7965</v>
+        <v>0.7697000000000001</v>
       </c>
       <c r="J8" t="n">
-        <v>23.895</v>
+        <v>23.091</v>
       </c>
     </row>
     <row r="9">
@@ -1789,10 +1789,10 @@
         <v>1.11</v>
       </c>
       <c r="I9" t="n">
-        <v>0.349</v>
+        <v>0.3111</v>
       </c>
       <c r="J9" t="n">
-        <v>10.47</v>
+        <v>9.333</v>
       </c>
     </row>
     <row r="10">
@@ -1829,10 +1829,10 @@
         <v>0.84</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5137</v>
+        <v>-0.4726</v>
       </c>
       <c r="J10" t="n">
-        <v>-15.411</v>
+        <v>-14.178</v>
       </c>
     </row>
     <row r="11">
@@ -1869,10 +1869,10 @@
         <v>0.78</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.6535</v>
+        <v>-0.6191</v>
       </c>
       <c r="J11" t="n">
-        <v>-19.605</v>
+        <v>-18.573</v>
       </c>
     </row>
     <row r="12">
@@ -1909,10 +1909,10 @@
         <v>1.63</v>
       </c>
       <c r="I12" t="n">
-        <v>1.0586</v>
+        <v>1.0242</v>
       </c>
       <c r="J12" t="n">
-        <v>35.9924</v>
+        <v>34.8228</v>
       </c>
     </row>
     <row r="13">
@@ -1949,10 +1949,10 @@
         <v>1.15</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3348</v>
+        <v>0.2828</v>
       </c>
       <c r="J13" t="n">
-        <v>11.3832</v>
+        <v>9.6152</v>
       </c>
     </row>
     <row r="14">
@@ -1989,10 +1989,10 @@
         <v>0.92</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1288</v>
+        <v>-0.1097</v>
       </c>
       <c r="J14" t="n">
-        <v>-4.3792</v>
+        <v>-3.7298</v>
       </c>
     </row>
     <row r="15">
@@ -2029,10 +2029,10 @@
         <v>0.83</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2277</v>
+        <v>-0.2074</v>
       </c>
       <c r="J15" t="n">
-        <v>-7.7418</v>
+        <v>-7.0516</v>
       </c>
     </row>
     <row r="16">
@@ -2069,10 +2069,10 @@
         <v>0.78</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.2775</v>
+        <v>-0.2589</v>
       </c>
       <c r="J16" t="n">
-        <v>-9.435</v>
+        <v>-8.8026</v>
       </c>
     </row>
     <row r="17">
@@ -2109,10 +2109,10 @@
         <v>1.32</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8341</v>
+        <v>0.8105</v>
       </c>
       <c r="J17" t="n">
-        <v>28.3594</v>
+        <v>27.557</v>
       </c>
     </row>
     <row r="18">
@@ -2149,10 +2149,10 @@
         <v>1.1</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3316</v>
+        <v>0.2916</v>
       </c>
       <c r="J18" t="n">
-        <v>11.2744</v>
+        <v>9.914400000000001</v>
       </c>
     </row>
     <row r="19">
@@ -2189,10 +2189,10 @@
         <v>1.03</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1296</v>
+        <v>0.1047</v>
       </c>
       <c r="J19" t="n">
-        <v>4.4064</v>
+        <v>3.5598</v>
       </c>
     </row>
     <row r="20">
@@ -2229,10 +2229,10 @@
         <v>0.97</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1437</v>
+        <v>-0.1137</v>
       </c>
       <c r="J20" t="n">
-        <v>-4.8858</v>
+        <v>-3.8658</v>
       </c>
     </row>
     <row r="21">
@@ -2269,10 +2269,10 @@
         <v>0.82</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.5507</v>
+        <v>-0.5102</v>
       </c>
       <c r="J21" t="n">
-        <v>-18.7238</v>
+        <v>-17.3468</v>
       </c>
     </row>
     <row r="22">
@@ -2309,10 +2309,10 @@
         <v>1.42</v>
       </c>
       <c r="I22" t="n">
-        <v>0.5576</v>
+        <v>0.4875</v>
       </c>
       <c r="J22" t="n">
-        <v>16.728</v>
+        <v>14.625</v>
       </c>
     </row>
     <row r="23">
@@ -2349,10 +2349,10 @@
         <v>1.29</v>
       </c>
       <c r="I23" t="n">
-        <v>0.4136</v>
+        <v>0.3494</v>
       </c>
       <c r="J23" t="n">
-        <v>12.408</v>
+        <v>10.482</v>
       </c>
     </row>
     <row r="24">
@@ -2389,10 +2389,10 @@
         <v>1.02</v>
       </c>
       <c r="I24" t="n">
-        <v>0.0462</v>
+        <v>0.0321</v>
       </c>
       <c r="J24" t="n">
-        <v>1.386</v>
+        <v>0.963</v>
       </c>
     </row>
     <row r="25">
@@ -2429,10 +2429,10 @@
         <v>0.9</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.1559</v>
+        <v>-0.1359</v>
       </c>
       <c r="J25" t="n">
-        <v>-4.677</v>
+        <v>-4.077</v>
       </c>
     </row>
     <row r="26">
@@ -2469,10 +2469,10 @@
         <v>0.9</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.1559</v>
+        <v>-0.1359</v>
       </c>
       <c r="J26" t="n">
-        <v>-4.677</v>
+        <v>-4.077</v>
       </c>
     </row>
     <row r="27">
@@ -2509,10 +2509,10 @@
         <v>1.48</v>
       </c>
       <c r="I27" t="n">
-        <v>0.6771</v>
+        <v>0.7179</v>
       </c>
       <c r="J27" t="n">
-        <v>20.313</v>
+        <v>21.537</v>
       </c>
     </row>
     <row r="28">
@@ -2549,10 +2549,10 @@
         <v>1.02</v>
       </c>
       <c r="I28" t="n">
-        <v>0.0564</v>
+        <v>0.0456</v>
       </c>
       <c r="J28" t="n">
-        <v>1.692</v>
+        <v>1.368</v>
       </c>
     </row>
     <row r="29">
@@ -2589,10 +2589,10 @@
         <v>0.89</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.1594</v>
+        <v>-0.1393</v>
       </c>
       <c r="J29" t="n">
-        <v>-4.782</v>
+        <v>-4.179</v>
       </c>
     </row>
     <row r="30">
@@ -2629,10 +2629,10 @@
         <v>0.87</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.1814</v>
+        <v>-0.1609</v>
       </c>
       <c r="J30" t="n">
-        <v>-5.442</v>
+        <v>-4.827</v>
       </c>
     </row>
     <row r="31">
@@ -2669,10 +2669,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.2437</v>
+        <v>-0.2236</v>
       </c>
       <c r="J31" t="n">
-        <v>-7.311</v>
+        <v>-6.708</v>
       </c>
     </row>
     <row r="32">
@@ -2709,10 +2709,10 @@
         <v>1.19</v>
       </c>
       <c r="I32" t="n">
-        <v>0.4189</v>
+        <v>0.3619</v>
       </c>
       <c r="J32" t="n">
-        <v>12.567</v>
+        <v>10.857</v>
       </c>
     </row>
     <row r="33">
@@ -2749,10 +2749,10 @@
         <v>1.09</v>
       </c>
       <c r="I33" t="n">
-        <v>0.2345</v>
+        <v>0.1896</v>
       </c>
       <c r="J33" t="n">
-        <v>7.035</v>
+        <v>5.688</v>
       </c>
     </row>
     <row r="34">
@@ -2789,10 +2789,10 @@
         <v>1.04</v>
       </c>
       <c r="I34" t="n">
-        <v>0.126</v>
+        <v>0.0951</v>
       </c>
       <c r="J34" t="n">
-        <v>3.78</v>
+        <v>2.853</v>
       </c>
     </row>
     <row r="35">
@@ -2829,10 +2829,10 @@
         <v>0.89</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.1574</v>
+        <v>-0.1374</v>
       </c>
       <c r="J35" t="n">
-        <v>-4.722</v>
+        <v>-4.122</v>
       </c>
     </row>
     <row r="36">
@@ -2869,10 +2869,10 @@
         <v>0.74</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.3095</v>
+        <v>-0.2921</v>
       </c>
       <c r="J36" t="n">
-        <v>-9.285</v>
+        <v>-8.763</v>
       </c>
     </row>
     <row r="37">
@@ -2909,10 +2909,10 @@
         <v>1.19</v>
       </c>
       <c r="I37" t="n">
-        <v>0.5527</v>
+        <v>0.5122</v>
       </c>
       <c r="J37" t="n">
-        <v>16.581</v>
+        <v>15.366</v>
       </c>
     </row>
     <row r="38">
@@ -2949,10 +2949,10 @@
         <v>1.12</v>
       </c>
       <c r="I38" t="n">
-        <v>0.3845</v>
+        <v>0.3428</v>
       </c>
       <c r="J38" t="n">
-        <v>11.535</v>
+        <v>10.284</v>
       </c>
     </row>
     <row r="39">
@@ -2989,10 +2989,10 @@
         <v>0.99</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.0648</v>
+        <v>-0.0465</v>
       </c>
       <c r="J39" t="n">
-        <v>-1.944</v>
+        <v>-1.395</v>
       </c>
     </row>
     <row r="40">
@@ -3029,10 +3029,10 @@
         <v>0.96</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.1759</v>
+        <v>-0.1427</v>
       </c>
       <c r="J40" t="n">
-        <v>-5.277</v>
+        <v>-4.281</v>
       </c>
     </row>
     <row r="41">
@@ -3069,10 +3069,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.2379</v>
+        <v>-0.1999</v>
       </c>
       <c r="J41" t="n">
-        <v>-7.137</v>
+        <v>-5.997</v>
       </c>
     </row>
     <row r="42">
@@ -3109,10 +3109,10 @@
         <v>1.23</v>
       </c>
       <c r="I42" t="n">
-        <v>0.4727</v>
+        <v>0.4141</v>
       </c>
       <c r="J42" t="n">
-        <v>13.2356</v>
+        <v>11.5948</v>
       </c>
     </row>
     <row r="43">
@@ -3149,10 +3149,10 @@
         <v>1.08</v>
       </c>
       <c r="I43" t="n">
-        <v>0.2053</v>
+        <v>0.1651</v>
       </c>
       <c r="J43" t="n">
-        <v>5.7484</v>
+        <v>4.6228</v>
       </c>
     </row>
     <row r="44">
@@ -3189,10 +3189,10 @@
         <v>1.03</v>
       </c>
       <c r="I44" t="n">
-        <v>0.0955</v>
+        <v>0.0717</v>
       </c>
       <c r="J44" t="n">
-        <v>2.674</v>
+        <v>2.0076</v>
       </c>
     </row>
     <row r="45">
@@ -3229,10 +3229,10 @@
         <v>1.02</v>
       </c>
       <c r="I45" t="n">
-        <v>0.0689</v>
+        <v>0.0504</v>
       </c>
       <c r="J45" t="n">
-        <v>1.9292</v>
+        <v>1.4112</v>
       </c>
     </row>
     <row r="46">
@@ -3269,10 +3269,10 @@
         <v>0.89</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.1626</v>
+        <v>-0.1423</v>
       </c>
       <c r="J46" t="n">
-        <v>-4.5528</v>
+        <v>-3.9844</v>
       </c>
     </row>
     <row r="47">
@@ -3309,10 +3309,10 @@
         <v>1.3</v>
       </c>
       <c r="I47" t="n">
-        <v>0.7921</v>
+        <v>0.765</v>
       </c>
       <c r="J47" t="n">
-        <v>22.1788</v>
+        <v>21.42</v>
       </c>
     </row>
     <row r="48">
@@ -3349,10 +3349,10 @@
         <v>1.18</v>
       </c>
       <c r="I48" t="n">
-        <v>0.5274</v>
+        <v>0.4865</v>
       </c>
       <c r="J48" t="n">
-        <v>14.7672</v>
+        <v>13.622</v>
       </c>
     </row>
     <row r="49">
@@ -3389,10 +3389,10 @@
         <v>1.07</v>
       </c>
       <c r="I49" t="n">
-        <v>0.2507</v>
+        <v>0.2147</v>
       </c>
       <c r="J49" t="n">
-        <v>7.0196</v>
+        <v>6.0116</v>
       </c>
     </row>
     <row r="50">
@@ -3429,10 +3429,10 @@
         <v>0.91</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.3246</v>
+        <v>-0.2827</v>
       </c>
       <c r="J50" t="n">
-        <v>-9.088800000000001</v>
+        <v>-7.9156</v>
       </c>
     </row>
     <row r="51">
@@ -3469,10 +3469,10 @@
         <v>0.78</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.6431</v>
+        <v>-0.607</v>
       </c>
       <c r="J51" t="n">
-        <v>-18.0068</v>
+        <v>-16.996</v>
       </c>
     </row>
     <row r="52">
@@ -3509,10 +3509,10 @@
         <v>1.01</v>
       </c>
       <c r="I52" t="n">
-        <v>0.0407</v>
+        <v>0.0307</v>
       </c>
       <c r="J52" t="n">
-        <v>1.1396</v>
+        <v>0.8596</v>
       </c>
     </row>
     <row r="53">
@@ -3549,10 +3549,10 @@
         <v>0.97</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.0545</v>
+        <v>-0.0437</v>
       </c>
       <c r="J53" t="n">
-        <v>-1.526</v>
+        <v>-1.2236</v>
       </c>
     </row>
     <row r="54">
@@ -3589,10 +3589,10 @@
         <v>0.92</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.1188</v>
+        <v>-0.1017</v>
       </c>
       <c r="J54" t="n">
-        <v>-3.3264</v>
+        <v>-2.8476</v>
       </c>
     </row>
     <row r="55">
@@ -3629,10 +3629,10 @@
         <v>0.9</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.1418</v>
+        <v>-0.1232</v>
       </c>
       <c r="J55" t="n">
-        <v>-3.9704</v>
+        <v>-3.4496</v>
       </c>
     </row>
     <row r="56">
@@ -3669,10 +3669,10 @@
         <v>0.89</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.1529</v>
+        <v>-0.1339</v>
       </c>
       <c r="J56" t="n">
-        <v>-4.2812</v>
+        <v>-3.7492</v>
       </c>
     </row>
     <row r="57">
@@ -3709,10 +3709,10 @@
         <v>1.5</v>
       </c>
       <c r="I57" t="n">
-        <v>0.6236</v>
+        <v>0.5518999999999999</v>
       </c>
       <c r="J57" t="n">
-        <v>17.4608</v>
+        <v>15.4532</v>
       </c>
     </row>
     <row r="58">
@@ -3749,10 +3749,10 @@
         <v>1.37</v>
       </c>
       <c r="I58" t="n">
-        <v>0.4882</v>
+        <v>0.4209</v>
       </c>
       <c r="J58" t="n">
-        <v>13.6696</v>
+        <v>11.7852</v>
       </c>
     </row>
     <row r="59">
@@ -3789,10 +3789,10 @@
         <v>1.31</v>
       </c>
       <c r="I59" t="n">
-        <v>0.4231</v>
+        <v>0.3598</v>
       </c>
       <c r="J59" t="n">
-        <v>11.8468</v>
+        <v>10.0744</v>
       </c>
     </row>
     <row r="60">
@@ -3829,10 +3829,10 @@
         <v>0.98</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.0587</v>
+        <v>-0.0465</v>
       </c>
       <c r="J60" t="n">
-        <v>-1.6436</v>
+        <v>-1.302</v>
       </c>
     </row>
     <row r="61">
@@ -3869,10 +3869,10 @@
         <v>0.89</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.1754</v>
+        <v>-0.1559</v>
       </c>
       <c r="J61" t="n">
-        <v>-4.9112</v>
+        <v>-4.3652</v>
       </c>
     </row>
     <row r="62">
@@ -3909,10 +3909,10 @@
         <v>1.81</v>
       </c>
       <c r="I62" t="n">
-        <v>1.445</v>
+        <v>1.4732</v>
       </c>
       <c r="J62" t="n">
-        <v>28.9</v>
+        <v>29.464</v>
       </c>
     </row>
     <row r="63">
@@ -3949,10 +3949,10 @@
         <v>1.62</v>
       </c>
       <c r="I63" t="n">
-        <v>1.2133</v>
+        <v>1.2324</v>
       </c>
       <c r="J63" t="n">
-        <v>24.266</v>
+        <v>24.648</v>
       </c>
     </row>
     <row r="64">
@@ -3989,10 +3989,10 @@
         <v>1.57</v>
       </c>
       <c r="I64" t="n">
-        <v>1.1509</v>
+        <v>1.169</v>
       </c>
       <c r="J64" t="n">
-        <v>23.018</v>
+        <v>23.38</v>
       </c>
     </row>
     <row r="65">
@@ -4029,10 +4029,10 @@
         <v>1.52</v>
       </c>
       <c r="I65" t="n">
-        <v>1.088</v>
+        <v>1.1051</v>
       </c>
       <c r="J65" t="n">
-        <v>21.76</v>
+        <v>22.102</v>
       </c>
     </row>
     <row r="66">
@@ -4069,10 +4069,10 @@
         <v>0.97</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.2175</v>
+        <v>-0.1931</v>
       </c>
       <c r="J66" t="n">
-        <v>-4.35</v>
+        <v>-3.862</v>
       </c>
     </row>
     <row r="67">
@@ -4109,10 +4109,10 @@
         <v>0.88</v>
       </c>
       <c r="I67" t="n">
-        <v>-0.1248</v>
+        <v>-0.1071</v>
       </c>
       <c r="J67" t="n">
-        <v>-2.496</v>
+        <v>-2.142</v>
       </c>
     </row>
     <row r="68">
@@ -4149,10 +4149,10 @@
         <v>0.85</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.1597</v>
+        <v>-0.1429</v>
       </c>
       <c r="J68" t="n">
-        <v>-3.194</v>
+        <v>-2.858</v>
       </c>
     </row>
     <row r="69">
@@ -4189,10 +4189,10 @@
         <v>0.59</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.4092</v>
+        <v>-0.3997</v>
       </c>
       <c r="J69" t="n">
-        <v>-8.183999999999999</v>
+        <v>-7.994</v>
       </c>
     </row>
     <row r="70">
@@ -4229,10 +4229,10 @@
         <v>0.49</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.4973</v>
+        <v>-0.4951</v>
       </c>
       <c r="J70" t="n">
-        <v>-9.946</v>
+        <v>-9.901999999999999</v>
       </c>
     </row>
     <row r="71">
@@ -4269,10 +4269,10 @@
         <v>0.48</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.506</v>
+        <v>-0.5048</v>
       </c>
       <c r="J71" t="n">
-        <v>-10.12</v>
+        <v>-10.096</v>
       </c>
     </row>
     <row r="72">
@@ -4309,10 +4309,10 @@
         <v>1.33</v>
       </c>
       <c r="I72" t="n">
-        <v>0.8277</v>
+        <v>0.8036</v>
       </c>
       <c r="J72" t="n">
-        <v>28.9695</v>
+        <v>28.126</v>
       </c>
     </row>
     <row r="73">
@@ -4349,10 +4349,10 @@
         <v>1.33</v>
       </c>
       <c r="I73" t="n">
-        <v>0.8277</v>
+        <v>0.8036</v>
       </c>
       <c r="J73" t="n">
-        <v>28.9695</v>
+        <v>28.126</v>
       </c>
     </row>
     <row r="74">
@@ -4389,10 +4389,10 @@
         <v>1.25</v>
       </c>
       <c r="I74" t="n">
-        <v>0.6618000000000001</v>
+        <v>0.6279</v>
       </c>
       <c r="J74" t="n">
-        <v>23.163</v>
+        <v>21.9765</v>
       </c>
     </row>
     <row r="75">
@@ -4429,10 +4429,10 @@
         <v>1</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.0225</v>
+        <v>-0.0172</v>
       </c>
       <c r="J75" t="n">
-        <v>-0.7875</v>
+        <v>-0.602</v>
       </c>
     </row>
     <row r="76">
@@ -4469,10 +4469,10 @@
         <v>0.78</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.6601</v>
+        <v>-0.6269</v>
       </c>
       <c r="J76" t="n">
-        <v>-23.1035</v>
+        <v>-21.9415</v>
       </c>
     </row>
     <row r="77">
@@ -4509,10 +4509,10 @@
         <v>1.37</v>
       </c>
       <c r="I77" t="n">
-        <v>0.7046</v>
+        <v>0.6484</v>
       </c>
       <c r="J77" t="n">
-        <v>24.661</v>
+        <v>22.694</v>
       </c>
     </row>
     <row r="78">
@@ -4549,10 +4549,10 @@
         <v>1.08</v>
       </c>
       <c r="I78" t="n">
-        <v>0.2118</v>
+        <v>0.1695</v>
       </c>
       <c r="J78" t="n">
-        <v>7.413</v>
+        <v>5.9325</v>
       </c>
     </row>
     <row r="79">
@@ -4589,10 +4589,10 @@
         <v>0.97</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.0585</v>
+        <v>-0.0458</v>
       </c>
       <c r="J79" t="n">
-        <v>-2.0475</v>
+        <v>-1.603</v>
       </c>
     </row>
     <row r="80">
@@ -4629,10 +4629,10 @@
         <v>0.85</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.2018</v>
+        <v>-0.1812</v>
       </c>
       <c r="J80" t="n">
-        <v>-7.063</v>
+        <v>-6.342</v>
       </c>
     </row>
     <row r="81">
@@ -4669,10 +4669,10 @@
         <v>0.75</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.3013</v>
+        <v>-0.2835</v>
       </c>
       <c r="J81" t="n">
-        <v>-10.5455</v>
+        <v>-9.922499999999999</v>
       </c>
     </row>
     <row r="82">
@@ -4709,10 +4709,10 @@
         <v>1.72</v>
       </c>
       <c r="I82" t="n">
-        <v>1.3653</v>
+        <v>1.3881</v>
       </c>
       <c r="J82" t="n">
-        <v>35.4978</v>
+        <v>36.0906</v>
       </c>
     </row>
     <row r="83">
@@ -4749,10 +4749,10 @@
         <v>1.41</v>
       </c>
       <c r="I83" t="n">
-        <v>0.9421</v>
+        <v>0.9343</v>
       </c>
       <c r="J83" t="n">
-        <v>24.4946</v>
+        <v>24.2918</v>
       </c>
     </row>
     <row r="84">
@@ -4789,10 +4789,10 @@
         <v>1.22</v>
       </c>
       <c r="I84" t="n">
-        <v>0.5717</v>
+        <v>0.5436</v>
       </c>
       <c r="J84" t="n">
-        <v>14.8642</v>
+        <v>14.1336</v>
       </c>
     </row>
     <row r="85">
@@ -4829,10 +4829,10 @@
         <v>1.19</v>
       </c>
       <c r="I85" t="n">
-        <v>0.5058</v>
+        <v>0.4759</v>
       </c>
       <c r="J85" t="n">
-        <v>13.1508</v>
+        <v>12.3734</v>
       </c>
     </row>
     <row r="86">
@@ -4869,10 +4869,10 @@
         <v>1.11</v>
       </c>
       <c r="I86" t="n">
-        <v>0.3151</v>
+        <v>0.2832</v>
       </c>
       <c r="J86" t="n">
-        <v>8.192600000000001</v>
+        <v>7.3632</v>
       </c>
     </row>
     <row r="87">
@@ -4909,10 +4909,10 @@
         <v>1.02</v>
       </c>
       <c r="I87" t="n">
-        <v>0.1216</v>
+        <v>0.09660000000000001</v>
       </c>
       <c r="J87" t="n">
-        <v>3.1616</v>
+        <v>2.5116</v>
       </c>
     </row>
     <row r="88">
@@ -4949,10 +4949,10 @@
         <v>1.01</v>
       </c>
       <c r="I88" t="n">
-        <v>0.0898</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="J88" t="n">
-        <v>2.3348</v>
+        <v>1.846</v>
       </c>
     </row>
     <row r="89">
@@ -4989,10 +4989,10 @@
         <v>0.88</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.1508</v>
+        <v>-0.1352</v>
       </c>
       <c r="J89" t="n">
-        <v>-3.9208</v>
+        <v>-3.5152</v>
       </c>
     </row>
     <row r="90">
@@ -5029,10 +5029,10 @@
         <v>0.7</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.3265</v>
+        <v>-0.3105</v>
       </c>
       <c r="J90" t="n">
-        <v>-8.489000000000001</v>
+        <v>-8.073</v>
       </c>
     </row>
     <row r="91">
@@ -5069,10 +5069,10 @@
         <v>0.34</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.6409</v>
+        <v>-0.6624</v>
       </c>
       <c r="J91" t="n">
-        <v>-16.6634</v>
+        <v>-17.2224</v>
       </c>
     </row>
     <row r="92">
@@ -5109,10 +5109,10 @@
         <v>1.14</v>
       </c>
       <c r="I92" t="n">
-        <v>0.288</v>
+        <v>0.2781</v>
       </c>
       <c r="J92" t="n">
-        <v>7.488</v>
+        <v>7.2306</v>
       </c>
     </row>
     <row r="93">
@@ -5149,10 +5149,10 @@
         <v>1</v>
       </c>
       <c r="I93" t="n">
-        <v>0.02</v>
+        <v>0.0176</v>
       </c>
       <c r="J93" t="n">
-        <v>0.52</v>
+        <v>0.4576</v>
       </c>
     </row>
     <row r="94">
@@ -5189,10 +5189,10 @@
         <v>0.74</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.2961</v>
+        <v>-0.2782</v>
       </c>
       <c r="J94" t="n">
-        <v>-7.6986</v>
+        <v>-7.2332</v>
       </c>
     </row>
     <row r="95">
@@ -5229,10 +5229,10 @@
         <v>0.74</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.2961</v>
+        <v>-0.2782</v>
       </c>
       <c r="J95" t="n">
-        <v>-7.6986</v>
+        <v>-7.2332</v>
       </c>
     </row>
     <row r="96">
@@ -5269,10 +5269,10 @@
         <v>0.65</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.3791</v>
+        <v>-0.3659</v>
       </c>
       <c r="J96" t="n">
-        <v>-9.8566</v>
+        <v>-9.513400000000001</v>
       </c>
     </row>
     <row r="97">
@@ -5309,10 +5309,10 @@
         <v>1.5</v>
       </c>
       <c r="I97" t="n">
-        <v>0.6121</v>
+        <v>0.5413</v>
       </c>
       <c r="J97" t="n">
-        <v>15.9146</v>
+        <v>14.0738</v>
       </c>
     </row>
     <row r="98">
@@ -5349,10 +5349,10 @@
         <v>1.44</v>
       </c>
       <c r="I98" t="n">
-        <v>0.5517</v>
+        <v>0.4828</v>
       </c>
       <c r="J98" t="n">
-        <v>14.3442</v>
+        <v>12.5528</v>
       </c>
     </row>
     <row r="99">
@@ -5389,10 +5389,10 @@
         <v>1.27</v>
       </c>
       <c r="I99" t="n">
-        <v>0.3735</v>
+        <v>0.3162</v>
       </c>
       <c r="J99" t="n">
-        <v>9.711</v>
+        <v>8.2212</v>
       </c>
     </row>
     <row r="100">
@@ -5429,10 +5429,10 @@
         <v>1.15</v>
       </c>
       <c r="I100" t="n">
-        <v>0.2302</v>
+        <v>0.187</v>
       </c>
       <c r="J100" t="n">
-        <v>5.9852</v>
+        <v>4.862</v>
       </c>
     </row>
     <row r="101">
@@ -5469,10 +5469,10 @@
         <v>1.1</v>
       </c>
       <c r="I101" t="n">
-        <v>0.162</v>
+        <v>0.1273</v>
       </c>
       <c r="J101" t="n">
-        <v>4.212</v>
+        <v>3.3098</v>
       </c>
     </row>
     <row r="102">
@@ -5509,10 +5509,10 @@
         <v>1.62</v>
       </c>
       <c r="I102" t="n">
-        <v>1.2327</v>
+        <v>1.2493</v>
       </c>
       <c r="J102" t="n">
-        <v>29.5848</v>
+        <v>29.9832</v>
       </c>
     </row>
     <row r="103">
@@ -5549,10 +5549,10 @@
         <v>1.49</v>
       </c>
       <c r="I103" t="n">
-        <v>1.0628</v>
+        <v>1.073</v>
       </c>
       <c r="J103" t="n">
-        <v>25.5072</v>
+        <v>25.752</v>
       </c>
     </row>
     <row r="104">
@@ -5589,10 +5589,10 @@
         <v>1.33</v>
       </c>
       <c r="I104" t="n">
-        <v>0.791</v>
+        <v>0.7738</v>
       </c>
       <c r="J104" t="n">
-        <v>18.984</v>
+        <v>18.5712</v>
       </c>
     </row>
     <row r="105">
@@ -5629,10 +5629,10 @@
         <v>1.24</v>
       </c>
       <c r="I105" t="n">
-        <v>0.61</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="J105" t="n">
-        <v>14.64</v>
+        <v>14.0208</v>
       </c>
     </row>
     <row r="106">
@@ -5669,10 +5669,10 @@
         <v>1.12</v>
       </c>
       <c r="I106" t="n">
-        <v>0.3357</v>
+        <v>0.3037</v>
       </c>
       <c r="J106" t="n">
-        <v>8.056800000000001</v>
+        <v>7.2888</v>
       </c>
     </row>
     <row r="107">
@@ -5709,10 +5709,10 @@
         <v>0.96</v>
       </c>
       <c r="I107" t="n">
-        <v>-0.0499</v>
+        <v>-0.039</v>
       </c>
       <c r="J107" t="n">
-        <v>-1.1976</v>
+        <v>-0.9360000000000001</v>
       </c>
     </row>
     <row r="108">
@@ -5749,10 +5749,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I108" t="n">
-        <v>-0.2239</v>
+        <v>-0.207</v>
       </c>
       <c r="J108" t="n">
-        <v>-5.3736</v>
+        <v>-4.968</v>
       </c>
     </row>
     <row r="109">
@@ -5789,10 +5789,10 @@
         <v>0.77</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.2614</v>
+        <v>-0.2442</v>
       </c>
       <c r="J109" t="n">
-        <v>-6.2736</v>
+        <v>-5.8608</v>
       </c>
     </row>
     <row r="110">
@@ -5829,10 +5829,10 @@
         <v>0.75</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.28</v>
+        <v>-0.2629</v>
       </c>
       <c r="J110" t="n">
-        <v>-6.72</v>
+        <v>-6.3096</v>
       </c>
     </row>
     <row r="111">
@@ -5869,10 +5869,10 @@
         <v>0.65</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.3718</v>
+        <v>-0.3582</v>
       </c>
       <c r="J111" t="n">
-        <v>-8.9232</v>
+        <v>-8.5968</v>
       </c>
     </row>
     <row r="112">
@@ -5909,10 +5909,10 @@
         <v>1.89</v>
       </c>
       <c r="I112" t="n">
-        <v>0.8243</v>
+        <v>0.771</v>
       </c>
       <c r="J112" t="n">
-        <v>18.9589</v>
+        <v>17.733</v>
       </c>
     </row>
     <row r="113">
@@ -5949,10 +5949,10 @@
         <v>1.56</v>
       </c>
       <c r="I113" t="n">
-        <v>0.6002</v>
+        <v>0.5642</v>
       </c>
       <c r="J113" t="n">
-        <v>13.8046</v>
+        <v>12.9766</v>
       </c>
     </row>
     <row r="114">
@@ -5989,10 +5989,10 @@
         <v>1.25</v>
       </c>
       <c r="I114" t="n">
-        <v>0.3418</v>
+        <v>0.289</v>
       </c>
       <c r="J114" t="n">
-        <v>7.8614</v>
+        <v>6.647</v>
       </c>
     </row>
     <row r="115">
@@ -6029,10 +6029,10 @@
         <v>1.21</v>
       </c>
       <c r="I115" t="n">
-        <v>0.2947</v>
+        <v>0.2459</v>
       </c>
       <c r="J115" t="n">
-        <v>6.7781</v>
+        <v>5.6557</v>
       </c>
     </row>
     <row r="116">
@@ -6069,10 +6069,10 @@
         <v>1.17</v>
       </c>
       <c r="I116" t="n">
-        <v>0.2454</v>
+        <v>0.2011</v>
       </c>
       <c r="J116" t="n">
-        <v>5.6442</v>
+        <v>4.6253</v>
       </c>
     </row>
     <row r="117">
@@ -6109,10 +6109,10 @@
         <v>0.95</v>
       </c>
       <c r="I117" t="n">
-        <v>-0.0552</v>
+        <v>-0.0423</v>
       </c>
       <c r="J117" t="n">
-        <v>-1.2696</v>
+        <v>-0.9729</v>
       </c>
     </row>
     <row r="118">
@@ -6149,10 +6149,10 @@
         <v>0.77</v>
       </c>
       <c r="I118" t="n">
-        <v>-0.2579</v>
+        <v>-0.2423</v>
       </c>
       <c r="J118" t="n">
-        <v>-5.9317</v>
+        <v>-5.5729</v>
       </c>
     </row>
     <row r="119">
@@ -6189,10 +6189,10 @@
         <v>0.71</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.3122</v>
+        <v>-0.2969</v>
       </c>
       <c r="J119" t="n">
-        <v>-7.1806</v>
+        <v>-6.8287</v>
       </c>
     </row>
     <row r="120">
@@ -6229,10 +6229,10 @@
         <v>0.7</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.3212</v>
+        <v>-0.3061</v>
       </c>
       <c r="J120" t="n">
-        <v>-7.3876</v>
+        <v>-7.0403</v>
       </c>
     </row>
     <row r="121">
@@ -6269,10 +6269,10 @@
         <v>0.58</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.4288</v>
+        <v>-0.4198</v>
       </c>
       <c r="J121" t="n">
-        <v>-9.862399999999999</v>
+        <v>-9.6554</v>
       </c>
     </row>
     <row r="122">
@@ -6309,10 +6309,10 @@
         <v>1.1</v>
       </c>
       <c r="I122" t="n">
-        <v>0.292</v>
+        <v>0.2449</v>
       </c>
       <c r="J122" t="n">
-        <v>7.008</v>
+        <v>5.8776</v>
       </c>
     </row>
     <row r="123">
@@ -6349,10 +6349,10 @@
         <v>1.03</v>
       </c>
       <c r="I123" t="n">
-        <v>0.1323</v>
+        <v>0.1018</v>
       </c>
       <c r="J123" t="n">
-        <v>3.1752</v>
+        <v>2.4432</v>
       </c>
     </row>
     <row r="124">
@@ -6389,10 +6389,10 @@
         <v>0.83</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.2082</v>
+        <v>-0.1898</v>
       </c>
       <c r="J124" t="n">
-        <v>-4.9968</v>
+        <v>-4.5552</v>
       </c>
     </row>
     <row r="125">
@@ -6429,10 +6429,10 @@
         <v>0.67</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.3599</v>
+        <v>-0.3453</v>
       </c>
       <c r="J125" t="n">
-        <v>-8.637600000000001</v>
+        <v>-8.2872</v>
       </c>
     </row>
     <row r="126">
@@ -6469,10 +6469,10 @@
         <v>0.59</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.4316</v>
+        <v>-0.4231</v>
       </c>
       <c r="J126" t="n">
-        <v>-10.3584</v>
+        <v>-10.1544</v>
       </c>
     </row>
     <row r="127">
@@ -6509,10 +6509,10 @@
         <v>1.6</v>
       </c>
       <c r="I127" t="n">
-        <v>1.0645</v>
+        <v>1.0545</v>
       </c>
       <c r="J127" t="n">
-        <v>25.548</v>
+        <v>25.308</v>
       </c>
     </row>
     <row r="128">
@@ -6549,10 +6549,10 @@
         <v>1.43</v>
       </c>
       <c r="I128" t="n">
-        <v>0.8388</v>
+        <v>0.8260999999999999</v>
       </c>
       <c r="J128" t="n">
-        <v>20.1312</v>
+        <v>19.8264</v>
       </c>
     </row>
     <row r="129">
@@ -6589,10 +6589,10 @@
         <v>1.26</v>
       </c>
       <c r="I129" t="n">
-        <v>0.599</v>
+        <v>0.5937</v>
       </c>
       <c r="J129" t="n">
-        <v>14.376</v>
+        <v>14.2488</v>
       </c>
     </row>
     <row r="130">
@@ -6629,10 +6629,10 @@
         <v>1.21</v>
       </c>
       <c r="I130" t="n">
-        <v>0.5207000000000001</v>
+        <v>0.5161</v>
       </c>
       <c r="J130" t="n">
-        <v>12.4968</v>
+        <v>12.3864</v>
       </c>
     </row>
     <row r="131">
@@ -6669,10 +6669,10 @@
         <v>1.16</v>
       </c>
       <c r="I131" t="n">
-        <v>0.4343</v>
+        <v>0.4056</v>
       </c>
       <c r="J131" t="n">
-        <v>10.4232</v>
+        <v>9.734400000000001</v>
       </c>
     </row>
     <row r="132">
@@ -6709,10 +6709,10 @@
         <v>1.15</v>
       </c>
       <c r="I132" t="n">
-        <v>0.4321</v>
+        <v>0.3931</v>
       </c>
       <c r="J132" t="n">
-        <v>9.5062</v>
+        <v>8.648199999999999</v>
       </c>
     </row>
     <row r="133">
@@ -6749,10 +6749,10 @@
         <v>0.93</v>
       </c>
       <c r="I133" t="n">
-        <v>-0.0827</v>
+        <v>-0.06859999999999999</v>
       </c>
       <c r="J133" t="n">
-        <v>-1.8194</v>
+        <v>-1.5092</v>
       </c>
     </row>
     <row r="134">
@@ -6789,10 +6789,10 @@
         <v>0.67</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.3486</v>
+        <v>-0.3343</v>
       </c>
       <c r="J134" t="n">
-        <v>-7.6692</v>
+        <v>-7.3546</v>
       </c>
     </row>
     <row r="135">
@@ -6829,10 +6829,10 @@
         <v>0.55</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.4556</v>
+        <v>-0.4491</v>
       </c>
       <c r="J135" t="n">
-        <v>-10.0232</v>
+        <v>-9.8802</v>
       </c>
     </row>
     <row r="136">
@@ -6869,10 +6869,10 @@
         <v>0.42</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.5686</v>
+        <v>-0.5769</v>
       </c>
       <c r="J136" t="n">
-        <v>-12.5092</v>
+        <v>-12.6918</v>
       </c>
     </row>
     <row r="137">
@@ -6909,10 +6909,10 @@
         <v>1.62</v>
       </c>
       <c r="I137" t="n">
-        <v>1.0786</v>
+        <v>1.0702</v>
       </c>
       <c r="J137" t="n">
-        <v>23.7292</v>
+        <v>23.5444</v>
       </c>
     </row>
     <row r="138">
@@ -6949,10 +6949,10 @@
         <v>1.59</v>
       </c>
       <c r="I138" t="n">
-        <v>1.0404</v>
+        <v>1.0309</v>
       </c>
       <c r="J138" t="n">
-        <v>22.8888</v>
+        <v>22.6798</v>
       </c>
     </row>
     <row r="139">
@@ -6989,10 +6989,10 @@
         <v>1.48</v>
       </c>
       <c r="I139" t="n">
-        <v>0.8977000000000001</v>
+        <v>0.8868</v>
       </c>
       <c r="J139" t="n">
-        <v>19.7494</v>
+        <v>19.5096</v>
       </c>
     </row>
     <row r="140">
@@ -7029,10 +7029,10 @@
         <v>1.24</v>
       </c>
       <c r="I140" t="n">
-        <v>0.5608</v>
+        <v>0.5585</v>
       </c>
       <c r="J140" t="n">
-        <v>12.3376</v>
+        <v>12.287</v>
       </c>
     </row>
     <row r="141">
@@ -7069,10 +7069,10 @@
         <v>1.08</v>
       </c>
       <c r="I141" t="n">
-        <v>0.2241</v>
+        <v>0.193</v>
       </c>
       <c r="J141" t="n">
-        <v>4.9302</v>
+        <v>4.246</v>
       </c>
     </row>
     <row r="142">
@@ -7109,10 +7109,10 @@
         <v>1.22</v>
       </c>
       <c r="I142" t="n">
-        <v>0.4453</v>
+        <v>0.3922</v>
       </c>
       <c r="J142" t="n">
-        <v>13.359</v>
+        <v>11.766</v>
       </c>
     </row>
     <row r="143">
@@ -7149,10 +7149,10 @@
         <v>1.21</v>
       </c>
       <c r="I143" t="n">
-        <v>0.4312</v>
+        <v>0.3764</v>
       </c>
       <c r="J143" t="n">
-        <v>12.936</v>
+        <v>11.292</v>
       </c>
     </row>
     <row r="144">
@@ -7189,10 +7189,10 @@
         <v>1.21</v>
       </c>
       <c r="I144" t="n">
-        <v>0.4312</v>
+        <v>0.3764</v>
       </c>
       <c r="J144" t="n">
-        <v>12.936</v>
+        <v>11.292</v>
       </c>
     </row>
     <row r="145">
@@ -7229,10 +7229,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.1059</v>
+        <v>-0.0881</v>
       </c>
       <c r="J145" t="n">
-        <v>-3.177</v>
+        <v>-2.643</v>
       </c>
     </row>
     <row r="146">
@@ -7269,10 +7269,10 @@
         <v>0.84</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.2192</v>
+        <v>-0.1989</v>
       </c>
       <c r="J146" t="n">
-        <v>-6.576</v>
+        <v>-5.967</v>
       </c>
     </row>
     <row r="147">
@@ -7309,10 +7309,10 @@
         <v>1.22</v>
       </c>
       <c r="I147" t="n">
-        <v>0.5839</v>
+        <v>0.5717</v>
       </c>
       <c r="J147" t="n">
-        <v>17.517</v>
+        <v>17.151</v>
       </c>
     </row>
     <row r="148">
@@ -7349,10 +7349,10 @@
         <v>1.1</v>
       </c>
       <c r="I148" t="n">
-        <v>0.3434</v>
+        <v>0.3014</v>
       </c>
       <c r="J148" t="n">
-        <v>10.302</v>
+        <v>9.042</v>
       </c>
     </row>
     <row r="149">
@@ -7389,10 +7389,10 @@
         <v>0.93</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.2584</v>
+        <v>-0.2201</v>
       </c>
       <c r="J149" t="n">
-        <v>-7.752</v>
+        <v>-6.603</v>
       </c>
     </row>
     <row r="150">
@@ -7429,10 +7429,10 @@
         <v>0.91</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.314</v>
+        <v>-0.2731</v>
       </c>
       <c r="J150" t="n">
-        <v>-9.42</v>
+        <v>-8.193</v>
       </c>
     </row>
     <row r="151">
@@ -7469,10 +7469,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.5629999999999999</v>
+        <v>-0.5226</v>
       </c>
       <c r="J151" t="n">
-        <v>-16.89</v>
+        <v>-15.678</v>
       </c>
     </row>
     <row r="152">
@@ -7509,10 +7509,10 @@
         <v>1.1</v>
       </c>
       <c r="I152" t="n">
-        <v>0.2551</v>
+        <v>0.2081</v>
       </c>
       <c r="J152" t="n">
-        <v>6.3775</v>
+        <v>5.2025</v>
       </c>
     </row>
     <row r="153">
@@ -7549,10 +7549,10 @@
         <v>1.05</v>
       </c>
       <c r="I153" t="n">
-        <v>0.15</v>
+        <v>0.1153</v>
       </c>
       <c r="J153" t="n">
-        <v>3.75</v>
+        <v>2.8825</v>
       </c>
     </row>
     <row r="154">
@@ -7589,10 +7589,10 @@
         <v>1.02</v>
       </c>
       <c r="I154" t="n">
-        <v>0.0751</v>
+        <v>0.0534</v>
       </c>
       <c r="J154" t="n">
-        <v>1.8775</v>
+        <v>1.335</v>
       </c>
     </row>
     <row r="155">
@@ -7629,10 +7629,10 @@
         <v>0.97</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.0573</v>
+        <v>-0.0451</v>
       </c>
       <c r="J155" t="n">
-        <v>-1.4325</v>
+        <v>-1.1275</v>
       </c>
     </row>
     <row r="156">
@@ -7669,10 +7669,10 @@
         <v>0.79</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.261</v>
+        <v>-0.2414</v>
       </c>
       <c r="J156" t="n">
-        <v>-6.525</v>
+        <v>-6.035</v>
       </c>
     </row>
     <row r="157">
@@ -7709,10 +7709,10 @@
         <v>1.42</v>
       </c>
       <c r="I157" t="n">
-        <v>0.8526</v>
+        <v>0.8368</v>
       </c>
       <c r="J157" t="n">
-        <v>21.315</v>
+        <v>20.92</v>
       </c>
     </row>
     <row r="158">
@@ -7749,10 +7749,10 @@
         <v>1.38</v>
       </c>
       <c r="I158" t="n">
-        <v>0.795</v>
+        <v>0.7791</v>
       </c>
       <c r="J158" t="n">
-        <v>19.875</v>
+        <v>19.4775</v>
       </c>
     </row>
     <row r="159">
@@ -7789,10 +7789,10 @@
         <v>1.13</v>
       </c>
       <c r="I159" t="n">
-        <v>0.391</v>
+        <v>0.3553</v>
       </c>
       <c r="J159" t="n">
-        <v>9.775</v>
+        <v>8.8825</v>
       </c>
     </row>
     <row r="160">
@@ -7829,10 +7829,10 @@
         <v>0.96</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.1989</v>
+        <v>-0.1643</v>
       </c>
       <c r="J160" t="n">
-        <v>-4.9725</v>
+        <v>-4.1075</v>
       </c>
     </row>
     <row r="161">
@@ -7869,10 +7869,10 @@
         <v>0.93</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.2907</v>
+        <v>-0.2507</v>
       </c>
       <c r="J161" t="n">
-        <v>-7.2675</v>
+        <v>-6.2675</v>
       </c>
     </row>
   </sheetData>
